--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H337"/>
+  <dimension ref="A1:H361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9882,6 +9882,678 @@
       </c>
       <c r="H337" t="n">
         <v>2419487.69</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>24115784.832</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+      <c r="F338" t="n">
+        <v>0</v>
+      </c>
+      <c r="G338" t="n">
+        <v>0</v>
+      </c>
+      <c r="H338" t="n">
+        <v>24115784.832</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>1703429.248</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0</v>
+      </c>
+      <c r="E339" t="n">
+        <v>0</v>
+      </c>
+      <c r="F339" t="n">
+        <v>0</v>
+      </c>
+      <c r="G339" t="n">
+        <v>0</v>
+      </c>
+      <c r="H339" t="n">
+        <v>1703429.248</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>14588561.447</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0</v>
+      </c>
+      <c r="E340" t="n">
+        <v>0</v>
+      </c>
+      <c r="F340" t="n">
+        <v>0</v>
+      </c>
+      <c r="G340" t="n">
+        <v>-15398.49</v>
+      </c>
+      <c r="H340" t="n">
+        <v>14573162.957</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>40531093.706</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>84657.50999999999</v>
+      </c>
+      <c r="F341" t="n">
+        <v>-84657.50999999999</v>
+      </c>
+      <c r="G341" t="n">
+        <v>15398.49</v>
+      </c>
+      <c r="H341" t="n">
+        <v>40461834.686</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>12170205.469</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" t="n">
+        <v>0</v>
+      </c>
+      <c r="F342" t="n">
+        <v>0</v>
+      </c>
+      <c r="G342" t="n">
+        <v>15055</v>
+      </c>
+      <c r="H342" t="n">
+        <v>12185260.469</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>13376158.213</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" t="n">
+        <v>1548666.366</v>
+      </c>
+      <c r="F343" t="n">
+        <v>-1548666.366</v>
+      </c>
+      <c r="G343" t="n">
+        <v>-15055</v>
+      </c>
+      <c r="H343" t="n">
+        <v>11812436.847</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>1618544.539</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" t="n">
+        <v>0</v>
+      </c>
+      <c r="F344" t="n">
+        <v>0</v>
+      </c>
+      <c r="G344" t="n">
+        <v>19325.803</v>
+      </c>
+      <c r="H344" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>15689235.486</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" t="n">
+        <v>89982.489</v>
+      </c>
+      <c r="F345" t="n">
+        <v>-89982.489</v>
+      </c>
+      <c r="G345" t="n">
+        <v>-19325.803</v>
+      </c>
+      <c r="H345" t="n">
+        <v>15579927.194</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>3387219.03</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0</v>
+      </c>
+      <c r="E346" t="n">
+        <v>0</v>
+      </c>
+      <c r="F346" t="n">
+        <v>0</v>
+      </c>
+      <c r="G346" t="n">
+        <v>0</v>
+      </c>
+      <c r="H346" t="n">
+        <v>3387219.03</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>17764657.013</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0</v>
+      </c>
+      <c r="E347" t="n">
+        <v>0</v>
+      </c>
+      <c r="F347" t="n">
+        <v>0</v>
+      </c>
+      <c r="G347" t="n">
+        <v>0</v>
+      </c>
+      <c r="H347" t="n">
+        <v>17764657.013</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>273789.87</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0</v>
+      </c>
+      <c r="E348" t="n">
+        <v>0</v>
+      </c>
+      <c r="F348" t="n">
+        <v>0</v>
+      </c>
+      <c r="G348" t="n">
+        <v>0</v>
+      </c>
+      <c r="H348" t="n">
+        <v>273789.87</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>3295246.644</v>
+      </c>
+      <c r="D349" t="n">
+        <v>13391.96</v>
+      </c>
+      <c r="E349" t="n">
+        <v>0</v>
+      </c>
+      <c r="F349" t="n">
+        <v>13391.96</v>
+      </c>
+      <c r="G349" t="n">
+        <v>0</v>
+      </c>
+      <c r="H349" t="n">
+        <v>3308638.604</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>12000343.77</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" t="n">
+        <v>0</v>
+      </c>
+      <c r="F350" t="n">
+        <v>0</v>
+      </c>
+      <c r="G350" t="n">
+        <v>-19329.8</v>
+      </c>
+      <c r="H350" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>141843702.183</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" t="n">
+        <v>1049306.3</v>
+      </c>
+      <c r="F351" t="n">
+        <v>-1049306.3</v>
+      </c>
+      <c r="G351" t="n">
+        <v>19329.8</v>
+      </c>
+      <c r="H351" t="n">
+        <v>140813725.683</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>7807094.957</v>
+      </c>
+      <c r="D352" t="n">
+        <v>372209.9</v>
+      </c>
+      <c r="E352" t="n">
+        <v>0</v>
+      </c>
+      <c r="F352" t="n">
+        <v>372209.9</v>
+      </c>
+      <c r="G352" t="n">
+        <v>0</v>
+      </c>
+      <c r="H352" t="n">
+        <v>8179304.857</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>22548466.126</v>
+      </c>
+      <c r="D353" t="n">
+        <v>221231.41</v>
+      </c>
+      <c r="E353" t="n">
+        <v>601350.4300000001</v>
+      </c>
+      <c r="F353" t="n">
+        <v>-380119.02</v>
+      </c>
+      <c r="G353" t="n">
+        <v>0</v>
+      </c>
+      <c r="H353" t="n">
+        <v>22168347.106</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>0</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0</v>
+      </c>
+      <c r="E354" t="n">
+        <v>0</v>
+      </c>
+      <c r="F354" t="n">
+        <v>0</v>
+      </c>
+      <c r="G354" t="n">
+        <v>0</v>
+      </c>
+      <c r="H354" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>0</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>0</v>
+      </c>
+      <c r="F355" t="n">
+        <v>0</v>
+      </c>
+      <c r="G355" t="n">
+        <v>0</v>
+      </c>
+      <c r="H355" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>949634.064</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" t="n">
+        <v>0</v>
+      </c>
+      <c r="F356" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" t="n">
+        <v>0</v>
+      </c>
+      <c r="H356" t="n">
+        <v>949634.064</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>945167.377</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" t="n">
+        <v>0</v>
+      </c>
+      <c r="F357" t="n">
+        <v>0</v>
+      </c>
+      <c r="G357" t="n">
+        <v>0</v>
+      </c>
+      <c r="H357" t="n">
+        <v>945167.377</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>5871594.333</v>
+      </c>
+      <c r="D358" t="n">
+        <v>0</v>
+      </c>
+      <c r="E358" t="n">
+        <v>0</v>
+      </c>
+      <c r="F358" t="n">
+        <v>0</v>
+      </c>
+      <c r="G358" t="n">
+        <v>0</v>
+      </c>
+      <c r="H358" t="n">
+        <v>5871594.333</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>11792129.596</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0</v>
+      </c>
+      <c r="E359" t="n">
+        <v>0</v>
+      </c>
+      <c r="F359" t="n">
+        <v>0</v>
+      </c>
+      <c r="G359" t="n">
+        <v>0</v>
+      </c>
+      <c r="H359" t="n">
+        <v>11792129.596</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>5640957.56</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0</v>
+      </c>
+      <c r="E360" t="n">
+        <v>0</v>
+      </c>
+      <c r="F360" t="n">
+        <v>0</v>
+      </c>
+      <c r="G360" t="n">
+        <v>-19731.12</v>
+      </c>
+      <c r="H360" t="n">
+        <v>5621226.44</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>2419487.69</v>
+      </c>
+      <c r="D361" t="n">
+        <v>0</v>
+      </c>
+      <c r="E361" t="n">
+        <v>0</v>
+      </c>
+      <c r="F361" t="n">
+        <v>0</v>
+      </c>
+      <c r="G361" t="n">
+        <v>19731.12</v>
+      </c>
+      <c r="H361" t="n">
+        <v>2439218.81</v>
       </c>
     </row>
   </sheetData>
@@ -9943,13 +10615,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40531093.706</v>
+        <v>40461834.686</v>
       </c>
       <c r="C3" t="n">
-        <v>14588561.447</v>
+        <v>14573162.957</v>
       </c>
       <c r="D3" t="n">
-        <v>55119655.153</v>
+        <v>55034997.643</v>
       </c>
     </row>
     <row r="4">
@@ -9959,13 +10631,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13376158.213</v>
+        <v>11812436.847</v>
       </c>
       <c r="C4" t="n">
-        <v>12170205.469</v>
+        <v>12185260.469</v>
       </c>
       <c r="D4" t="n">
-        <v>25546363.682</v>
+        <v>23997697.316</v>
       </c>
     </row>
     <row r="5">
@@ -9975,13 +10647,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15689235.486</v>
+        <v>15579927.194</v>
       </c>
       <c r="C5" t="n">
-        <v>1618544.539</v>
+        <v>1637870.342</v>
       </c>
       <c r="D5" t="n">
-        <v>17307780.025</v>
+        <v>17217797.536</v>
       </c>
     </row>
     <row r="6">
@@ -10007,13 +10679,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3295246.644</v>
+        <v>3308638.604</v>
       </c>
       <c r="C7" t="n">
         <v>273789.87</v>
       </c>
       <c r="D7" t="n">
-        <v>3569036.514</v>
+        <v>3582428.474</v>
       </c>
     </row>
     <row r="8">
@@ -10023,13 +10695,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141843702.183</v>
+        <v>140813725.683</v>
       </c>
       <c r="C8" t="n">
-        <v>12000343.77</v>
+        <v>11981013.97</v>
       </c>
       <c r="D8" t="n">
-        <v>153844045.953</v>
+        <v>152794739.653</v>
       </c>
     </row>
     <row r="9">
@@ -10039,13 +10711,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22548466.126</v>
+        <v>22168347.106</v>
       </c>
       <c r="C9" t="n">
-        <v>7807094.957</v>
+        <v>8179304.857</v>
       </c>
       <c r="D9" t="n">
-        <v>30355561.083</v>
+        <v>30347651.963</v>
       </c>
     </row>
     <row r="10">
@@ -10103,10 +10775,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2419487.69</v>
+        <v>2439218.81</v>
       </c>
       <c r="C13" t="n">
-        <v>5640957.56</v>
+        <v>5621226.44</v>
       </c>
       <c r="D13" t="n">
         <v>8060445.25</v>
@@ -10155,13 +10827,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>271908773.282</v>
+        <v>268789512.164</v>
       </c>
       <c r="C2" t="n">
-        <v>88423729.87099999</v>
+        <v>88775861.164</v>
       </c>
       <c r="D2" t="n">
-        <v>360332503.153</v>
+        <v>357565373.3280001</v>
       </c>
     </row>
     <row r="5">
@@ -10255,10 +10927,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2457230.712</v>
+        <v>2541888.222</v>
       </c>
       <c r="E9" t="n">
-        <v>40531093.706</v>
+        <v>40461834.686</v>
       </c>
     </row>
     <row r="10">
@@ -10279,7 +10951,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>14588561.447</v>
+        <v>14573162.957</v>
       </c>
     </row>
     <row r="11">
@@ -10297,10 +10969,10 @@
         <v>7944.85</v>
       </c>
       <c r="D11" t="n">
-        <v>5631138.443</v>
+        <v>7179804.809</v>
       </c>
       <c r="E11" t="n">
-        <v>13376158.213</v>
+        <v>11812436.847</v>
       </c>
     </row>
     <row r="12">
@@ -10321,7 +10993,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>12170205.469</v>
+        <v>12185260.469</v>
       </c>
     </row>
     <row r="13">
@@ -10339,10 +11011,10 @@
         <v>275185.199</v>
       </c>
       <c r="D13" t="n">
-        <v>714523.4770000001</v>
+        <v>804505.966</v>
       </c>
       <c r="E13" t="n">
-        <v>15689235.486</v>
+        <v>15579927.194</v>
       </c>
     </row>
     <row r="14">
@@ -10363,7 +11035,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1618544.539</v>
+        <v>1637870.342</v>
       </c>
     </row>
     <row r="15">
@@ -10420,13 +11092,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>13391.96</v>
       </c>
       <c r="D17" t="n">
         <v>346959.6</v>
       </c>
       <c r="E17" t="n">
-        <v>3295246.644</v>
+        <v>3308638.604</v>
       </c>
     </row>
     <row r="18">
@@ -10465,10 +11137,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15020099.25</v>
+        <v>16069405.55</v>
       </c>
       <c r="E19" t="n">
-        <v>141843702.183</v>
+        <v>140813725.683</v>
       </c>
     </row>
     <row r="20">
@@ -10489,7 +11161,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>12000343.77</v>
+        <v>11981013.97</v>
       </c>
     </row>
     <row r="21">
@@ -10504,13 +11176,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10089.96</v>
+        <v>231321.37</v>
       </c>
       <c r="D21" t="n">
-        <v>2964461.58</v>
+        <v>3565812.01</v>
       </c>
       <c r="E21" t="n">
-        <v>22548466.126</v>
+        <v>22168347.106</v>
       </c>
     </row>
     <row r="22">
@@ -10525,13 +11197,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>372209.9</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>7807094.957</v>
+        <v>8179304.857</v>
       </c>
     </row>
     <row r="23">
@@ -10678,7 +11350,7 @@
         <v>95827.17</v>
       </c>
       <c r="E29" t="n">
-        <v>2419487.69</v>
+        <v>2439218.81</v>
       </c>
     </row>
     <row r="30">
@@ -10699,7 +11371,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>5640957.56</v>
+        <v>5621226.44</v>
       </c>
     </row>
   </sheetData>

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H361"/>
+  <dimension ref="A1:H385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10553,6 +10553,678 @@
         <v>19731.12</v>
       </c>
       <c r="H361" t="n">
+        <v>2439218.81</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>24115784.832</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0</v>
+      </c>
+      <c r="E362" t="n">
+        <v>0</v>
+      </c>
+      <c r="F362" t="n">
+        <v>0</v>
+      </c>
+      <c r="G362" t="n">
+        <v>0</v>
+      </c>
+      <c r="H362" t="n">
+        <v>24115784.832</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>1703429.248</v>
+      </c>
+      <c r="D363" t="n">
+        <v>0</v>
+      </c>
+      <c r="E363" t="n">
+        <v>0</v>
+      </c>
+      <c r="F363" t="n">
+        <v>0</v>
+      </c>
+      <c r="G363" t="n">
+        <v>0</v>
+      </c>
+      <c r="H363" t="n">
+        <v>1703429.248</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>14573162.957</v>
+      </c>
+      <c r="D364" t="n">
+        <v>0</v>
+      </c>
+      <c r="E364" t="n">
+        <v>0</v>
+      </c>
+      <c r="F364" t="n">
+        <v>0</v>
+      </c>
+      <c r="G364" t="n">
+        <v>-607094.34</v>
+      </c>
+      <c r="H364" t="n">
+        <v>13966068.617</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>40461834.686</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0</v>
+      </c>
+      <c r="E365" t="n">
+        <v>1207435.143</v>
+      </c>
+      <c r="F365" t="n">
+        <v>-1207435.143</v>
+      </c>
+      <c r="G365" t="n">
+        <v>607094.34</v>
+      </c>
+      <c r="H365" t="n">
+        <v>39861493.883</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>12185260.469</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" t="n">
+        <v>0</v>
+      </c>
+      <c r="F366" t="n">
+        <v>0</v>
+      </c>
+      <c r="G366" t="n">
+        <v>-183273.614</v>
+      </c>
+      <c r="H366" t="n">
+        <v>12001986.855</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>11812436.847</v>
+      </c>
+      <c r="D367" t="n">
+        <v>24897.79</v>
+      </c>
+      <c r="E367" t="n">
+        <v>609899.55</v>
+      </c>
+      <c r="F367" t="n">
+        <v>-585001.76</v>
+      </c>
+      <c r="G367" t="n">
+        <v>183273.614</v>
+      </c>
+      <c r="H367" t="n">
+        <v>11410708.701</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D368" t="n">
+        <v>0</v>
+      </c>
+      <c r="E368" t="n">
+        <v>0</v>
+      </c>
+      <c r="F368" t="n">
+        <v>0</v>
+      </c>
+      <c r="G368" t="n">
+        <v>0</v>
+      </c>
+      <c r="H368" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>15579927.194</v>
+      </c>
+      <c r="D369" t="n">
+        <v>918.2</v>
+      </c>
+      <c r="E369" t="n">
+        <v>0</v>
+      </c>
+      <c r="F369" t="n">
+        <v>918.2</v>
+      </c>
+      <c r="G369" t="n">
+        <v>0</v>
+      </c>
+      <c r="H369" t="n">
+        <v>15580845.394</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>3387219.03</v>
+      </c>
+      <c r="D370" t="n">
+        <v>0</v>
+      </c>
+      <c r="E370" t="n">
+        <v>0</v>
+      </c>
+      <c r="F370" t="n">
+        <v>0</v>
+      </c>
+      <c r="G370" t="n">
+        <v>0</v>
+      </c>
+      <c r="H370" t="n">
+        <v>3387219.03</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>17764657.013</v>
+      </c>
+      <c r="D371" t="n">
+        <v>0</v>
+      </c>
+      <c r="E371" t="n">
+        <v>0</v>
+      </c>
+      <c r="F371" t="n">
+        <v>0</v>
+      </c>
+      <c r="G371" t="n">
+        <v>0</v>
+      </c>
+      <c r="H371" t="n">
+        <v>17764657.013</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>273789.87</v>
+      </c>
+      <c r="D372" t="n">
+        <v>0</v>
+      </c>
+      <c r="E372" t="n">
+        <v>0</v>
+      </c>
+      <c r="F372" t="n">
+        <v>0</v>
+      </c>
+      <c r="G372" t="n">
+        <v>0</v>
+      </c>
+      <c r="H372" t="n">
+        <v>273789.87</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>3308638.604</v>
+      </c>
+      <c r="D373" t="n">
+        <v>0</v>
+      </c>
+      <c r="E373" t="n">
+        <v>0</v>
+      </c>
+      <c r="F373" t="n">
+        <v>0</v>
+      </c>
+      <c r="G373" t="n">
+        <v>0</v>
+      </c>
+      <c r="H373" t="n">
+        <v>3308638.604</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D374" t="n">
+        <v>0</v>
+      </c>
+      <c r="E374" t="n">
+        <v>0</v>
+      </c>
+      <c r="F374" t="n">
+        <v>0</v>
+      </c>
+      <c r="G374" t="n">
+        <v>0</v>
+      </c>
+      <c r="H374" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>140813725.683</v>
+      </c>
+      <c r="D375" t="n">
+        <v>0</v>
+      </c>
+      <c r="E375" t="n">
+        <v>0</v>
+      </c>
+      <c r="F375" t="n">
+        <v>0</v>
+      </c>
+      <c r="G375" t="n">
+        <v>0</v>
+      </c>
+      <c r="H375" t="n">
+        <v>140813725.683</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>8179304.857</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0</v>
+      </c>
+      <c r="E376" t="n">
+        <v>0</v>
+      </c>
+      <c r="F376" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" t="n">
+        <v>0</v>
+      </c>
+      <c r="H376" t="n">
+        <v>8179304.857</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>22168347.106</v>
+      </c>
+      <c r="D377" t="n">
+        <v>0</v>
+      </c>
+      <c r="E377" t="n">
+        <v>600017.8199999999</v>
+      </c>
+      <c r="F377" t="n">
+        <v>-600017.8199999999</v>
+      </c>
+      <c r="G377" t="n">
+        <v>0</v>
+      </c>
+      <c r="H377" t="n">
+        <v>21568329.286</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>0</v>
+      </c>
+      <c r="D378" t="n">
+        <v>0</v>
+      </c>
+      <c r="E378" t="n">
+        <v>0</v>
+      </c>
+      <c r="F378" t="n">
+        <v>0</v>
+      </c>
+      <c r="G378" t="n">
+        <v>0</v>
+      </c>
+      <c r="H378" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>0</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" t="n">
+        <v>0</v>
+      </c>
+      <c r="F379" t="n">
+        <v>0</v>
+      </c>
+      <c r="G379" t="n">
+        <v>0</v>
+      </c>
+      <c r="H379" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>949634.064</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0</v>
+      </c>
+      <c r="E380" t="n">
+        <v>0</v>
+      </c>
+      <c r="F380" t="n">
+        <v>0</v>
+      </c>
+      <c r="G380" t="n">
+        <v>0</v>
+      </c>
+      <c r="H380" t="n">
+        <v>949634.064</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>945167.377</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0</v>
+      </c>
+      <c r="E381" t="n">
+        <v>0</v>
+      </c>
+      <c r="F381" t="n">
+        <v>0</v>
+      </c>
+      <c r="G381" t="n">
+        <v>0</v>
+      </c>
+      <c r="H381" t="n">
+        <v>945167.377</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>5871594.333</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0</v>
+      </c>
+      <c r="E382" t="n">
+        <v>0</v>
+      </c>
+      <c r="F382" t="n">
+        <v>0</v>
+      </c>
+      <c r="G382" t="n">
+        <v>0</v>
+      </c>
+      <c r="H382" t="n">
+        <v>5871594.333</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>11792129.596</v>
+      </c>
+      <c r="D383" t="n">
+        <v>0</v>
+      </c>
+      <c r="E383" t="n">
+        <v>0</v>
+      </c>
+      <c r="F383" t="n">
+        <v>0</v>
+      </c>
+      <c r="G383" t="n">
+        <v>0</v>
+      </c>
+      <c r="H383" t="n">
+        <v>11792129.596</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>5621226.44</v>
+      </c>
+      <c r="D384" t="n">
+        <v>0</v>
+      </c>
+      <c r="E384" t="n">
+        <v>0</v>
+      </c>
+      <c r="F384" t="n">
+        <v>0</v>
+      </c>
+      <c r="G384" t="n">
+        <v>0</v>
+      </c>
+      <c r="H384" t="n">
+        <v>5621226.44</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>2439218.81</v>
+      </c>
+      <c r="D385" t="n">
+        <v>0</v>
+      </c>
+      <c r="E385" t="n">
+        <v>0</v>
+      </c>
+      <c r="F385" t="n">
+        <v>0</v>
+      </c>
+      <c r="G385" t="n">
+        <v>0</v>
+      </c>
+      <c r="H385" t="n">
         <v>2439218.81</v>
       </c>
     </row>
@@ -10615,13 +11287,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40461834.686</v>
+        <v>39861493.883</v>
       </c>
       <c r="C3" t="n">
-        <v>14573162.957</v>
+        <v>13966068.617</v>
       </c>
       <c r="D3" t="n">
-        <v>55034997.643</v>
+        <v>53827562.5</v>
       </c>
     </row>
     <row r="4">
@@ -10631,13 +11303,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11812436.847</v>
+        <v>11410708.701</v>
       </c>
       <c r="C4" t="n">
-        <v>12185260.469</v>
+        <v>12001986.855</v>
       </c>
       <c r="D4" t="n">
-        <v>23997697.316</v>
+        <v>23412695.556</v>
       </c>
     </row>
     <row r="5">
@@ -10647,13 +11319,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15579927.194</v>
+        <v>15580845.394</v>
       </c>
       <c r="C5" t="n">
         <v>1637870.342</v>
       </c>
       <c r="D5" t="n">
-        <v>17217797.536</v>
+        <v>17218715.736</v>
       </c>
     </row>
     <row r="6">
@@ -10711,13 +11383,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22168347.106</v>
+        <v>21568329.286</v>
       </c>
       <c r="C9" t="n">
         <v>8179304.857</v>
       </c>
       <c r="D9" t="n">
-        <v>30347651.963</v>
+        <v>29747634.143</v>
       </c>
     </row>
     <row r="10">
@@ -10795,7 +11467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10823,251 +11495,246 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>267188343.595</v>
+      </c>
+      <c r="C2" t="n">
+        <v>87985493.20999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>355173836.805</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B3" t="n">
         <v>268789512.164</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C3" t="n">
         <v>88775861.164</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>357565373.3280001</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt; [상세] 창고별 월간 입출고 및 기말 재고</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>YearMonth</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Region_Type</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>RECEIVED</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>WITHDRAWN</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>TOTAL_TODAY</t>
         </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ASAHI DEPOSITORY LLC Eligible</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3186015.09</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1703429.248</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ASAHI DEPOSITORY LLC Registered</t>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>824168.84</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>24115784.832</v>
+        <v>1703429.248</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BRINK'S, INC. Eligible</t>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2541888.222</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>40461834.686</v>
+        <v>24115784.832</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRINK'S, INC. Registered</t>
+          <t>BRINK'S, INC. Eligible</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1207435.143</v>
       </c>
       <c r="E10" t="n">
-        <v>14573162.957</v>
+        <v>39861493.883</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CNT DEPOSITORY, INC. Eligible</t>
+          <t>BRINK'S, INC. Registered</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7944.85</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>7179804.809</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>11812436.847</v>
+        <v>13966068.617</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CNT DEPOSITORY, INC. Registered</t>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>291987.7</v>
+        <v>24897.79</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>609899.55</v>
       </c>
       <c r="E12" t="n">
-        <v>12185260.469</v>
+        <v>11410708.701</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DELAWARE DEPOSITORY Eligible</t>
+          <t>CNT DEPOSITORY, INC. Registered</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>275185.199</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>804505.966</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>15579927.194</v>
+        <v>12001986.855</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DELAWARE DEPOSITORY Registered</t>
+          <t>DELAWARE DEPOSITORY Eligible</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>918.2</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1637870.342</v>
+        <v>15580845.394</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HSBC BANK, USA Eligible</t>
+          <t>DELAWARE DEPOSITORY Registered</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3581337.69</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>17764657.013</v>
+        <v>1637870.342</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HSBC BANK, USA Registered</t>
+          <t>HSBC BANK, USA Eligible</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -11077,39 +11744,39 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>3387219.03</v>
+        <v>17764657.013</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+          <t>HSBC BANK, USA Registered</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13391.96</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>346959.6</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>3308638.604</v>
+        <v>3387219.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -11119,39 +11786,39 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>273789.87</v>
+        <v>3308638.604</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JP MORGAN CHASE BANK NA Eligible</t>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16069405.55</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>140813725.683</v>
+        <v>273789.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JP MORGAN CHASE BANK NA Registered</t>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -11161,60 +11828,60 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>11981013.97</v>
+        <v>140813725.683</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>231321.37</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3565812.01</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>22168347.106</v>
+        <v>11981013.97</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>372209.9</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>600017.8199999999</v>
       </c>
       <c r="E22" t="n">
-        <v>8179304.857</v>
+        <v>21568329.286</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -11224,18 +11891,18 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>8179304.857</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -11251,33 +11918,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MALCA-AMIT USA, LLC Eligible</t>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>128731</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>945167.377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MALCA-AMIT USA, LLC Registered</t>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -11287,39 +11954,39 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>949634.064</v>
+        <v>945167.377</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+          <t>MALCA-AMIT USA, LLC Registered</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1854483.234</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>11792129.596</v>
+        <v>949634.064</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -11329,48 +11996,573 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>5871594.333</v>
+        <v>11792129.596</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>95827.17</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>2439218.81</v>
+        <v>5871594.333</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2439218.81</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5621226.44</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3186015.09</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1703429.248</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>824168.84</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>24115784.832</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2541888.222</v>
+      </c>
+      <c r="E34" t="n">
+        <v>40461834.686</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>14573162.957</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>7944.85</v>
+      </c>
+      <c r="D36" t="n">
+        <v>7179804.809</v>
+      </c>
+      <c r="E36" t="n">
+        <v>11812436.847</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>291987.7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>12185260.469</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>275185.199</v>
+      </c>
+      <c r="D38" t="n">
+        <v>804505.966</v>
+      </c>
+      <c r="E38" t="n">
+        <v>15579927.194</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3581337.69</v>
+      </c>
+      <c r="E40" t="n">
+        <v>17764657.013</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3387219.03</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>13391.96</v>
+      </c>
+      <c r="D42" t="n">
+        <v>346959.6</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3308638.604</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>273789.87</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16069405.55</v>
+      </c>
+      <c r="E44" t="n">
+        <v>140813725.683</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>231321.37</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3565812.01</v>
+      </c>
+      <c r="E46" t="n">
+        <v>22168347.106</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>372209.9</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>8179304.857</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>128731</v>
+      </c>
+      <c r="E50" t="n">
+        <v>945167.377</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>949634.064</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1854483.234</v>
+      </c>
+      <c r="E52" t="n">
+        <v>11792129.596</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>5871594.333</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>95827.17</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2439218.81</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>STONEX PRECIOUS METALS LLC Registered</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C55" t="n">
         <v>392565.06</v>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
         <v>5621226.44</v>
       </c>
     </row>

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H385"/>
+  <dimension ref="A1:H409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11225,6 +11225,678 @@
         <v>0</v>
       </c>
       <c r="H385" t="n">
+        <v>2439218.81</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>24115784.832</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0</v>
+      </c>
+      <c r="E386" t="n">
+        <v>0</v>
+      </c>
+      <c r="F386" t="n">
+        <v>0</v>
+      </c>
+      <c r="G386" t="n">
+        <v>0</v>
+      </c>
+      <c r="H386" t="n">
+        <v>24115784.832</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>1703429.248</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0</v>
+      </c>
+      <c r="E387" t="n">
+        <v>64999.2</v>
+      </c>
+      <c r="F387" t="n">
+        <v>-64999.2</v>
+      </c>
+      <c r="G387" t="n">
+        <v>0</v>
+      </c>
+      <c r="H387" t="n">
+        <v>1638430.048</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>13966068.617</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0</v>
+      </c>
+      <c r="E388" t="n">
+        <v>0</v>
+      </c>
+      <c r="F388" t="n">
+        <v>0</v>
+      </c>
+      <c r="G388" t="n">
+        <v>-379199.63</v>
+      </c>
+      <c r="H388" t="n">
+        <v>13586868.987</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>39861493.883</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0</v>
+      </c>
+      <c r="E389" t="n">
+        <v>600589.7</v>
+      </c>
+      <c r="F389" t="n">
+        <v>-600589.7</v>
+      </c>
+      <c r="G389" t="n">
+        <v>379199.63</v>
+      </c>
+      <c r="H389" t="n">
+        <v>39640103.813</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>12001986.855</v>
+      </c>
+      <c r="D390" t="n">
+        <v>0</v>
+      </c>
+      <c r="E390" t="n">
+        <v>0</v>
+      </c>
+      <c r="F390" t="n">
+        <v>0</v>
+      </c>
+      <c r="G390" t="n">
+        <v>0</v>
+      </c>
+      <c r="H390" t="n">
+        <v>12001986.855</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>11410708.701</v>
+      </c>
+      <c r="D391" t="n">
+        <v>0</v>
+      </c>
+      <c r="E391" t="n">
+        <v>800321.617</v>
+      </c>
+      <c r="F391" t="n">
+        <v>-800321.617</v>
+      </c>
+      <c r="G391" t="n">
+        <v>0</v>
+      </c>
+      <c r="H391" t="n">
+        <v>10610387.084</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D392" t="n">
+        <v>0</v>
+      </c>
+      <c r="E392" t="n">
+        <v>0</v>
+      </c>
+      <c r="F392" t="n">
+        <v>0</v>
+      </c>
+      <c r="G392" t="n">
+        <v>0</v>
+      </c>
+      <c r="H392" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>15580845.394</v>
+      </c>
+      <c r="D393" t="n">
+        <v>0</v>
+      </c>
+      <c r="E393" t="n">
+        <v>918.2</v>
+      </c>
+      <c r="F393" t="n">
+        <v>-918.2</v>
+      </c>
+      <c r="G393" t="n">
+        <v>0</v>
+      </c>
+      <c r="H393" t="n">
+        <v>15579927.194</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>3387219.03</v>
+      </c>
+      <c r="D394" t="n">
+        <v>0</v>
+      </c>
+      <c r="E394" t="n">
+        <v>0</v>
+      </c>
+      <c r="F394" t="n">
+        <v>0</v>
+      </c>
+      <c r="G394" t="n">
+        <v>0</v>
+      </c>
+      <c r="H394" t="n">
+        <v>3387219.03</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>17764657.013</v>
+      </c>
+      <c r="D395" t="n">
+        <v>0</v>
+      </c>
+      <c r="E395" t="n">
+        <v>0</v>
+      </c>
+      <c r="F395" t="n">
+        <v>0</v>
+      </c>
+      <c r="G395" t="n">
+        <v>0</v>
+      </c>
+      <c r="H395" t="n">
+        <v>17764657.013</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>273789.87</v>
+      </c>
+      <c r="D396" t="n">
+        <v>0</v>
+      </c>
+      <c r="E396" t="n">
+        <v>0</v>
+      </c>
+      <c r="F396" t="n">
+        <v>0</v>
+      </c>
+      <c r="G396" t="n">
+        <v>-95274.67999999999</v>
+      </c>
+      <c r="H396" t="n">
+        <v>178515.19</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>3308638.604</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0</v>
+      </c>
+      <c r="E397" t="n">
+        <v>603511.95</v>
+      </c>
+      <c r="F397" t="n">
+        <v>-603511.95</v>
+      </c>
+      <c r="G397" t="n">
+        <v>95274.67999999999</v>
+      </c>
+      <c r="H397" t="n">
+        <v>2800401.334</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D398" t="n">
+        <v>0</v>
+      </c>
+      <c r="E398" t="n">
+        <v>0</v>
+      </c>
+      <c r="F398" t="n">
+        <v>0</v>
+      </c>
+      <c r="G398" t="n">
+        <v>0</v>
+      </c>
+      <c r="H398" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>140813725.683</v>
+      </c>
+      <c r="D399" t="n">
+        <v>0</v>
+      </c>
+      <c r="E399" t="n">
+        <v>0</v>
+      </c>
+      <c r="F399" t="n">
+        <v>0</v>
+      </c>
+      <c r="G399" t="n">
+        <v>0</v>
+      </c>
+      <c r="H399" t="n">
+        <v>140813725.683</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>8179304.857</v>
+      </c>
+      <c r="D400" t="n">
+        <v>0</v>
+      </c>
+      <c r="E400" t="n">
+        <v>0</v>
+      </c>
+      <c r="F400" t="n">
+        <v>0</v>
+      </c>
+      <c r="G400" t="n">
+        <v>0</v>
+      </c>
+      <c r="H400" t="n">
+        <v>8179304.857</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>21568329.286</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0</v>
+      </c>
+      <c r="E401" t="n">
+        <v>0</v>
+      </c>
+      <c r="F401" t="n">
+        <v>0</v>
+      </c>
+      <c r="G401" t="n">
+        <v>0</v>
+      </c>
+      <c r="H401" t="n">
+        <v>21568329.286</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>0</v>
+      </c>
+      <c r="D402" t="n">
+        <v>0</v>
+      </c>
+      <c r="E402" t="n">
+        <v>0</v>
+      </c>
+      <c r="F402" t="n">
+        <v>0</v>
+      </c>
+      <c r="G402" t="n">
+        <v>0</v>
+      </c>
+      <c r="H402" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>0</v>
+      </c>
+      <c r="D403" t="n">
+        <v>0</v>
+      </c>
+      <c r="E403" t="n">
+        <v>0</v>
+      </c>
+      <c r="F403" t="n">
+        <v>0</v>
+      </c>
+      <c r="G403" t="n">
+        <v>0</v>
+      </c>
+      <c r="H403" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>949634.064</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0</v>
+      </c>
+      <c r="E404" t="n">
+        <v>0</v>
+      </c>
+      <c r="F404" t="n">
+        <v>0</v>
+      </c>
+      <c r="G404" t="n">
+        <v>-367523.727</v>
+      </c>
+      <c r="H404" t="n">
+        <v>582110.3370000001</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>945167.377</v>
+      </c>
+      <c r="D405" t="n">
+        <v>0</v>
+      </c>
+      <c r="E405" t="n">
+        <v>0</v>
+      </c>
+      <c r="F405" t="n">
+        <v>0</v>
+      </c>
+      <c r="G405" t="n">
+        <v>367523.727</v>
+      </c>
+      <c r="H405" t="n">
+        <v>1312691.104</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>5871594.333</v>
+      </c>
+      <c r="D406" t="n">
+        <v>0</v>
+      </c>
+      <c r="E406" t="n">
+        <v>0</v>
+      </c>
+      <c r="F406" t="n">
+        <v>0</v>
+      </c>
+      <c r="G406" t="n">
+        <v>0</v>
+      </c>
+      <c r="H406" t="n">
+        <v>5871594.333</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>11792129.596</v>
+      </c>
+      <c r="D407" t="n">
+        <v>0</v>
+      </c>
+      <c r="E407" t="n">
+        <v>883624.584</v>
+      </c>
+      <c r="F407" t="n">
+        <v>-883624.584</v>
+      </c>
+      <c r="G407" t="n">
+        <v>0</v>
+      </c>
+      <c r="H407" t="n">
+        <v>10908505.012</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>5621226.44</v>
+      </c>
+      <c r="D408" t="n">
+        <v>0</v>
+      </c>
+      <c r="E408" t="n">
+        <v>0</v>
+      </c>
+      <c r="F408" t="n">
+        <v>0</v>
+      </c>
+      <c r="G408" t="n">
+        <v>0</v>
+      </c>
+      <c r="H408" t="n">
+        <v>5621226.44</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>2439218.81</v>
+      </c>
+      <c r="D409" t="n">
+        <v>0</v>
+      </c>
+      <c r="E409" t="n">
+        <v>0</v>
+      </c>
+      <c r="F409" t="n">
+        <v>0</v>
+      </c>
+      <c r="G409" t="n">
+        <v>0</v>
+      </c>
+      <c r="H409" t="n">
         <v>2439218.81</v>
       </c>
     </row>
@@ -11271,13 +11943,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1703429.248</v>
+        <v>1638430.048</v>
       </c>
       <c r="C2" t="n">
         <v>24115784.832</v>
       </c>
       <c r="D2" t="n">
-        <v>25819214.08</v>
+        <v>25754214.88</v>
       </c>
     </row>
     <row r="3">
@@ -11287,13 +11959,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39861493.883</v>
+        <v>39640103.813</v>
       </c>
       <c r="C3" t="n">
-        <v>13966068.617</v>
+        <v>13586868.987</v>
       </c>
       <c r="D3" t="n">
-        <v>53827562.5</v>
+        <v>53226972.8</v>
       </c>
     </row>
     <row r="4">
@@ -11303,13 +11975,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11410708.701</v>
+        <v>10610387.084</v>
       </c>
       <c r="C4" t="n">
         <v>12001986.855</v>
       </c>
       <c r="D4" t="n">
-        <v>23412695.556</v>
+        <v>22612373.939</v>
       </c>
     </row>
     <row r="5">
@@ -11319,13 +11991,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15580845.394</v>
+        <v>15579927.194</v>
       </c>
       <c r="C5" t="n">
         <v>1637870.342</v>
       </c>
       <c r="D5" t="n">
-        <v>17218715.736</v>
+        <v>17217797.536</v>
       </c>
     </row>
     <row r="6">
@@ -11351,13 +12023,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3308638.604</v>
+        <v>2800401.334</v>
       </c>
       <c r="C7" t="n">
-        <v>273789.87</v>
+        <v>178515.19</v>
       </c>
       <c r="D7" t="n">
-        <v>3582428.474</v>
+        <v>2978916.524</v>
       </c>
     </row>
     <row r="8">
@@ -11415,10 +12087,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>945167.377</v>
+        <v>1312691.104</v>
       </c>
       <c r="C11" t="n">
-        <v>949634.064</v>
+        <v>582110.3370000001</v>
       </c>
       <c r="D11" t="n">
         <v>1894801.441</v>
@@ -11431,13 +12103,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11792129.596</v>
+        <v>10908505.012</v>
       </c>
       <c r="C12" t="n">
         <v>5871594.333</v>
       </c>
       <c r="D12" t="n">
-        <v>17663723.929</v>
+        <v>16780099.345</v>
       </c>
     </row>
     <row r="13">
@@ -11499,13 +12171,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>267188343.595</v>
+        <v>265076376.381</v>
       </c>
       <c r="C2" t="n">
-        <v>87985493.20999999</v>
+        <v>87143495.17299999</v>
       </c>
       <c r="D2" t="n">
-        <v>355173836.805</v>
+        <v>352219871.554</v>
       </c>
     </row>
     <row r="3">
@@ -11573,10 +12245,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>64999.2</v>
       </c>
       <c r="E8" t="n">
-        <v>1703429.248</v>
+        <v>1638430.048</v>
       </c>
     </row>
     <row r="9">
@@ -11615,10 +12287,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1207435.143</v>
+        <v>1808024.843</v>
       </c>
       <c r="E10" t="n">
-        <v>39861493.883</v>
+        <v>39640103.813</v>
       </c>
     </row>
     <row r="11">
@@ -11639,7 +12311,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>13966068.617</v>
+        <v>13586868.987</v>
       </c>
     </row>
     <row r="12">
@@ -11657,10 +12329,10 @@
         <v>24897.79</v>
       </c>
       <c r="D12" t="n">
-        <v>609899.55</v>
+        <v>1410221.167</v>
       </c>
       <c r="E12" t="n">
-        <v>11410708.701</v>
+        <v>10610387.084</v>
       </c>
     </row>
     <row r="13">
@@ -11699,10 +12371,10 @@
         <v>918.2</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>918.2</v>
       </c>
       <c r="E14" t="n">
-        <v>15580845.394</v>
+        <v>15579927.194</v>
       </c>
     </row>
     <row r="15">
@@ -11783,10 +12455,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>603511.95</v>
       </c>
       <c r="E18" t="n">
-        <v>3308638.604</v>
+        <v>2800401.334</v>
       </c>
     </row>
     <row r="19">
@@ -11807,7 +12479,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>273789.87</v>
+        <v>178515.19</v>
       </c>
     </row>
     <row r="20">
@@ -11954,7 +12626,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>945167.377</v>
+        <v>1312691.104</v>
       </c>
     </row>
     <row r="27">
@@ -11975,7 +12647,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>949634.064</v>
+        <v>582110.3370000001</v>
       </c>
     </row>
     <row r="28">
@@ -11993,10 +12665,10 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>883624.584</v>
       </c>
       <c r="E28" t="n">
-        <v>11792129.596</v>
+        <v>10908505.012</v>
       </c>
     </row>
     <row r="29">

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H409"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11898,6 +11898,678 @@
       </c>
       <c r="H409" t="n">
         <v>2439218.81</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>24115784.832</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0</v>
+      </c>
+      <c r="E410" t="n">
+        <v>0</v>
+      </c>
+      <c r="F410" t="n">
+        <v>0</v>
+      </c>
+      <c r="G410" t="n">
+        <v>-1883862.24</v>
+      </c>
+      <c r="H410" t="n">
+        <v>22231922.592</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>1638430.048</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0</v>
+      </c>
+      <c r="E411" t="n">
+        <v>0</v>
+      </c>
+      <c r="F411" t="n">
+        <v>0</v>
+      </c>
+      <c r="G411" t="n">
+        <v>1883862.24</v>
+      </c>
+      <c r="H411" t="n">
+        <v>3522292.288</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>13586868.987</v>
+      </c>
+      <c r="D412" t="n">
+        <v>0</v>
+      </c>
+      <c r="E412" t="n">
+        <v>0</v>
+      </c>
+      <c r="F412" t="n">
+        <v>0</v>
+      </c>
+      <c r="G412" t="n">
+        <v>-302937.884</v>
+      </c>
+      <c r="H412" t="n">
+        <v>13283931.103</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>39640103.813</v>
+      </c>
+      <c r="D413" t="n">
+        <v>0</v>
+      </c>
+      <c r="E413" t="n">
+        <v>332603.13</v>
+      </c>
+      <c r="F413" t="n">
+        <v>-332603.13</v>
+      </c>
+      <c r="G413" t="n">
+        <v>302937.884</v>
+      </c>
+      <c r="H413" t="n">
+        <v>39610438.567</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>12001986.855</v>
+      </c>
+      <c r="D414" t="n">
+        <v>0</v>
+      </c>
+      <c r="E414" t="n">
+        <v>0</v>
+      </c>
+      <c r="F414" t="n">
+        <v>0</v>
+      </c>
+      <c r="G414" t="n">
+        <v>0</v>
+      </c>
+      <c r="H414" t="n">
+        <v>12001986.855</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>10610387.084</v>
+      </c>
+      <c r="D415" t="n">
+        <v>3994.72</v>
+      </c>
+      <c r="E415" t="n">
+        <v>387345.529</v>
+      </c>
+      <c r="F415" t="n">
+        <v>-383350.809</v>
+      </c>
+      <c r="G415" t="n">
+        <v>0</v>
+      </c>
+      <c r="H415" t="n">
+        <v>10227036.275</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D416" t="n">
+        <v>0</v>
+      </c>
+      <c r="E416" t="n">
+        <v>0</v>
+      </c>
+      <c r="F416" t="n">
+        <v>0</v>
+      </c>
+      <c r="G416" t="n">
+        <v>0</v>
+      </c>
+      <c r="H416" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>15579927.194</v>
+      </c>
+      <c r="D417" t="n">
+        <v>0</v>
+      </c>
+      <c r="E417" t="n">
+        <v>14918.81</v>
+      </c>
+      <c r="F417" t="n">
+        <v>-14918.81</v>
+      </c>
+      <c r="G417" t="n">
+        <v>0</v>
+      </c>
+      <c r="H417" t="n">
+        <v>15565008.384</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>3387219.03</v>
+      </c>
+      <c r="D418" t="n">
+        <v>0</v>
+      </c>
+      <c r="E418" t="n">
+        <v>0</v>
+      </c>
+      <c r="F418" t="n">
+        <v>0</v>
+      </c>
+      <c r="G418" t="n">
+        <v>0</v>
+      </c>
+      <c r="H418" t="n">
+        <v>3387219.03</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>17764657.013</v>
+      </c>
+      <c r="D419" t="n">
+        <v>0</v>
+      </c>
+      <c r="E419" t="n">
+        <v>15260.8</v>
+      </c>
+      <c r="F419" t="n">
+        <v>-15260.8</v>
+      </c>
+      <c r="G419" t="n">
+        <v>0</v>
+      </c>
+      <c r="H419" t="n">
+        <v>17749396.213</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>178515.19</v>
+      </c>
+      <c r="D420" t="n">
+        <v>0</v>
+      </c>
+      <c r="E420" t="n">
+        <v>0</v>
+      </c>
+      <c r="F420" t="n">
+        <v>0</v>
+      </c>
+      <c r="G420" t="n">
+        <v>0</v>
+      </c>
+      <c r="H420" t="n">
+        <v>178515.19</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>2800401.334</v>
+      </c>
+      <c r="D421" t="n">
+        <v>0</v>
+      </c>
+      <c r="E421" t="n">
+        <v>0</v>
+      </c>
+      <c r="F421" t="n">
+        <v>0</v>
+      </c>
+      <c r="G421" t="n">
+        <v>0</v>
+      </c>
+      <c r="H421" t="n">
+        <v>2800401.334</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D422" t="n">
+        <v>0</v>
+      </c>
+      <c r="E422" t="n">
+        <v>0</v>
+      </c>
+      <c r="F422" t="n">
+        <v>0</v>
+      </c>
+      <c r="G422" t="n">
+        <v>0</v>
+      </c>
+      <c r="H422" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>140813725.683</v>
+      </c>
+      <c r="D423" t="n">
+        <v>0</v>
+      </c>
+      <c r="E423" t="n">
+        <v>0</v>
+      </c>
+      <c r="F423" t="n">
+        <v>0</v>
+      </c>
+      <c r="G423" t="n">
+        <v>0</v>
+      </c>
+      <c r="H423" t="n">
+        <v>140813725.683</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>8179304.857</v>
+      </c>
+      <c r="D424" t="n">
+        <v>0</v>
+      </c>
+      <c r="E424" t="n">
+        <v>0</v>
+      </c>
+      <c r="F424" t="n">
+        <v>0</v>
+      </c>
+      <c r="G424" t="n">
+        <v>-3731045.67</v>
+      </c>
+      <c r="H424" t="n">
+        <v>4448259.187</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>21568329.286</v>
+      </c>
+      <c r="D425" t="n">
+        <v>0</v>
+      </c>
+      <c r="E425" t="n">
+        <v>0</v>
+      </c>
+      <c r="F425" t="n">
+        <v>0</v>
+      </c>
+      <c r="G425" t="n">
+        <v>3731045.67</v>
+      </c>
+      <c r="H425" t="n">
+        <v>25299374.956</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>0</v>
+      </c>
+      <c r="D426" t="n">
+        <v>0</v>
+      </c>
+      <c r="E426" t="n">
+        <v>0</v>
+      </c>
+      <c r="F426" t="n">
+        <v>0</v>
+      </c>
+      <c r="G426" t="n">
+        <v>0</v>
+      </c>
+      <c r="H426" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>0</v>
+      </c>
+      <c r="D427" t="n">
+        <v>0</v>
+      </c>
+      <c r="E427" t="n">
+        <v>0</v>
+      </c>
+      <c r="F427" t="n">
+        <v>0</v>
+      </c>
+      <c r="G427" t="n">
+        <v>0</v>
+      </c>
+      <c r="H427" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>582110.3370000001</v>
+      </c>
+      <c r="D428" t="n">
+        <v>0</v>
+      </c>
+      <c r="E428" t="n">
+        <v>0</v>
+      </c>
+      <c r="F428" t="n">
+        <v>0</v>
+      </c>
+      <c r="G428" t="n">
+        <v>0</v>
+      </c>
+      <c r="H428" t="n">
+        <v>582110.3370000001</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>1312691.104</v>
+      </c>
+      <c r="D429" t="n">
+        <v>0</v>
+      </c>
+      <c r="E429" t="n">
+        <v>0</v>
+      </c>
+      <c r="F429" t="n">
+        <v>0</v>
+      </c>
+      <c r="G429" t="n">
+        <v>0</v>
+      </c>
+      <c r="H429" t="n">
+        <v>1312691.104</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>5871594.333</v>
+      </c>
+      <c r="D430" t="n">
+        <v>0</v>
+      </c>
+      <c r="E430" t="n">
+        <v>0</v>
+      </c>
+      <c r="F430" t="n">
+        <v>0</v>
+      </c>
+      <c r="G430" t="n">
+        <v>0</v>
+      </c>
+      <c r="H430" t="n">
+        <v>5871594.333</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>10908505.012</v>
+      </c>
+      <c r="D431" t="n">
+        <v>0</v>
+      </c>
+      <c r="E431" t="n">
+        <v>0</v>
+      </c>
+      <c r="F431" t="n">
+        <v>0</v>
+      </c>
+      <c r="G431" t="n">
+        <v>0</v>
+      </c>
+      <c r="H431" t="n">
+        <v>10908505.012</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>5621226.44</v>
+      </c>
+      <c r="D432" t="n">
+        <v>9656.629999999999</v>
+      </c>
+      <c r="E432" t="n">
+        <v>0</v>
+      </c>
+      <c r="F432" t="n">
+        <v>9656.629999999999</v>
+      </c>
+      <c r="G432" t="n">
+        <v>0</v>
+      </c>
+      <c r="H432" t="n">
+        <v>5630883.07</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>2439218.81</v>
+      </c>
+      <c r="D433" t="n">
+        <v>0</v>
+      </c>
+      <c r="E433" t="n">
+        <v>141469.56</v>
+      </c>
+      <c r="F433" t="n">
+        <v>-141469.56</v>
+      </c>
+      <c r="G433" t="n">
+        <v>0</v>
+      </c>
+      <c r="H433" t="n">
+        <v>2297749.25</v>
       </c>
     </row>
   </sheetData>
@@ -11943,10 +12615,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1638430.048</v>
+        <v>3522292.288</v>
       </c>
       <c r="C2" t="n">
-        <v>24115784.832</v>
+        <v>22231922.592</v>
       </c>
       <c r="D2" t="n">
         <v>25754214.88</v>
@@ -11959,13 +12631,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39640103.813</v>
+        <v>39610438.567</v>
       </c>
       <c r="C3" t="n">
-        <v>13586868.987</v>
+        <v>13283931.103</v>
       </c>
       <c r="D3" t="n">
-        <v>53226972.8</v>
+        <v>52894369.67</v>
       </c>
     </row>
     <row r="4">
@@ -11975,13 +12647,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10610387.084</v>
+        <v>10227036.275</v>
       </c>
       <c r="C4" t="n">
         <v>12001986.855</v>
       </c>
       <c r="D4" t="n">
-        <v>22612373.939</v>
+        <v>22229023.13</v>
       </c>
     </row>
     <row r="5">
@@ -11991,13 +12663,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15579927.194</v>
+        <v>15565008.384</v>
       </c>
       <c r="C5" t="n">
         <v>1637870.342</v>
       </c>
       <c r="D5" t="n">
-        <v>17217797.536</v>
+        <v>17202878.726</v>
       </c>
     </row>
     <row r="6">
@@ -12007,13 +12679,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17764657.013</v>
+        <v>17749396.213</v>
       </c>
       <c r="C6" t="n">
         <v>3387219.03</v>
       </c>
       <c r="D6" t="n">
-        <v>21151876.043</v>
+        <v>21136615.243</v>
       </c>
     </row>
     <row r="7">
@@ -12055,10 +12727,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21568329.286</v>
+        <v>25299374.956</v>
       </c>
       <c r="C9" t="n">
-        <v>8179304.857</v>
+        <v>4448259.187</v>
       </c>
       <c r="D9" t="n">
         <v>29747634.143</v>
@@ -12119,13 +12791,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2439218.81</v>
+        <v>2297749.25</v>
       </c>
       <c r="C13" t="n">
-        <v>5621226.44</v>
+        <v>5630883.07</v>
       </c>
       <c r="D13" t="n">
-        <v>8060445.25</v>
+        <v>7928632.32</v>
       </c>
     </row>
   </sheetData>
@@ -12171,13 +12843,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>265076376.381</v>
+        <v>270106619.066</v>
       </c>
       <c r="C2" t="n">
-        <v>87143495.17299999</v>
+        <v>81235306.009</v>
       </c>
       <c r="D2" t="n">
-        <v>352219871.554</v>
+        <v>351341925.075</v>
       </c>
     </row>
     <row r="3">
@@ -12248,7 +12920,7 @@
         <v>64999.2</v>
       </c>
       <c r="E8" t="n">
-        <v>1638430.048</v>
+        <v>3522292.288</v>
       </c>
     </row>
     <row r="9">
@@ -12269,7 +12941,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>24115784.832</v>
+        <v>22231922.592</v>
       </c>
     </row>
     <row r="10">
@@ -12287,10 +12959,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1808024.843</v>
+        <v>2140627.973</v>
       </c>
       <c r="E10" t="n">
-        <v>39640103.813</v>
+        <v>39610438.567</v>
       </c>
     </row>
     <row r="11">
@@ -12311,7 +12983,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>13586868.987</v>
+        <v>13283931.103</v>
       </c>
     </row>
     <row r="12">
@@ -12326,13 +12998,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24897.79</v>
+        <v>28892.51</v>
       </c>
       <c r="D12" t="n">
-        <v>1410221.167</v>
+        <v>1797566.696</v>
       </c>
       <c r="E12" t="n">
-        <v>10610387.084</v>
+        <v>10227036.275</v>
       </c>
     </row>
     <row r="13">
@@ -12371,10 +13043,10 @@
         <v>918.2</v>
       </c>
       <c r="D14" t="n">
-        <v>918.2</v>
+        <v>15837.01</v>
       </c>
       <c r="E14" t="n">
-        <v>15579927.194</v>
+        <v>15565008.384</v>
       </c>
     </row>
     <row r="15">
@@ -12413,10 +13085,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>15260.8</v>
       </c>
       <c r="E16" t="n">
-        <v>17764657.013</v>
+        <v>17749396.213</v>
       </c>
     </row>
     <row r="17">
@@ -12542,7 +13214,7 @@
         <v>600017.8199999999</v>
       </c>
       <c r="E22" t="n">
-        <v>21568329.286</v>
+        <v>25299374.956</v>
       </c>
     </row>
     <row r="23">
@@ -12563,7 +13235,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>8179304.857</v>
+        <v>4448259.187</v>
       </c>
     </row>
     <row r="24">
@@ -12707,10 +13379,10 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>141469.56</v>
       </c>
       <c r="E30" t="n">
-        <v>2439218.81</v>
+        <v>2297749.25</v>
       </c>
     </row>
     <row r="31">
@@ -12725,13 +13397,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>9656.629999999999</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>5621226.44</v>
+        <v>5630883.07</v>
       </c>
     </row>
     <row r="32">

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12569,6 +12569,678 @@
         <v>0</v>
       </c>
       <c r="H433" t="n">
+        <v>2297749.25</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>22231922.592</v>
+      </c>
+      <c r="D434" t="n">
+        <v>0</v>
+      </c>
+      <c r="E434" t="n">
+        <v>0</v>
+      </c>
+      <c r="F434" t="n">
+        <v>0</v>
+      </c>
+      <c r="G434" t="n">
+        <v>0</v>
+      </c>
+      <c r="H434" t="n">
+        <v>22231922.592</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>3522292.288</v>
+      </c>
+      <c r="D435" t="n">
+        <v>0</v>
+      </c>
+      <c r="E435" t="n">
+        <v>0</v>
+      </c>
+      <c r="F435" t="n">
+        <v>0</v>
+      </c>
+      <c r="G435" t="n">
+        <v>0</v>
+      </c>
+      <c r="H435" t="n">
+        <v>3522292.288</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>13283931.103</v>
+      </c>
+      <c r="D436" t="n">
+        <v>0</v>
+      </c>
+      <c r="E436" t="n">
+        <v>0</v>
+      </c>
+      <c r="F436" t="n">
+        <v>0</v>
+      </c>
+      <c r="G436" t="n">
+        <v>0</v>
+      </c>
+      <c r="H436" t="n">
+        <v>13283931.103</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>39610438.567</v>
+      </c>
+      <c r="D437" t="n">
+        <v>0</v>
+      </c>
+      <c r="E437" t="n">
+        <v>305127.77</v>
+      </c>
+      <c r="F437" t="n">
+        <v>-305127.77</v>
+      </c>
+      <c r="G437" t="n">
+        <v>0</v>
+      </c>
+      <c r="H437" t="n">
+        <v>39305310.797</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>12001986.855</v>
+      </c>
+      <c r="D438" t="n">
+        <v>0</v>
+      </c>
+      <c r="E438" t="n">
+        <v>0</v>
+      </c>
+      <c r="F438" t="n">
+        <v>0</v>
+      </c>
+      <c r="G438" t="n">
+        <v>0</v>
+      </c>
+      <c r="H438" t="n">
+        <v>12001986.855</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>10227036.275</v>
+      </c>
+      <c r="D439" t="n">
+        <v>0</v>
+      </c>
+      <c r="E439" t="n">
+        <v>611508.09</v>
+      </c>
+      <c r="F439" t="n">
+        <v>-611508.09</v>
+      </c>
+      <c r="G439" t="n">
+        <v>0</v>
+      </c>
+      <c r="H439" t="n">
+        <v>9615528.185000001</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D440" t="n">
+        <v>0</v>
+      </c>
+      <c r="E440" t="n">
+        <v>0</v>
+      </c>
+      <c r="F440" t="n">
+        <v>0</v>
+      </c>
+      <c r="G440" t="n">
+        <v>0</v>
+      </c>
+      <c r="H440" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>15565008.384</v>
+      </c>
+      <c r="D441" t="n">
+        <v>0</v>
+      </c>
+      <c r="E441" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F441" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G441" t="n">
+        <v>0</v>
+      </c>
+      <c r="H441" t="n">
+        <v>15564008.384</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>3387219.03</v>
+      </c>
+      <c r="D442" t="n">
+        <v>0</v>
+      </c>
+      <c r="E442" t="n">
+        <v>0</v>
+      </c>
+      <c r="F442" t="n">
+        <v>0</v>
+      </c>
+      <c r="G442" t="n">
+        <v>0</v>
+      </c>
+      <c r="H442" t="n">
+        <v>3387219.03</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>17749396.213</v>
+      </c>
+      <c r="D443" t="n">
+        <v>0</v>
+      </c>
+      <c r="E443" t="n">
+        <v>0</v>
+      </c>
+      <c r="F443" t="n">
+        <v>0</v>
+      </c>
+      <c r="G443" t="n">
+        <v>0</v>
+      </c>
+      <c r="H443" t="n">
+        <v>17749396.213</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>178515.19</v>
+      </c>
+      <c r="D444" t="n">
+        <v>0</v>
+      </c>
+      <c r="E444" t="n">
+        <v>0</v>
+      </c>
+      <c r="F444" t="n">
+        <v>0</v>
+      </c>
+      <c r="G444" t="n">
+        <v>0</v>
+      </c>
+      <c r="H444" t="n">
+        <v>178515.19</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>2800401.334</v>
+      </c>
+      <c r="D445" t="n">
+        <v>0</v>
+      </c>
+      <c r="E445" t="n">
+        <v>0</v>
+      </c>
+      <c r="F445" t="n">
+        <v>0</v>
+      </c>
+      <c r="G445" t="n">
+        <v>0</v>
+      </c>
+      <c r="H445" t="n">
+        <v>2800401.334</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D446" t="n">
+        <v>0</v>
+      </c>
+      <c r="E446" t="n">
+        <v>0</v>
+      </c>
+      <c r="F446" t="n">
+        <v>0</v>
+      </c>
+      <c r="G446" t="n">
+        <v>0</v>
+      </c>
+      <c r="H446" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>140813725.683</v>
+      </c>
+      <c r="D447" t="n">
+        <v>0</v>
+      </c>
+      <c r="E447" t="n">
+        <v>0</v>
+      </c>
+      <c r="F447" t="n">
+        <v>0</v>
+      </c>
+      <c r="G447" t="n">
+        <v>0</v>
+      </c>
+      <c r="H447" t="n">
+        <v>140813725.683</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>4448259.187</v>
+      </c>
+      <c r="D448" t="n">
+        <v>0</v>
+      </c>
+      <c r="E448" t="n">
+        <v>0</v>
+      </c>
+      <c r="F448" t="n">
+        <v>0</v>
+      </c>
+      <c r="G448" t="n">
+        <v>498427.31</v>
+      </c>
+      <c r="H448" t="n">
+        <v>4946686.497</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>25299374.956</v>
+      </c>
+      <c r="D449" t="n">
+        <v>0</v>
+      </c>
+      <c r="E449" t="n">
+        <v>0</v>
+      </c>
+      <c r="F449" t="n">
+        <v>0</v>
+      </c>
+      <c r="G449" t="n">
+        <v>-498427.31</v>
+      </c>
+      <c r="H449" t="n">
+        <v>24800947.646</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>0</v>
+      </c>
+      <c r="D450" t="n">
+        <v>0</v>
+      </c>
+      <c r="E450" t="n">
+        <v>0</v>
+      </c>
+      <c r="F450" t="n">
+        <v>0</v>
+      </c>
+      <c r="G450" t="n">
+        <v>0</v>
+      </c>
+      <c r="H450" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>0</v>
+      </c>
+      <c r="D451" t="n">
+        <v>0</v>
+      </c>
+      <c r="E451" t="n">
+        <v>0</v>
+      </c>
+      <c r="F451" t="n">
+        <v>0</v>
+      </c>
+      <c r="G451" t="n">
+        <v>0</v>
+      </c>
+      <c r="H451" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>582110.3370000001</v>
+      </c>
+      <c r="D452" t="n">
+        <v>0</v>
+      </c>
+      <c r="E452" t="n">
+        <v>0</v>
+      </c>
+      <c r="F452" t="n">
+        <v>0</v>
+      </c>
+      <c r="G452" t="n">
+        <v>0</v>
+      </c>
+      <c r="H452" t="n">
+        <v>582110.3370000001</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>1312691.104</v>
+      </c>
+      <c r="D453" t="n">
+        <v>0</v>
+      </c>
+      <c r="E453" t="n">
+        <v>0</v>
+      </c>
+      <c r="F453" t="n">
+        <v>0</v>
+      </c>
+      <c r="G453" t="n">
+        <v>0</v>
+      </c>
+      <c r="H453" t="n">
+        <v>1312691.104</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>5871594.333</v>
+      </c>
+      <c r="D454" t="n">
+        <v>0</v>
+      </c>
+      <c r="E454" t="n">
+        <v>0</v>
+      </c>
+      <c r="F454" t="n">
+        <v>0</v>
+      </c>
+      <c r="G454" t="n">
+        <v>0</v>
+      </c>
+      <c r="H454" t="n">
+        <v>5871594.333</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>10908505.012</v>
+      </c>
+      <c r="D455" t="n">
+        <v>0</v>
+      </c>
+      <c r="E455" t="n">
+        <v>1278394.461</v>
+      </c>
+      <c r="F455" t="n">
+        <v>-1278394.461</v>
+      </c>
+      <c r="G455" t="n">
+        <v>0</v>
+      </c>
+      <c r="H455" t="n">
+        <v>9630110.551000001</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>5630883.07</v>
+      </c>
+      <c r="D456" t="n">
+        <v>0</v>
+      </c>
+      <c r="E456" t="n">
+        <v>0</v>
+      </c>
+      <c r="F456" t="n">
+        <v>0</v>
+      </c>
+      <c r="G456" t="n">
+        <v>0</v>
+      </c>
+      <c r="H456" t="n">
+        <v>5630883.07</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>2297749.25</v>
+      </c>
+      <c r="D457" t="n">
+        <v>0</v>
+      </c>
+      <c r="E457" t="n">
+        <v>0</v>
+      </c>
+      <c r="F457" t="n">
+        <v>0</v>
+      </c>
+      <c r="G457" t="n">
+        <v>0</v>
+      </c>
+      <c r="H457" t="n">
         <v>2297749.25</v>
       </c>
     </row>
@@ -12631,13 +13303,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39610438.567</v>
+        <v>39305310.797</v>
       </c>
       <c r="C3" t="n">
         <v>13283931.103</v>
       </c>
       <c r="D3" t="n">
-        <v>52894369.67</v>
+        <v>52589241.9</v>
       </c>
     </row>
     <row r="4">
@@ -12647,13 +13319,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10227036.275</v>
+        <v>9615528.185000001</v>
       </c>
       <c r="C4" t="n">
         <v>12001986.855</v>
       </c>
       <c r="D4" t="n">
-        <v>22229023.13</v>
+        <v>21617515.04</v>
       </c>
     </row>
     <row r="5">
@@ -12663,13 +13335,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15565008.384</v>
+        <v>15564008.384</v>
       </c>
       <c r="C5" t="n">
         <v>1637870.342</v>
       </c>
       <c r="D5" t="n">
-        <v>17202878.726</v>
+        <v>17201878.726</v>
       </c>
     </row>
     <row r="6">
@@ -12727,10 +13399,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25299374.956</v>
+        <v>24800947.646</v>
       </c>
       <c r="C9" t="n">
-        <v>4448259.187</v>
+        <v>4946686.497</v>
       </c>
       <c r="D9" t="n">
         <v>29747634.143</v>
@@ -12775,13 +13447,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10908505.012</v>
+        <v>9630110.551000001</v>
       </c>
       <c r="C12" t="n">
         <v>5871594.333</v>
       </c>
       <c r="D12" t="n">
-        <v>16780099.345</v>
+        <v>15501704.884</v>
       </c>
     </row>
     <row r="13">
@@ -12843,13 +13515,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>270106619.066</v>
+        <v>267412161.435</v>
       </c>
       <c r="C2" t="n">
-        <v>81235306.009</v>
+        <v>81733733.31900001</v>
       </c>
       <c r="D2" t="n">
-        <v>351341925.075</v>
+        <v>349145894.754</v>
       </c>
     </row>
     <row r="3">
@@ -12959,10 +13631,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2140627.973</v>
+        <v>2445755.743</v>
       </c>
       <c r="E10" t="n">
-        <v>39610438.567</v>
+        <v>39305310.797</v>
       </c>
     </row>
     <row r="11">
@@ -13001,10 +13673,10 @@
         <v>28892.51</v>
       </c>
       <c r="D12" t="n">
-        <v>1797566.696</v>
+        <v>2409074.786</v>
       </c>
       <c r="E12" t="n">
-        <v>10227036.275</v>
+        <v>9615528.185000001</v>
       </c>
     </row>
     <row r="13">
@@ -13043,10 +13715,10 @@
         <v>918.2</v>
       </c>
       <c r="D14" t="n">
-        <v>15837.01</v>
+        <v>16837.01</v>
       </c>
       <c r="E14" t="n">
-        <v>15565008.384</v>
+        <v>15564008.384</v>
       </c>
     </row>
     <row r="15">
@@ -13214,7 +13886,7 @@
         <v>600017.8199999999</v>
       </c>
       <c r="E22" t="n">
-        <v>25299374.956</v>
+        <v>24800947.646</v>
       </c>
     </row>
     <row r="23">
@@ -13235,7 +13907,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4448259.187</v>
+        <v>4946686.497</v>
       </c>
     </row>
     <row r="24">
@@ -13337,10 +14009,10 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>883624.584</v>
+        <v>2162019.045</v>
       </c>
       <c r="E28" t="n">
-        <v>10908505.012</v>
+        <v>9630110.551000001</v>
       </c>
     </row>
     <row r="29">

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H457"/>
+  <dimension ref="A1:H481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13242,6 +13242,678 @@
       </c>
       <c r="H457" t="n">
         <v>2297749.25</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>22231922.592</v>
+      </c>
+      <c r="D458" t="n">
+        <v>0</v>
+      </c>
+      <c r="E458" t="n">
+        <v>0</v>
+      </c>
+      <c r="F458" t="n">
+        <v>0</v>
+      </c>
+      <c r="G458" t="n">
+        <v>0</v>
+      </c>
+      <c r="H458" t="n">
+        <v>22231922.592</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>3522292.288</v>
+      </c>
+      <c r="D459" t="n">
+        <v>0</v>
+      </c>
+      <c r="E459" t="n">
+        <v>1002692.77</v>
+      </c>
+      <c r="F459" t="n">
+        <v>-1002692.77</v>
+      </c>
+      <c r="G459" t="n">
+        <v>0</v>
+      </c>
+      <c r="H459" t="n">
+        <v>2519599.518</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>13283931.103</v>
+      </c>
+      <c r="D460" t="n">
+        <v>0</v>
+      </c>
+      <c r="E460" t="n">
+        <v>0</v>
+      </c>
+      <c r="F460" t="n">
+        <v>0</v>
+      </c>
+      <c r="G460" t="n">
+        <v>-755150.3199999999</v>
+      </c>
+      <c r="H460" t="n">
+        <v>12528780.783</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>39305310.797</v>
+      </c>
+      <c r="D461" t="n">
+        <v>0</v>
+      </c>
+      <c r="E461" t="n">
+        <v>0</v>
+      </c>
+      <c r="F461" t="n">
+        <v>0</v>
+      </c>
+      <c r="G461" t="n">
+        <v>755150.3199999999</v>
+      </c>
+      <c r="H461" t="n">
+        <v>40060461.117</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>12001986.855</v>
+      </c>
+      <c r="D462" t="n">
+        <v>0</v>
+      </c>
+      <c r="E462" t="n">
+        <v>0</v>
+      </c>
+      <c r="F462" t="n">
+        <v>0</v>
+      </c>
+      <c r="G462" t="n">
+        <v>0</v>
+      </c>
+      <c r="H462" t="n">
+        <v>12001986.855</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>9615528.185000001</v>
+      </c>
+      <c r="D463" t="n">
+        <v>0</v>
+      </c>
+      <c r="E463" t="n">
+        <v>532445.9</v>
+      </c>
+      <c r="F463" t="n">
+        <v>-532445.9</v>
+      </c>
+      <c r="G463" t="n">
+        <v>0</v>
+      </c>
+      <c r="H463" t="n">
+        <v>9083082.285</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D464" t="n">
+        <v>0</v>
+      </c>
+      <c r="E464" t="n">
+        <v>0</v>
+      </c>
+      <c r="F464" t="n">
+        <v>0</v>
+      </c>
+      <c r="G464" t="n">
+        <v>0</v>
+      </c>
+      <c r="H464" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>15564008.384</v>
+      </c>
+      <c r="D465" t="n">
+        <v>918.2</v>
+      </c>
+      <c r="E465" t="n">
+        <v>0</v>
+      </c>
+      <c r="F465" t="n">
+        <v>918.2</v>
+      </c>
+      <c r="G465" t="n">
+        <v>0</v>
+      </c>
+      <c r="H465" t="n">
+        <v>15564926.584</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>3387219.03</v>
+      </c>
+      <c r="D466" t="n">
+        <v>0</v>
+      </c>
+      <c r="E466" t="n">
+        <v>0</v>
+      </c>
+      <c r="F466" t="n">
+        <v>0</v>
+      </c>
+      <c r="G466" t="n">
+        <v>0</v>
+      </c>
+      <c r="H466" t="n">
+        <v>3387219.03</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>17749396.213</v>
+      </c>
+      <c r="D467" t="n">
+        <v>0</v>
+      </c>
+      <c r="E467" t="n">
+        <v>0</v>
+      </c>
+      <c r="F467" t="n">
+        <v>0</v>
+      </c>
+      <c r="G467" t="n">
+        <v>0</v>
+      </c>
+      <c r="H467" t="n">
+        <v>17749396.213</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>178515.19</v>
+      </c>
+      <c r="D468" t="n">
+        <v>0</v>
+      </c>
+      <c r="E468" t="n">
+        <v>0</v>
+      </c>
+      <c r="F468" t="n">
+        <v>0</v>
+      </c>
+      <c r="G468" t="n">
+        <v>0</v>
+      </c>
+      <c r="H468" t="n">
+        <v>178515.19</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>2800401.334</v>
+      </c>
+      <c r="D469" t="n">
+        <v>0</v>
+      </c>
+      <c r="E469" t="n">
+        <v>0</v>
+      </c>
+      <c r="F469" t="n">
+        <v>0</v>
+      </c>
+      <c r="G469" t="n">
+        <v>0</v>
+      </c>
+      <c r="H469" t="n">
+        <v>2800401.334</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D470" t="n">
+        <v>0</v>
+      </c>
+      <c r="E470" t="n">
+        <v>0</v>
+      </c>
+      <c r="F470" t="n">
+        <v>0</v>
+      </c>
+      <c r="G470" t="n">
+        <v>0</v>
+      </c>
+      <c r="H470" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>140813725.683</v>
+      </c>
+      <c r="D471" t="n">
+        <v>0</v>
+      </c>
+      <c r="E471" t="n">
+        <v>19329.8</v>
+      </c>
+      <c r="F471" t="n">
+        <v>-19329.8</v>
+      </c>
+      <c r="G471" t="n">
+        <v>0</v>
+      </c>
+      <c r="H471" t="n">
+        <v>140794395.883</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>4946686.497</v>
+      </c>
+      <c r="D472" t="n">
+        <v>0</v>
+      </c>
+      <c r="E472" t="n">
+        <v>0</v>
+      </c>
+      <c r="F472" t="n">
+        <v>0</v>
+      </c>
+      <c r="G472" t="n">
+        <v>0</v>
+      </c>
+      <c r="H472" t="n">
+        <v>4946686.497</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>24800947.646</v>
+      </c>
+      <c r="D473" t="n">
+        <v>0</v>
+      </c>
+      <c r="E473" t="n">
+        <v>0</v>
+      </c>
+      <c r="F473" t="n">
+        <v>0</v>
+      </c>
+      <c r="G473" t="n">
+        <v>0</v>
+      </c>
+      <c r="H473" t="n">
+        <v>24800947.646</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>0</v>
+      </c>
+      <c r="D474" t="n">
+        <v>0</v>
+      </c>
+      <c r="E474" t="n">
+        <v>0</v>
+      </c>
+      <c r="F474" t="n">
+        <v>0</v>
+      </c>
+      <c r="G474" t="n">
+        <v>0</v>
+      </c>
+      <c r="H474" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>0</v>
+      </c>
+      <c r="D475" t="n">
+        <v>0</v>
+      </c>
+      <c r="E475" t="n">
+        <v>0</v>
+      </c>
+      <c r="F475" t="n">
+        <v>0</v>
+      </c>
+      <c r="G475" t="n">
+        <v>0</v>
+      </c>
+      <c r="H475" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>582110.3370000001</v>
+      </c>
+      <c r="D476" t="n">
+        <v>0</v>
+      </c>
+      <c r="E476" t="n">
+        <v>0</v>
+      </c>
+      <c r="F476" t="n">
+        <v>0</v>
+      </c>
+      <c r="G476" t="n">
+        <v>0</v>
+      </c>
+      <c r="H476" t="n">
+        <v>582110.3370000001</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>1312691.104</v>
+      </c>
+      <c r="D477" t="n">
+        <v>0</v>
+      </c>
+      <c r="E477" t="n">
+        <v>0</v>
+      </c>
+      <c r="F477" t="n">
+        <v>0</v>
+      </c>
+      <c r="G477" t="n">
+        <v>0</v>
+      </c>
+      <c r="H477" t="n">
+        <v>1312691.104</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>5871594.333</v>
+      </c>
+      <c r="D478" t="n">
+        <v>0</v>
+      </c>
+      <c r="E478" t="n">
+        <v>0</v>
+      </c>
+      <c r="F478" t="n">
+        <v>0</v>
+      </c>
+      <c r="G478" t="n">
+        <v>-458643.782</v>
+      </c>
+      <c r="H478" t="n">
+        <v>5412950.551</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>9630110.551000001</v>
+      </c>
+      <c r="D479" t="n">
+        <v>0</v>
+      </c>
+      <c r="E479" t="n">
+        <v>1284641.702</v>
+      </c>
+      <c r="F479" t="n">
+        <v>-1284641.702</v>
+      </c>
+      <c r="G479" t="n">
+        <v>458643.782</v>
+      </c>
+      <c r="H479" t="n">
+        <v>8804112.630999999</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>5630883.07</v>
+      </c>
+      <c r="D480" t="n">
+        <v>0</v>
+      </c>
+      <c r="E480" t="n">
+        <v>0</v>
+      </c>
+      <c r="F480" t="n">
+        <v>0</v>
+      </c>
+      <c r="G480" t="n">
+        <v>-531345.0699999999</v>
+      </c>
+      <c r="H480" t="n">
+        <v>5099538</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>2297749.25</v>
+      </c>
+      <c r="D481" t="n">
+        <v>0</v>
+      </c>
+      <c r="E481" t="n">
+        <v>19731.12</v>
+      </c>
+      <c r="F481" t="n">
+        <v>-19731.12</v>
+      </c>
+      <c r="G481" t="n">
+        <v>531345.0699999999</v>
+      </c>
+      <c r="H481" t="n">
+        <v>2809363.2</v>
       </c>
     </row>
   </sheetData>
@@ -13287,13 +13959,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3522292.288</v>
+        <v>2519599.518</v>
       </c>
       <c r="C2" t="n">
         <v>22231922.592</v>
       </c>
       <c r="D2" t="n">
-        <v>25754214.88</v>
+        <v>24751522.11</v>
       </c>
     </row>
     <row r="3">
@@ -13303,10 +13975,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39305310.797</v>
+        <v>40060461.117</v>
       </c>
       <c r="C3" t="n">
-        <v>13283931.103</v>
+        <v>12528780.783</v>
       </c>
       <c r="D3" t="n">
         <v>52589241.9</v>
@@ -13319,13 +13991,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9615528.185000001</v>
+        <v>9083082.285</v>
       </c>
       <c r="C4" t="n">
         <v>12001986.855</v>
       </c>
       <c r="D4" t="n">
-        <v>21617515.04</v>
+        <v>21085069.14</v>
       </c>
     </row>
     <row r="5">
@@ -13335,13 +14007,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15564008.384</v>
+        <v>15564926.584</v>
       </c>
       <c r="C5" t="n">
         <v>1637870.342</v>
       </c>
       <c r="D5" t="n">
-        <v>17201878.726</v>
+        <v>17202796.926</v>
       </c>
     </row>
     <row r="6">
@@ -13383,13 +14055,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>140813725.683</v>
+        <v>140794395.883</v>
       </c>
       <c r="C8" t="n">
         <v>11981013.97</v>
       </c>
       <c r="D8" t="n">
-        <v>152794739.653</v>
+        <v>152775409.853</v>
       </c>
     </row>
     <row r="9">
@@ -13447,13 +14119,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9630110.551000001</v>
+        <v>8804112.630999999</v>
       </c>
       <c r="C12" t="n">
-        <v>5871594.333</v>
+        <v>5412950.551</v>
       </c>
       <c r="D12" t="n">
-        <v>15501704.884</v>
+        <v>14217063.182</v>
       </c>
     </row>
     <row r="13">
@@ -13463,13 +14135,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2297749.25</v>
+        <v>2809363.2</v>
       </c>
       <c r="C13" t="n">
-        <v>5630883.07</v>
+        <v>5099538</v>
       </c>
       <c r="D13" t="n">
-        <v>7928632.32</v>
+        <v>7908901.2</v>
       </c>
     </row>
   </sheetData>
@@ -13515,13 +14187,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>267412161.435</v>
+        <v>266299377.515</v>
       </c>
       <c r="C2" t="n">
-        <v>81733733.31900001</v>
+        <v>79988594.147</v>
       </c>
       <c r="D2" t="n">
-        <v>349145894.754</v>
+        <v>346287971.662</v>
       </c>
     </row>
     <row r="3">
@@ -13589,10 +14261,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>64999.2</v>
+        <v>1067691.97</v>
       </c>
       <c r="E8" t="n">
-        <v>3522292.288</v>
+        <v>2519599.518</v>
       </c>
     </row>
     <row r="9">
@@ -13634,7 +14306,7 @@
         <v>2445755.743</v>
       </c>
       <c r="E10" t="n">
-        <v>39305310.797</v>
+        <v>40060461.117</v>
       </c>
     </row>
     <row r="11">
@@ -13655,7 +14327,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>13283931.103</v>
+        <v>12528780.783</v>
       </c>
     </row>
     <row r="12">
@@ -13673,10 +14345,10 @@
         <v>28892.51</v>
       </c>
       <c r="D12" t="n">
-        <v>2409074.786</v>
+        <v>2941520.686</v>
       </c>
       <c r="E12" t="n">
-        <v>9615528.185000001</v>
+        <v>9083082.285</v>
       </c>
     </row>
     <row r="13">
@@ -13712,13 +14384,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>918.2</v>
+        <v>1836.4</v>
       </c>
       <c r="D14" t="n">
         <v>16837.01</v>
       </c>
       <c r="E14" t="n">
-        <v>15564008.384</v>
+        <v>15564926.584</v>
       </c>
     </row>
     <row r="15">
@@ -13841,10 +14513,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>19329.8</v>
       </c>
       <c r="E20" t="n">
-        <v>140813725.683</v>
+        <v>140794395.883</v>
       </c>
     </row>
     <row r="21">
@@ -14009,10 +14681,10 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>2162019.045</v>
+        <v>3446660.747</v>
       </c>
       <c r="E28" t="n">
-        <v>9630110.551000001</v>
+        <v>8804112.630999999</v>
       </c>
     </row>
     <row r="29">
@@ -14033,7 +14705,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>5871594.333</v>
+        <v>5412950.551</v>
       </c>
     </row>
     <row r="30">
@@ -14051,10 +14723,10 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>141469.56</v>
+        <v>161200.68</v>
       </c>
       <c r="E30" t="n">
-        <v>2297749.25</v>
+        <v>2809363.2</v>
       </c>
     </row>
     <row r="31">
@@ -14075,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>5630883.07</v>
+        <v>5099538</v>
       </c>
     </row>
     <row r="32">

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H481"/>
+  <dimension ref="A1:H505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13914,6 +13914,678 @@
       </c>
       <c r="H481" t="n">
         <v>2809363.2</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>22231922.592</v>
+      </c>
+      <c r="D482" t="n">
+        <v>0</v>
+      </c>
+      <c r="E482" t="n">
+        <v>0</v>
+      </c>
+      <c r="F482" t="n">
+        <v>0</v>
+      </c>
+      <c r="G482" t="n">
+        <v>0</v>
+      </c>
+      <c r="H482" t="n">
+        <v>22231922.592</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>2519599.518</v>
+      </c>
+      <c r="D483" t="n">
+        <v>0</v>
+      </c>
+      <c r="E483" t="n">
+        <v>0</v>
+      </c>
+      <c r="F483" t="n">
+        <v>0</v>
+      </c>
+      <c r="G483" t="n">
+        <v>0</v>
+      </c>
+      <c r="H483" t="n">
+        <v>2519599.518</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>12528780.783</v>
+      </c>
+      <c r="D484" t="n">
+        <v>0</v>
+      </c>
+      <c r="E484" t="n">
+        <v>0</v>
+      </c>
+      <c r="F484" t="n">
+        <v>0</v>
+      </c>
+      <c r="G484" t="n">
+        <v>-740429.08</v>
+      </c>
+      <c r="H484" t="n">
+        <v>11788351.703</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>40060461.117</v>
+      </c>
+      <c r="D485" t="n">
+        <v>0</v>
+      </c>
+      <c r="E485" t="n">
+        <v>0</v>
+      </c>
+      <c r="F485" t="n">
+        <v>0</v>
+      </c>
+      <c r="G485" t="n">
+        <v>740429.08</v>
+      </c>
+      <c r="H485" t="n">
+        <v>40800890.197</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>12001986.855</v>
+      </c>
+      <c r="D486" t="n">
+        <v>0</v>
+      </c>
+      <c r="E486" t="n">
+        <v>0</v>
+      </c>
+      <c r="F486" t="n">
+        <v>0</v>
+      </c>
+      <c r="G486" t="n">
+        <v>-216028.372</v>
+      </c>
+      <c r="H486" t="n">
+        <v>11785958.484</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>9083082.285</v>
+      </c>
+      <c r="D487" t="n">
+        <v>0</v>
+      </c>
+      <c r="E487" t="n">
+        <v>0</v>
+      </c>
+      <c r="F487" t="n">
+        <v>0</v>
+      </c>
+      <c r="G487" t="n">
+        <v>216028.372</v>
+      </c>
+      <c r="H487" t="n">
+        <v>9299110.657</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D488" t="n">
+        <v>0</v>
+      </c>
+      <c r="E488" t="n">
+        <v>0</v>
+      </c>
+      <c r="F488" t="n">
+        <v>0</v>
+      </c>
+      <c r="G488" t="n">
+        <v>0</v>
+      </c>
+      <c r="H488" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>15564926.584</v>
+      </c>
+      <c r="D489" t="n">
+        <v>0</v>
+      </c>
+      <c r="E489" t="n">
+        <v>35481.714</v>
+      </c>
+      <c r="F489" t="n">
+        <v>-35481.714</v>
+      </c>
+      <c r="G489" t="n">
+        <v>0</v>
+      </c>
+      <c r="H489" t="n">
+        <v>15529444.87</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>3387219.03</v>
+      </c>
+      <c r="D490" t="n">
+        <v>0</v>
+      </c>
+      <c r="E490" t="n">
+        <v>0</v>
+      </c>
+      <c r="F490" t="n">
+        <v>0</v>
+      </c>
+      <c r="G490" t="n">
+        <v>-10040.38</v>
+      </c>
+      <c r="H490" t="n">
+        <v>3377178.65</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>17749396.213</v>
+      </c>
+      <c r="D491" t="n">
+        <v>0</v>
+      </c>
+      <c r="E491" t="n">
+        <v>0</v>
+      </c>
+      <c r="F491" t="n">
+        <v>0</v>
+      </c>
+      <c r="G491" t="n">
+        <v>10040.38</v>
+      </c>
+      <c r="H491" t="n">
+        <v>17759436.593</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>178515.19</v>
+      </c>
+      <c r="D492" t="n">
+        <v>0</v>
+      </c>
+      <c r="E492" t="n">
+        <v>0</v>
+      </c>
+      <c r="F492" t="n">
+        <v>0</v>
+      </c>
+      <c r="G492" t="n">
+        <v>0</v>
+      </c>
+      <c r="H492" t="n">
+        <v>178515.19</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>2800401.334</v>
+      </c>
+      <c r="D493" t="n">
+        <v>0</v>
+      </c>
+      <c r="E493" t="n">
+        <v>0</v>
+      </c>
+      <c r="F493" t="n">
+        <v>0</v>
+      </c>
+      <c r="G493" t="n">
+        <v>0</v>
+      </c>
+      <c r="H493" t="n">
+        <v>2800401.334</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D494" t="n">
+        <v>0</v>
+      </c>
+      <c r="E494" t="n">
+        <v>0</v>
+      </c>
+      <c r="F494" t="n">
+        <v>0</v>
+      </c>
+      <c r="G494" t="n">
+        <v>0</v>
+      </c>
+      <c r="H494" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>140794395.883</v>
+      </c>
+      <c r="D495" t="n">
+        <v>0</v>
+      </c>
+      <c r="E495" t="n">
+        <v>594709.9</v>
+      </c>
+      <c r="F495" t="n">
+        <v>-594709.9</v>
+      </c>
+      <c r="G495" t="n">
+        <v>0</v>
+      </c>
+      <c r="H495" t="n">
+        <v>140199685.983</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>4946686.497</v>
+      </c>
+      <c r="D496" t="n">
+        <v>0</v>
+      </c>
+      <c r="E496" t="n">
+        <v>0</v>
+      </c>
+      <c r="F496" t="n">
+        <v>0</v>
+      </c>
+      <c r="G496" t="n">
+        <v>-553120.1</v>
+      </c>
+      <c r="H496" t="n">
+        <v>4393566.397</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>24800947.646</v>
+      </c>
+      <c r="D497" t="n">
+        <v>0</v>
+      </c>
+      <c r="E497" t="n">
+        <v>0</v>
+      </c>
+      <c r="F497" t="n">
+        <v>0</v>
+      </c>
+      <c r="G497" t="n">
+        <v>553120.1</v>
+      </c>
+      <c r="H497" t="n">
+        <v>25354067.746</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>0</v>
+      </c>
+      <c r="D498" t="n">
+        <v>0</v>
+      </c>
+      <c r="E498" t="n">
+        <v>0</v>
+      </c>
+      <c r="F498" t="n">
+        <v>0</v>
+      </c>
+      <c r="G498" t="n">
+        <v>0</v>
+      </c>
+      <c r="H498" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>0</v>
+      </c>
+      <c r="D499" t="n">
+        <v>0</v>
+      </c>
+      <c r="E499" t="n">
+        <v>0</v>
+      </c>
+      <c r="F499" t="n">
+        <v>0</v>
+      </c>
+      <c r="G499" t="n">
+        <v>0</v>
+      </c>
+      <c r="H499" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>582110.3370000001</v>
+      </c>
+      <c r="D500" t="n">
+        <v>0</v>
+      </c>
+      <c r="E500" t="n">
+        <v>0</v>
+      </c>
+      <c r="F500" t="n">
+        <v>0</v>
+      </c>
+      <c r="G500" t="n">
+        <v>0</v>
+      </c>
+      <c r="H500" t="n">
+        <v>582110.3370000001</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>1312691.104</v>
+      </c>
+      <c r="D501" t="n">
+        <v>0</v>
+      </c>
+      <c r="E501" t="n">
+        <v>367523.727</v>
+      </c>
+      <c r="F501" t="n">
+        <v>-367523.727</v>
+      </c>
+      <c r="G501" t="n">
+        <v>0</v>
+      </c>
+      <c r="H501" t="n">
+        <v>945167.377</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>5412950.551</v>
+      </c>
+      <c r="D502" t="n">
+        <v>0</v>
+      </c>
+      <c r="E502" t="n">
+        <v>0</v>
+      </c>
+      <c r="F502" t="n">
+        <v>0</v>
+      </c>
+      <c r="G502" t="n">
+        <v>0</v>
+      </c>
+      <c r="H502" t="n">
+        <v>5412950.551</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>8804112.630999999</v>
+      </c>
+      <c r="D503" t="n">
+        <v>0</v>
+      </c>
+      <c r="E503" t="n">
+        <v>0</v>
+      </c>
+      <c r="F503" t="n">
+        <v>0</v>
+      </c>
+      <c r="G503" t="n">
+        <v>0</v>
+      </c>
+      <c r="H503" t="n">
+        <v>8804112.630999999</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>5099538</v>
+      </c>
+      <c r="D504" t="n">
+        <v>20186.22</v>
+      </c>
+      <c r="E504" t="n">
+        <v>0</v>
+      </c>
+      <c r="F504" t="n">
+        <v>20186.22</v>
+      </c>
+      <c r="G504" t="n">
+        <v>-5194.73</v>
+      </c>
+      <c r="H504" t="n">
+        <v>5114529.49</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>2809363.2</v>
+      </c>
+      <c r="D505" t="n">
+        <v>0</v>
+      </c>
+      <c r="E505" t="n">
+        <v>0</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0</v>
+      </c>
+      <c r="G505" t="n">
+        <v>5194.73</v>
+      </c>
+      <c r="H505" t="n">
+        <v>2814557.93</v>
       </c>
     </row>
   </sheetData>
@@ -13975,10 +14647,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40060461.117</v>
+        <v>40800890.197</v>
       </c>
       <c r="C3" t="n">
-        <v>12528780.783</v>
+        <v>11788351.703</v>
       </c>
       <c r="D3" t="n">
         <v>52589241.9</v>
@@ -13991,13 +14663,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9083082.285</v>
+        <v>9299110.657</v>
       </c>
       <c r="C4" t="n">
-        <v>12001986.855</v>
+        <v>11785958.484</v>
       </c>
       <c r="D4" t="n">
-        <v>21085069.14</v>
+        <v>21085069.141</v>
       </c>
     </row>
     <row r="5">
@@ -14007,13 +14679,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15564926.584</v>
+        <v>15529444.87</v>
       </c>
       <c r="C5" t="n">
         <v>1637870.342</v>
       </c>
       <c r="D5" t="n">
-        <v>17202796.926</v>
+        <v>17167315.212</v>
       </c>
     </row>
     <row r="6">
@@ -14023,10 +14695,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17749396.213</v>
+        <v>17759436.593</v>
       </c>
       <c r="C6" t="n">
-        <v>3387219.03</v>
+        <v>3377178.65</v>
       </c>
       <c r="D6" t="n">
         <v>21136615.243</v>
@@ -14055,13 +14727,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>140794395.883</v>
+        <v>140199685.983</v>
       </c>
       <c r="C8" t="n">
         <v>11981013.97</v>
       </c>
       <c r="D8" t="n">
-        <v>152775409.853</v>
+        <v>152180699.953</v>
       </c>
     </row>
     <row r="9">
@@ -14071,10 +14743,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24800947.646</v>
+        <v>25354067.746</v>
       </c>
       <c r="C9" t="n">
-        <v>4946686.497</v>
+        <v>4393566.397</v>
       </c>
       <c r="D9" t="n">
         <v>29747634.143</v>
@@ -14103,13 +14775,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1312691.104</v>
+        <v>945167.377</v>
       </c>
       <c r="C11" t="n">
         <v>582110.3370000001</v>
       </c>
       <c r="D11" t="n">
-        <v>1894801.441</v>
+        <v>1527277.714</v>
       </c>
     </row>
     <row r="12">
@@ -14135,13 +14807,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2809363.2</v>
+        <v>2814557.93</v>
       </c>
       <c r="C13" t="n">
-        <v>5099538</v>
+        <v>5114529.49</v>
       </c>
       <c r="D13" t="n">
-        <v>7908901.2</v>
+        <v>7929087.42</v>
       </c>
     </row>
   </sheetData>
@@ -14187,13 +14859,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>266299377.515</v>
+        <v>266826474.836</v>
       </c>
       <c r="C2" t="n">
-        <v>79988594.147</v>
+        <v>78483967.706</v>
       </c>
       <c r="D2" t="n">
-        <v>346287971.662</v>
+        <v>345310442.542</v>
       </c>
     </row>
     <row r="3">
@@ -14306,7 +14978,7 @@
         <v>2445755.743</v>
       </c>
       <c r="E10" t="n">
-        <v>40060461.117</v>
+        <v>40800890.197</v>
       </c>
     </row>
     <row r="11">
@@ -14327,7 +14999,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>12528780.783</v>
+        <v>11788351.703</v>
       </c>
     </row>
     <row r="12">
@@ -14348,7 +15020,7 @@
         <v>2941520.686</v>
       </c>
       <c r="E12" t="n">
-        <v>9083082.285</v>
+        <v>9299110.657</v>
       </c>
     </row>
     <row r="13">
@@ -14369,7 +15041,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>12001986.855</v>
+        <v>11785958.484</v>
       </c>
     </row>
     <row r="14">
@@ -14387,10 +15059,10 @@
         <v>1836.4</v>
       </c>
       <c r="D14" t="n">
-        <v>16837.01</v>
+        <v>52318.724</v>
       </c>
       <c r="E14" t="n">
-        <v>15564926.584</v>
+        <v>15529444.87</v>
       </c>
     </row>
     <row r="15">
@@ -14432,7 +15104,7 @@
         <v>15260.8</v>
       </c>
       <c r="E16" t="n">
-        <v>17749396.213</v>
+        <v>17759436.593</v>
       </c>
     </row>
     <row r="17">
@@ -14453,7 +15125,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>3387219.03</v>
+        <v>3377178.65</v>
       </c>
     </row>
     <row r="18">
@@ -14513,10 +15185,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>19329.8</v>
+        <v>614039.7000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>140794395.883</v>
+        <v>140199685.983</v>
       </c>
     </row>
     <row r="21">
@@ -14558,7 +15230,7 @@
         <v>600017.8199999999</v>
       </c>
       <c r="E22" t="n">
-        <v>24800947.646</v>
+        <v>25354067.746</v>
       </c>
     </row>
     <row r="23">
@@ -14579,7 +15251,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4946686.497</v>
+        <v>4393566.397</v>
       </c>
     </row>
     <row r="24">
@@ -14639,10 +15311,10 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>367523.727</v>
       </c>
       <c r="E26" t="n">
-        <v>1312691.104</v>
+        <v>945167.377</v>
       </c>
     </row>
     <row r="27">
@@ -14726,7 +15398,7 @@
         <v>161200.68</v>
       </c>
       <c r="E30" t="n">
-        <v>2809363.2</v>
+        <v>2814557.93</v>
       </c>
     </row>
     <row r="31">
@@ -14741,13 +15413,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9656.629999999999</v>
+        <v>29842.85</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>5099538</v>
+        <v>5114529.49</v>
       </c>
     </row>
     <row r="32">

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H505"/>
+  <dimension ref="A1:H529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14585,6 +14585,678 @@
         <v>5194.73</v>
       </c>
       <c r="H505" t="n">
+        <v>2814557.93</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>22231922.592</v>
+      </c>
+      <c r="D506" t="n">
+        <v>0</v>
+      </c>
+      <c r="E506" t="n">
+        <v>0</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0</v>
+      </c>
+      <c r="G506" t="n">
+        <v>0</v>
+      </c>
+      <c r="H506" t="n">
+        <v>22231922.592</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>2519599.518</v>
+      </c>
+      <c r="D507" t="n">
+        <v>0</v>
+      </c>
+      <c r="E507" t="n">
+        <v>0</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0</v>
+      </c>
+      <c r="G507" t="n">
+        <v>0</v>
+      </c>
+      <c r="H507" t="n">
+        <v>2519599.518</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>11788351.703</v>
+      </c>
+      <c r="D508" t="n">
+        <v>0</v>
+      </c>
+      <c r="E508" t="n">
+        <v>0</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0</v>
+      </c>
+      <c r="G508" t="n">
+        <v>-136505.132</v>
+      </c>
+      <c r="H508" t="n">
+        <v>11651846.571</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>40800890.197</v>
+      </c>
+      <c r="D509" t="n">
+        <v>0</v>
+      </c>
+      <c r="E509" t="n">
+        <v>0</v>
+      </c>
+      <c r="F509" t="n">
+        <v>0</v>
+      </c>
+      <c r="G509" t="n">
+        <v>136505.132</v>
+      </c>
+      <c r="H509" t="n">
+        <v>40937395.329</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>11785958.484</v>
+      </c>
+      <c r="D510" t="n">
+        <v>0</v>
+      </c>
+      <c r="E510" t="n">
+        <v>0</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0</v>
+      </c>
+      <c r="G510" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H510" t="n">
+        <v>11785958.483</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>9299110.657</v>
+      </c>
+      <c r="D511" t="n">
+        <v>0</v>
+      </c>
+      <c r="E511" t="n">
+        <v>603147.62</v>
+      </c>
+      <c r="F511" t="n">
+        <v>-603147.62</v>
+      </c>
+      <c r="G511" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H511" t="n">
+        <v>8695963.036</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D512" t="n">
+        <v>0</v>
+      </c>
+      <c r="E512" t="n">
+        <v>0</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0</v>
+      </c>
+      <c r="G512" t="n">
+        <v>0</v>
+      </c>
+      <c r="H512" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>15529444.87</v>
+      </c>
+      <c r="D513" t="n">
+        <v>0</v>
+      </c>
+      <c r="E513" t="n">
+        <v>5999.85</v>
+      </c>
+      <c r="F513" t="n">
+        <v>-5999.85</v>
+      </c>
+      <c r="G513" t="n">
+        <v>0</v>
+      </c>
+      <c r="H513" t="n">
+        <v>15523445.02</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>3377178.65</v>
+      </c>
+      <c r="D514" t="n">
+        <v>0</v>
+      </c>
+      <c r="E514" t="n">
+        <v>0</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0</v>
+      </c>
+      <c r="G514" t="n">
+        <v>0</v>
+      </c>
+      <c r="H514" t="n">
+        <v>3377178.65</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>17759436.593</v>
+      </c>
+      <c r="D515" t="n">
+        <v>0</v>
+      </c>
+      <c r="E515" t="n">
+        <v>0</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0</v>
+      </c>
+      <c r="G515" t="n">
+        <v>0</v>
+      </c>
+      <c r="H515" t="n">
+        <v>17759436.593</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>178515.19</v>
+      </c>
+      <c r="D516" t="n">
+        <v>0</v>
+      </c>
+      <c r="E516" t="n">
+        <v>0</v>
+      </c>
+      <c r="F516" t="n">
+        <v>0</v>
+      </c>
+      <c r="G516" t="n">
+        <v>0</v>
+      </c>
+      <c r="H516" t="n">
+        <v>178515.19</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>2800401.334</v>
+      </c>
+      <c r="D517" t="n">
+        <v>0</v>
+      </c>
+      <c r="E517" t="n">
+        <v>0</v>
+      </c>
+      <c r="F517" t="n">
+        <v>0</v>
+      </c>
+      <c r="G517" t="n">
+        <v>0</v>
+      </c>
+      <c r="H517" t="n">
+        <v>2800401.334</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D518" t="n">
+        <v>0</v>
+      </c>
+      <c r="E518" t="n">
+        <v>0</v>
+      </c>
+      <c r="F518" t="n">
+        <v>0</v>
+      </c>
+      <c r="G518" t="n">
+        <v>0</v>
+      </c>
+      <c r="H518" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>140199685.983</v>
+      </c>
+      <c r="D519" t="n">
+        <v>0</v>
+      </c>
+      <c r="E519" t="n">
+        <v>159493.2</v>
+      </c>
+      <c r="F519" t="n">
+        <v>-159493.2</v>
+      </c>
+      <c r="G519" t="n">
+        <v>0</v>
+      </c>
+      <c r="H519" t="n">
+        <v>140040192.783</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>4393566.397</v>
+      </c>
+      <c r="D520" t="n">
+        <v>0</v>
+      </c>
+      <c r="E520" t="n">
+        <v>0</v>
+      </c>
+      <c r="F520" t="n">
+        <v>0</v>
+      </c>
+      <c r="G520" t="n">
+        <v>0</v>
+      </c>
+      <c r="H520" t="n">
+        <v>4393566.397</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>25354067.746</v>
+      </c>
+      <c r="D521" t="n">
+        <v>0</v>
+      </c>
+      <c r="E521" t="n">
+        <v>0</v>
+      </c>
+      <c r="F521" t="n">
+        <v>0</v>
+      </c>
+      <c r="G521" t="n">
+        <v>0</v>
+      </c>
+      <c r="H521" t="n">
+        <v>25354067.746</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>0</v>
+      </c>
+      <c r="D522" t="n">
+        <v>0</v>
+      </c>
+      <c r="E522" t="n">
+        <v>0</v>
+      </c>
+      <c r="F522" t="n">
+        <v>0</v>
+      </c>
+      <c r="G522" t="n">
+        <v>0</v>
+      </c>
+      <c r="H522" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>0</v>
+      </c>
+      <c r="D523" t="n">
+        <v>0</v>
+      </c>
+      <c r="E523" t="n">
+        <v>0</v>
+      </c>
+      <c r="F523" t="n">
+        <v>0</v>
+      </c>
+      <c r="G523" t="n">
+        <v>0</v>
+      </c>
+      <c r="H523" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>582110.3370000001</v>
+      </c>
+      <c r="D524" t="n">
+        <v>0</v>
+      </c>
+      <c r="E524" t="n">
+        <v>0</v>
+      </c>
+      <c r="F524" t="n">
+        <v>0</v>
+      </c>
+      <c r="G524" t="n">
+        <v>0</v>
+      </c>
+      <c r="H524" t="n">
+        <v>582110.3370000001</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>945167.377</v>
+      </c>
+      <c r="D525" t="n">
+        <v>0</v>
+      </c>
+      <c r="E525" t="n">
+        <v>0</v>
+      </c>
+      <c r="F525" t="n">
+        <v>0</v>
+      </c>
+      <c r="G525" t="n">
+        <v>0</v>
+      </c>
+      <c r="H525" t="n">
+        <v>945167.377</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>5412950.551</v>
+      </c>
+      <c r="D526" t="n">
+        <v>0</v>
+      </c>
+      <c r="E526" t="n">
+        <v>0</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0</v>
+      </c>
+      <c r="G526" t="n">
+        <v>0</v>
+      </c>
+      <c r="H526" t="n">
+        <v>5412950.551</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>8804112.630999999</v>
+      </c>
+      <c r="D527" t="n">
+        <v>0</v>
+      </c>
+      <c r="E527" t="n">
+        <v>0</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0</v>
+      </c>
+      <c r="G527" t="n">
+        <v>0</v>
+      </c>
+      <c r="H527" t="n">
+        <v>8804112.630999999</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>5114529.49</v>
+      </c>
+      <c r="D528" t="n">
+        <v>0</v>
+      </c>
+      <c r="E528" t="n">
+        <v>0</v>
+      </c>
+      <c r="F528" t="n">
+        <v>0</v>
+      </c>
+      <c r="G528" t="n">
+        <v>0</v>
+      </c>
+      <c r="H528" t="n">
+        <v>5114529.49</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>2814557.93</v>
+      </c>
+      <c r="D529" t="n">
+        <v>0</v>
+      </c>
+      <c r="E529" t="n">
+        <v>0</v>
+      </c>
+      <c r="F529" t="n">
+        <v>0</v>
+      </c>
+      <c r="G529" t="n">
+        <v>0</v>
+      </c>
+      <c r="H529" t="n">
         <v>2814557.93</v>
       </c>
     </row>
@@ -14647,13 +15319,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40800890.197</v>
+        <v>40937395.329</v>
       </c>
       <c r="C3" t="n">
-        <v>11788351.703</v>
+        <v>11651846.571</v>
       </c>
       <c r="D3" t="n">
-        <v>52589241.9</v>
+        <v>52589241.90000001</v>
       </c>
     </row>
     <row r="4">
@@ -14663,13 +15335,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9299110.657</v>
+        <v>8695963.036</v>
       </c>
       <c r="C4" t="n">
-        <v>11785958.484</v>
+        <v>11785958.483</v>
       </c>
       <c r="D4" t="n">
-        <v>21085069.141</v>
+        <v>20481921.519</v>
       </c>
     </row>
     <row r="5">
@@ -14679,13 +15351,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15529444.87</v>
+        <v>15523445.02</v>
       </c>
       <c r="C5" t="n">
         <v>1637870.342</v>
       </c>
       <c r="D5" t="n">
-        <v>17167315.212</v>
+        <v>17161315.362</v>
       </c>
     </row>
     <row r="6">
@@ -14727,13 +15399,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>140199685.983</v>
+        <v>140040192.783</v>
       </c>
       <c r="C8" t="n">
         <v>11981013.97</v>
       </c>
       <c r="D8" t="n">
-        <v>152180699.953</v>
+        <v>152021206.753</v>
       </c>
     </row>
     <row r="9">
@@ -14859,13 +15531,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>266826474.836</v>
+        <v>266194339.297</v>
       </c>
       <c r="C2" t="n">
-        <v>78483967.706</v>
+        <v>78347462.573</v>
       </c>
       <c r="D2" t="n">
-        <v>345310442.542</v>
+        <v>344541801.8699999</v>
       </c>
     </row>
     <row r="3">
@@ -14978,7 +15650,7 @@
         <v>2445755.743</v>
       </c>
       <c r="E10" t="n">
-        <v>40800890.197</v>
+        <v>40937395.329</v>
       </c>
     </row>
     <row r="11">
@@ -14999,7 +15671,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>11788351.703</v>
+        <v>11651846.571</v>
       </c>
     </row>
     <row r="12">
@@ -15017,10 +15689,10 @@
         <v>28892.51</v>
       </c>
       <c r="D12" t="n">
-        <v>2941520.686</v>
+        <v>3544668.306</v>
       </c>
       <c r="E12" t="n">
-        <v>9299110.657</v>
+        <v>8695963.036</v>
       </c>
     </row>
     <row r="13">
@@ -15041,7 +15713,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>11785958.484</v>
+        <v>11785958.483</v>
       </c>
     </row>
     <row r="14">
@@ -15059,10 +15731,10 @@
         <v>1836.4</v>
       </c>
       <c r="D14" t="n">
-        <v>52318.724</v>
+        <v>58318.574</v>
       </c>
       <c r="E14" t="n">
-        <v>15529444.87</v>
+        <v>15523445.02</v>
       </c>
     </row>
     <row r="15">
@@ -15185,10 +15857,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>614039.7000000001</v>
+        <v>773532.9000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>140199685.983</v>
+        <v>140040192.783</v>
       </c>
     </row>
     <row r="21">

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H529"/>
+  <dimension ref="A1:H553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15257,6 +15257,678 @@
         <v>0</v>
       </c>
       <c r="H529" t="n">
+        <v>2814557.93</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>22231922.592</v>
+      </c>
+      <c r="D530" t="n">
+        <v>0</v>
+      </c>
+      <c r="E530" t="n">
+        <v>0</v>
+      </c>
+      <c r="F530" t="n">
+        <v>0</v>
+      </c>
+      <c r="G530" t="n">
+        <v>0</v>
+      </c>
+      <c r="H530" t="n">
+        <v>22231922.592</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>2519599.518</v>
+      </c>
+      <c r="D531" t="n">
+        <v>0</v>
+      </c>
+      <c r="E531" t="n">
+        <v>0</v>
+      </c>
+      <c r="F531" t="n">
+        <v>0</v>
+      </c>
+      <c r="G531" t="n">
+        <v>0</v>
+      </c>
+      <c r="H531" t="n">
+        <v>2519599.518</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>11651846.571</v>
+      </c>
+      <c r="D532" t="n">
+        <v>0</v>
+      </c>
+      <c r="E532" t="n">
+        <v>0</v>
+      </c>
+      <c r="F532" t="n">
+        <v>0</v>
+      </c>
+      <c r="G532" t="n">
+        <v>0</v>
+      </c>
+      <c r="H532" t="n">
+        <v>11651846.571</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>40937395.329</v>
+      </c>
+      <c r="D533" t="n">
+        <v>0</v>
+      </c>
+      <c r="E533" t="n">
+        <v>0</v>
+      </c>
+      <c r="F533" t="n">
+        <v>0</v>
+      </c>
+      <c r="G533" t="n">
+        <v>0</v>
+      </c>
+      <c r="H533" t="n">
+        <v>40937395.329</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>11785958.483</v>
+      </c>
+      <c r="D534" t="n">
+        <v>0</v>
+      </c>
+      <c r="E534" t="n">
+        <v>0</v>
+      </c>
+      <c r="F534" t="n">
+        <v>0</v>
+      </c>
+      <c r="G534" t="n">
+        <v>0</v>
+      </c>
+      <c r="H534" t="n">
+        <v>11785958.483</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>8695963.036</v>
+      </c>
+      <c r="D535" t="n">
+        <v>598969.33</v>
+      </c>
+      <c r="E535" t="n">
+        <v>0</v>
+      </c>
+      <c r="F535" t="n">
+        <v>598969.33</v>
+      </c>
+      <c r="G535" t="n">
+        <v>0</v>
+      </c>
+      <c r="H535" t="n">
+        <v>9294932.366</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D536" t="n">
+        <v>0</v>
+      </c>
+      <c r="E536" t="n">
+        <v>0</v>
+      </c>
+      <c r="F536" t="n">
+        <v>0</v>
+      </c>
+      <c r="G536" t="n">
+        <v>0</v>
+      </c>
+      <c r="H536" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>15523445.02</v>
+      </c>
+      <c r="D537" t="n">
+        <v>0</v>
+      </c>
+      <c r="E537" t="n">
+        <v>0</v>
+      </c>
+      <c r="F537" t="n">
+        <v>0</v>
+      </c>
+      <c r="G537" t="n">
+        <v>0</v>
+      </c>
+      <c r="H537" t="n">
+        <v>15523445.02</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>3377178.65</v>
+      </c>
+      <c r="D538" t="n">
+        <v>0</v>
+      </c>
+      <c r="E538" t="n">
+        <v>0</v>
+      </c>
+      <c r="F538" t="n">
+        <v>0</v>
+      </c>
+      <c r="G538" t="n">
+        <v>0</v>
+      </c>
+      <c r="H538" t="n">
+        <v>3377178.65</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>17759436.593</v>
+      </c>
+      <c r="D539" t="n">
+        <v>0</v>
+      </c>
+      <c r="E539" t="n">
+        <v>16006.37</v>
+      </c>
+      <c r="F539" t="n">
+        <v>-16006.37</v>
+      </c>
+      <c r="G539" t="n">
+        <v>0</v>
+      </c>
+      <c r="H539" t="n">
+        <v>17743430.223</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>178515.19</v>
+      </c>
+      <c r="D540" t="n">
+        <v>0</v>
+      </c>
+      <c r="E540" t="n">
+        <v>0</v>
+      </c>
+      <c r="F540" t="n">
+        <v>0</v>
+      </c>
+      <c r="G540" t="n">
+        <v>0</v>
+      </c>
+      <c r="H540" t="n">
+        <v>178515.19</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>2800401.334</v>
+      </c>
+      <c r="D541" t="n">
+        <v>0</v>
+      </c>
+      <c r="E541" t="n">
+        <v>0</v>
+      </c>
+      <c r="F541" t="n">
+        <v>0</v>
+      </c>
+      <c r="G541" t="n">
+        <v>0</v>
+      </c>
+      <c r="H541" t="n">
+        <v>2800401.334</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D542" t="n">
+        <v>0</v>
+      </c>
+      <c r="E542" t="n">
+        <v>0</v>
+      </c>
+      <c r="F542" t="n">
+        <v>0</v>
+      </c>
+      <c r="G542" t="n">
+        <v>0</v>
+      </c>
+      <c r="H542" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>140040192.783</v>
+      </c>
+      <c r="D543" t="n">
+        <v>0</v>
+      </c>
+      <c r="E543" t="n">
+        <v>0</v>
+      </c>
+      <c r="F543" t="n">
+        <v>0</v>
+      </c>
+      <c r="G543" t="n">
+        <v>0</v>
+      </c>
+      <c r="H543" t="n">
+        <v>140040192.783</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>4393566.397</v>
+      </c>
+      <c r="D544" t="n">
+        <v>0</v>
+      </c>
+      <c r="E544" t="n">
+        <v>0</v>
+      </c>
+      <c r="F544" t="n">
+        <v>0</v>
+      </c>
+      <c r="G544" t="n">
+        <v>0</v>
+      </c>
+      <c r="H544" t="n">
+        <v>4393566.397</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>25354067.746</v>
+      </c>
+      <c r="D545" t="n">
+        <v>0</v>
+      </c>
+      <c r="E545" t="n">
+        <v>0</v>
+      </c>
+      <c r="F545" t="n">
+        <v>0</v>
+      </c>
+      <c r="G545" t="n">
+        <v>0</v>
+      </c>
+      <c r="H545" t="n">
+        <v>25354067.746</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>0</v>
+      </c>
+      <c r="D546" t="n">
+        <v>0</v>
+      </c>
+      <c r="E546" t="n">
+        <v>0</v>
+      </c>
+      <c r="F546" t="n">
+        <v>0</v>
+      </c>
+      <c r="G546" t="n">
+        <v>0</v>
+      </c>
+      <c r="H546" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>0</v>
+      </c>
+      <c r="D547" t="n">
+        <v>0</v>
+      </c>
+      <c r="E547" t="n">
+        <v>0</v>
+      </c>
+      <c r="F547" t="n">
+        <v>0</v>
+      </c>
+      <c r="G547" t="n">
+        <v>0</v>
+      </c>
+      <c r="H547" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>582110.3370000001</v>
+      </c>
+      <c r="D548" t="n">
+        <v>0</v>
+      </c>
+      <c r="E548" t="n">
+        <v>0</v>
+      </c>
+      <c r="F548" t="n">
+        <v>0</v>
+      </c>
+      <c r="G548" t="n">
+        <v>0</v>
+      </c>
+      <c r="H548" t="n">
+        <v>582110.3370000001</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>945167.377</v>
+      </c>
+      <c r="D549" t="n">
+        <v>0</v>
+      </c>
+      <c r="E549" t="n">
+        <v>0</v>
+      </c>
+      <c r="F549" t="n">
+        <v>0</v>
+      </c>
+      <c r="G549" t="n">
+        <v>0</v>
+      </c>
+      <c r="H549" t="n">
+        <v>945167.377</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>5412950.551</v>
+      </c>
+      <c r="D550" t="n">
+        <v>0</v>
+      </c>
+      <c r="E550" t="n">
+        <v>0</v>
+      </c>
+      <c r="F550" t="n">
+        <v>0</v>
+      </c>
+      <c r="G550" t="n">
+        <v>4667.506</v>
+      </c>
+      <c r="H550" t="n">
+        <v>5417618.057</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>8804112.630999999</v>
+      </c>
+      <c r="D551" t="n">
+        <v>0</v>
+      </c>
+      <c r="E551" t="n">
+        <v>1058679.682</v>
+      </c>
+      <c r="F551" t="n">
+        <v>-1058679.682</v>
+      </c>
+      <c r="G551" t="n">
+        <v>-4667.506</v>
+      </c>
+      <c r="H551" t="n">
+        <v>7740765.443</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>5114529.49</v>
+      </c>
+      <c r="D552" t="n">
+        <v>258738.85</v>
+      </c>
+      <c r="E552" t="n">
+        <v>0</v>
+      </c>
+      <c r="F552" t="n">
+        <v>258738.85</v>
+      </c>
+      <c r="G552" t="n">
+        <v>0</v>
+      </c>
+      <c r="H552" t="n">
+        <v>5373268.34</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>2814557.93</v>
+      </c>
+      <c r="D553" t="n">
+        <v>0</v>
+      </c>
+      <c r="E553" t="n">
+        <v>0</v>
+      </c>
+      <c r="F553" t="n">
+        <v>0</v>
+      </c>
+      <c r="G553" t="n">
+        <v>0</v>
+      </c>
+      <c r="H553" t="n">
         <v>2814557.93</v>
       </c>
     </row>
@@ -15335,13 +16007,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8695963.036</v>
+        <v>9294932.366</v>
       </c>
       <c r="C4" t="n">
         <v>11785958.483</v>
       </c>
       <c r="D4" t="n">
-        <v>20481921.519</v>
+        <v>21080890.849</v>
       </c>
     </row>
     <row r="5">
@@ -15367,13 +16039,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17759436.593</v>
+        <v>17743430.223</v>
       </c>
       <c r="C6" t="n">
         <v>3377178.65</v>
       </c>
       <c r="D6" t="n">
-        <v>21136615.243</v>
+        <v>21120608.873</v>
       </c>
     </row>
     <row r="7">
@@ -15463,13 +16135,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8804112.630999999</v>
+        <v>7740765.443</v>
       </c>
       <c r="C12" t="n">
-        <v>5412950.551</v>
+        <v>5417618.057</v>
       </c>
       <c r="D12" t="n">
-        <v>14217063.182</v>
+        <v>13158383.5</v>
       </c>
     </row>
     <row r="13">
@@ -15482,10 +16154,10 @@
         <v>2814557.93</v>
       </c>
       <c r="C13" t="n">
-        <v>5114529.49</v>
+        <v>5373268.34</v>
       </c>
       <c r="D13" t="n">
-        <v>7929087.42</v>
+        <v>8187826.27</v>
       </c>
     </row>
   </sheetData>
@@ -15531,13 +16203,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>266194339.297</v>
+        <v>265713955.069</v>
       </c>
       <c r="C2" t="n">
-        <v>78347462.573</v>
+        <v>78610868.92900001</v>
       </c>
       <c r="D2" t="n">
-        <v>344541801.8699999</v>
+        <v>344324823.998</v>
       </c>
     </row>
     <row r="3">
@@ -15686,13 +16358,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28892.51</v>
+        <v>627861.84</v>
       </c>
       <c r="D12" t="n">
         <v>3544668.306</v>
       </c>
       <c r="E12" t="n">
-        <v>8695963.036</v>
+        <v>9294932.366</v>
       </c>
     </row>
     <row r="13">
@@ -15773,10 +16445,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>15260.8</v>
+        <v>31267.17</v>
       </c>
       <c r="E16" t="n">
-        <v>17759436.593</v>
+        <v>17743430.223</v>
       </c>
     </row>
     <row r="17">
@@ -16025,10 +16697,10 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>3446660.747</v>
+        <v>4505340.429</v>
       </c>
       <c r="E28" t="n">
-        <v>8804112.630999999</v>
+        <v>7740765.443</v>
       </c>
     </row>
     <row r="29">
@@ -16049,7 +16721,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>5412950.551</v>
+        <v>5417618.057</v>
       </c>
     </row>
     <row r="30">
@@ -16085,13 +16757,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>29842.85</v>
+        <v>288581.7</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>5114529.49</v>
+        <v>5373268.34</v>
       </c>
     </row>
     <row r="32">

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H553"/>
+  <dimension ref="A1:H577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15929,6 +15929,678 @@
         <v>0</v>
       </c>
       <c r="H553" t="n">
+        <v>2814557.93</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>22231922.592</v>
+      </c>
+      <c r="D554" t="n">
+        <v>0</v>
+      </c>
+      <c r="E554" t="n">
+        <v>0</v>
+      </c>
+      <c r="F554" t="n">
+        <v>0</v>
+      </c>
+      <c r="G554" t="n">
+        <v>0</v>
+      </c>
+      <c r="H554" t="n">
+        <v>22231922.592</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>2519599.518</v>
+      </c>
+      <c r="D555" t="n">
+        <v>0</v>
+      </c>
+      <c r="E555" t="n">
+        <v>604498.91</v>
+      </c>
+      <c r="F555" t="n">
+        <v>-604498.91</v>
+      </c>
+      <c r="G555" t="n">
+        <v>0</v>
+      </c>
+      <c r="H555" t="n">
+        <v>1915100.608</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>11651846.571</v>
+      </c>
+      <c r="D556" t="n">
+        <v>0</v>
+      </c>
+      <c r="E556" t="n">
+        <v>0</v>
+      </c>
+      <c r="F556" t="n">
+        <v>0</v>
+      </c>
+      <c r="G556" t="n">
+        <v>0</v>
+      </c>
+      <c r="H556" t="n">
+        <v>11651846.571</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>40937395.329</v>
+      </c>
+      <c r="D557" t="n">
+        <v>0</v>
+      </c>
+      <c r="E557" t="n">
+        <v>1765459.168</v>
+      </c>
+      <c r="F557" t="n">
+        <v>-1765459.168</v>
+      </c>
+      <c r="G557" t="n">
+        <v>0</v>
+      </c>
+      <c r="H557" t="n">
+        <v>39171936.161</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>11785958.483</v>
+      </c>
+      <c r="D558" t="n">
+        <v>0</v>
+      </c>
+      <c r="E558" t="n">
+        <v>0</v>
+      </c>
+      <c r="F558" t="n">
+        <v>0</v>
+      </c>
+      <c r="G558" t="n">
+        <v>0</v>
+      </c>
+      <c r="H558" t="n">
+        <v>11785958.483</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>9294932.366</v>
+      </c>
+      <c r="D559" t="n">
+        <v>0</v>
+      </c>
+      <c r="E559" t="n">
+        <v>0</v>
+      </c>
+      <c r="F559" t="n">
+        <v>0</v>
+      </c>
+      <c r="G559" t="n">
+        <v>0</v>
+      </c>
+      <c r="H559" t="n">
+        <v>9294932.366</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D560" t="n">
+        <v>0</v>
+      </c>
+      <c r="E560" t="n">
+        <v>0</v>
+      </c>
+      <c r="F560" t="n">
+        <v>0</v>
+      </c>
+      <c r="G560" t="n">
+        <v>0</v>
+      </c>
+      <c r="H560" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>15523445.02</v>
+      </c>
+      <c r="D561" t="n">
+        <v>953.5</v>
+      </c>
+      <c r="E561" t="n">
+        <v>11954.515</v>
+      </c>
+      <c r="F561" t="n">
+        <v>-11001.015</v>
+      </c>
+      <c r="G561" t="n">
+        <v>0</v>
+      </c>
+      <c r="H561" t="n">
+        <v>15512444.005</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>3377178.65</v>
+      </c>
+      <c r="D562" t="n">
+        <v>0</v>
+      </c>
+      <c r="E562" t="n">
+        <v>0</v>
+      </c>
+      <c r="F562" t="n">
+        <v>0</v>
+      </c>
+      <c r="G562" t="n">
+        <v>0</v>
+      </c>
+      <c r="H562" t="n">
+        <v>3377178.65</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>17743430.223</v>
+      </c>
+      <c r="D563" t="n">
+        <v>0</v>
+      </c>
+      <c r="E563" t="n">
+        <v>0</v>
+      </c>
+      <c r="F563" t="n">
+        <v>0</v>
+      </c>
+      <c r="G563" t="n">
+        <v>0</v>
+      </c>
+      <c r="H563" t="n">
+        <v>17743430.223</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>178515.19</v>
+      </c>
+      <c r="D564" t="n">
+        <v>0</v>
+      </c>
+      <c r="E564" t="n">
+        <v>0</v>
+      </c>
+      <c r="F564" t="n">
+        <v>0</v>
+      </c>
+      <c r="G564" t="n">
+        <v>0</v>
+      </c>
+      <c r="H564" t="n">
+        <v>178515.19</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>2800401.334</v>
+      </c>
+      <c r="D565" t="n">
+        <v>0</v>
+      </c>
+      <c r="E565" t="n">
+        <v>0</v>
+      </c>
+      <c r="F565" t="n">
+        <v>0</v>
+      </c>
+      <c r="G565" t="n">
+        <v>0</v>
+      </c>
+      <c r="H565" t="n">
+        <v>2800401.334</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D566" t="n">
+        <v>0</v>
+      </c>
+      <c r="E566" t="n">
+        <v>0</v>
+      </c>
+      <c r="F566" t="n">
+        <v>0</v>
+      </c>
+      <c r="G566" t="n">
+        <v>0</v>
+      </c>
+      <c r="H566" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>140040192.783</v>
+      </c>
+      <c r="D567" t="n">
+        <v>0</v>
+      </c>
+      <c r="E567" t="n">
+        <v>0</v>
+      </c>
+      <c r="F567" t="n">
+        <v>0</v>
+      </c>
+      <c r="G567" t="n">
+        <v>0</v>
+      </c>
+      <c r="H567" t="n">
+        <v>140040192.783</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>4393566.397</v>
+      </c>
+      <c r="D568" t="n">
+        <v>0</v>
+      </c>
+      <c r="E568" t="n">
+        <v>0</v>
+      </c>
+      <c r="F568" t="n">
+        <v>0</v>
+      </c>
+      <c r="G568" t="n">
+        <v>0</v>
+      </c>
+      <c r="H568" t="n">
+        <v>4393566.397</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>25354067.746</v>
+      </c>
+      <c r="D569" t="n">
+        <v>0</v>
+      </c>
+      <c r="E569" t="n">
+        <v>562137.41</v>
+      </c>
+      <c r="F569" t="n">
+        <v>-562137.41</v>
+      </c>
+      <c r="G569" t="n">
+        <v>0</v>
+      </c>
+      <c r="H569" t="n">
+        <v>24791930.336</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>0</v>
+      </c>
+      <c r="D570" t="n">
+        <v>0</v>
+      </c>
+      <c r="E570" t="n">
+        <v>0</v>
+      </c>
+      <c r="F570" t="n">
+        <v>0</v>
+      </c>
+      <c r="G570" t="n">
+        <v>0</v>
+      </c>
+      <c r="H570" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>0</v>
+      </c>
+      <c r="D571" t="n">
+        <v>0</v>
+      </c>
+      <c r="E571" t="n">
+        <v>0</v>
+      </c>
+      <c r="F571" t="n">
+        <v>0</v>
+      </c>
+      <c r="G571" t="n">
+        <v>0</v>
+      </c>
+      <c r="H571" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>582110.3370000001</v>
+      </c>
+      <c r="D572" t="n">
+        <v>0</v>
+      </c>
+      <c r="E572" t="n">
+        <v>0</v>
+      </c>
+      <c r="F572" t="n">
+        <v>0</v>
+      </c>
+      <c r="G572" t="n">
+        <v>0</v>
+      </c>
+      <c r="H572" t="n">
+        <v>582110.3370000001</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>945167.377</v>
+      </c>
+      <c r="D573" t="n">
+        <v>0</v>
+      </c>
+      <c r="E573" t="n">
+        <v>0</v>
+      </c>
+      <c r="F573" t="n">
+        <v>0</v>
+      </c>
+      <c r="G573" t="n">
+        <v>0</v>
+      </c>
+      <c r="H573" t="n">
+        <v>945167.377</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>5417618.057</v>
+      </c>
+      <c r="D574" t="n">
+        <v>0</v>
+      </c>
+      <c r="E574" t="n">
+        <v>0</v>
+      </c>
+      <c r="F574" t="n">
+        <v>0</v>
+      </c>
+      <c r="G574" t="n">
+        <v>0</v>
+      </c>
+      <c r="H574" t="n">
+        <v>5417618.057</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>7740765.443</v>
+      </c>
+      <c r="D575" t="n">
+        <v>0</v>
+      </c>
+      <c r="E575" t="n">
+        <v>0</v>
+      </c>
+      <c r="F575" t="n">
+        <v>0</v>
+      </c>
+      <c r="G575" t="n">
+        <v>0</v>
+      </c>
+      <c r="H575" t="n">
+        <v>7740765.443</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>5373268.34</v>
+      </c>
+      <c r="D576" t="n">
+        <v>341481.36</v>
+      </c>
+      <c r="E576" t="n">
+        <v>0</v>
+      </c>
+      <c r="F576" t="n">
+        <v>341481.36</v>
+      </c>
+      <c r="G576" t="n">
+        <v>0</v>
+      </c>
+      <c r="H576" t="n">
+        <v>5714749.7</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>2814557.93</v>
+      </c>
+      <c r="D577" t="n">
+        <v>0</v>
+      </c>
+      <c r="E577" t="n">
+        <v>0</v>
+      </c>
+      <c r="F577" t="n">
+        <v>0</v>
+      </c>
+      <c r="G577" t="n">
+        <v>0</v>
+      </c>
+      <c r="H577" t="n">
         <v>2814557.93</v>
       </c>
     </row>
@@ -15975,13 +16647,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2519599.518</v>
+        <v>1915100.608</v>
       </c>
       <c r="C2" t="n">
         <v>22231922.592</v>
       </c>
       <c r="D2" t="n">
-        <v>24751522.11</v>
+        <v>24147023.2</v>
       </c>
     </row>
     <row r="3">
@@ -15991,13 +16663,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40937395.329</v>
+        <v>39171936.161</v>
       </c>
       <c r="C3" t="n">
         <v>11651846.571</v>
       </c>
       <c r="D3" t="n">
-        <v>52589241.90000001</v>
+        <v>50823782.732</v>
       </c>
     </row>
     <row r="4">
@@ -16023,13 +16695,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15523445.02</v>
+        <v>15512444.005</v>
       </c>
       <c r="C5" t="n">
         <v>1637870.342</v>
       </c>
       <c r="D5" t="n">
-        <v>17161315.362</v>
+        <v>17150314.347</v>
       </c>
     </row>
     <row r="6">
@@ -16087,13 +16759,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25354067.746</v>
+        <v>24791930.336</v>
       </c>
       <c r="C9" t="n">
         <v>4393566.397</v>
       </c>
       <c r="D9" t="n">
-        <v>29747634.143</v>
+        <v>29185496.733</v>
       </c>
     </row>
     <row r="10">
@@ -16154,10 +16826,10 @@
         <v>2814557.93</v>
       </c>
       <c r="C13" t="n">
-        <v>5373268.34</v>
+        <v>5714749.7</v>
       </c>
       <c r="D13" t="n">
-        <v>8187826.27</v>
+        <v>8529307.630000001</v>
       </c>
     </row>
   </sheetData>
@@ -16203,13 +16875,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>265713955.069</v>
+        <v>262770858.566</v>
       </c>
       <c r="C2" t="n">
-        <v>78610868.92900001</v>
+        <v>78952350.289</v>
       </c>
       <c r="D2" t="n">
-        <v>344324823.998</v>
+        <v>341723208.855</v>
       </c>
     </row>
     <row r="3">
@@ -16277,10 +16949,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1067691.97</v>
+        <v>1672190.88</v>
       </c>
       <c r="E8" t="n">
-        <v>2519599.518</v>
+        <v>1915100.608</v>
       </c>
     </row>
     <row r="9">
@@ -16319,10 +16991,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2445755.743</v>
+        <v>4211214.911</v>
       </c>
       <c r="E10" t="n">
-        <v>40937395.329</v>
+        <v>39171936.161</v>
       </c>
     </row>
     <row r="11">
@@ -16400,13 +17072,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1836.4</v>
+        <v>2789.9</v>
       </c>
       <c r="D14" t="n">
-        <v>58318.574</v>
+        <v>70273.08900000001</v>
       </c>
       <c r="E14" t="n">
-        <v>15523445.02</v>
+        <v>15512444.005</v>
       </c>
     </row>
     <row r="15">
@@ -16571,10 +17243,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>600017.8199999999</v>
+        <v>1162155.23</v>
       </c>
       <c r="E22" t="n">
-        <v>25354067.746</v>
+        <v>24791930.336</v>
       </c>
     </row>
     <row r="23">
@@ -16757,13 +17429,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>288581.7</v>
+        <v>630063.0600000001</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>5373268.34</v>
+        <v>5714749.7</v>
       </c>
     </row>
     <row r="32">

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H577"/>
+  <dimension ref="A1:H601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16601,6 +16601,678 @@
         <v>0</v>
       </c>
       <c r="H577" t="n">
+        <v>2814557.93</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>22231922.592</v>
+      </c>
+      <c r="D578" t="n">
+        <v>0</v>
+      </c>
+      <c r="E578" t="n">
+        <v>0</v>
+      </c>
+      <c r="F578" t="n">
+        <v>0</v>
+      </c>
+      <c r="G578" t="n">
+        <v>-4948.6</v>
+      </c>
+      <c r="H578" t="n">
+        <v>22226973.992</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>1915100.608</v>
+      </c>
+      <c r="D579" t="n">
+        <v>0</v>
+      </c>
+      <c r="E579" t="n">
+        <v>855646.63</v>
+      </c>
+      <c r="F579" t="n">
+        <v>-855646.63</v>
+      </c>
+      <c r="G579" t="n">
+        <v>4948.6</v>
+      </c>
+      <c r="H579" t="n">
+        <v>1064402.578</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>11651846.571</v>
+      </c>
+      <c r="D580" t="n">
+        <v>0</v>
+      </c>
+      <c r="E580" t="n">
+        <v>0</v>
+      </c>
+      <c r="F580" t="n">
+        <v>0</v>
+      </c>
+      <c r="G580" t="n">
+        <v>0</v>
+      </c>
+      <c r="H580" t="n">
+        <v>11651846.571</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>39171936.161</v>
+      </c>
+      <c r="D581" t="n">
+        <v>0</v>
+      </c>
+      <c r="E581" t="n">
+        <v>30360.24</v>
+      </c>
+      <c r="F581" t="n">
+        <v>-30360.24</v>
+      </c>
+      <c r="G581" t="n">
+        <v>0</v>
+      </c>
+      <c r="H581" t="n">
+        <v>39141575.921</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>11785958.483</v>
+      </c>
+      <c r="D582" t="n">
+        <v>0</v>
+      </c>
+      <c r="E582" t="n">
+        <v>0</v>
+      </c>
+      <c r="F582" t="n">
+        <v>0</v>
+      </c>
+      <c r="G582" t="n">
+        <v>0</v>
+      </c>
+      <c r="H582" t="n">
+        <v>11785958.483</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>9294932.366</v>
+      </c>
+      <c r="D583" t="n">
+        <v>0</v>
+      </c>
+      <c r="E583" t="n">
+        <v>216028.372</v>
+      </c>
+      <c r="F583" t="n">
+        <v>-216028.372</v>
+      </c>
+      <c r="G583" t="n">
+        <v>0</v>
+      </c>
+      <c r="H583" t="n">
+        <v>9078903.994999999</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D584" t="n">
+        <v>0</v>
+      </c>
+      <c r="E584" t="n">
+        <v>0</v>
+      </c>
+      <c r="F584" t="n">
+        <v>0</v>
+      </c>
+      <c r="G584" t="n">
+        <v>0</v>
+      </c>
+      <c r="H584" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>15512444.005</v>
+      </c>
+      <c r="D585" t="n">
+        <v>6030.3</v>
+      </c>
+      <c r="E585" t="n">
+        <v>0</v>
+      </c>
+      <c r="F585" t="n">
+        <v>6030.3</v>
+      </c>
+      <c r="G585" t="n">
+        <v>0</v>
+      </c>
+      <c r="H585" t="n">
+        <v>15518474.305</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>3377178.65</v>
+      </c>
+      <c r="D586" t="n">
+        <v>0</v>
+      </c>
+      <c r="E586" t="n">
+        <v>0</v>
+      </c>
+      <c r="F586" t="n">
+        <v>0</v>
+      </c>
+      <c r="G586" t="n">
+        <v>0</v>
+      </c>
+      <c r="H586" t="n">
+        <v>3377178.65</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>17743430.223</v>
+      </c>
+      <c r="D587" t="n">
+        <v>0</v>
+      </c>
+      <c r="E587" t="n">
+        <v>0</v>
+      </c>
+      <c r="F587" t="n">
+        <v>0</v>
+      </c>
+      <c r="G587" t="n">
+        <v>0</v>
+      </c>
+      <c r="H587" t="n">
+        <v>17743430.223</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>178515.19</v>
+      </c>
+      <c r="D588" t="n">
+        <v>0</v>
+      </c>
+      <c r="E588" t="n">
+        <v>0</v>
+      </c>
+      <c r="F588" t="n">
+        <v>0</v>
+      </c>
+      <c r="G588" t="n">
+        <v>0</v>
+      </c>
+      <c r="H588" t="n">
+        <v>178515.19</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>2800401.334</v>
+      </c>
+      <c r="D589" t="n">
+        <v>0</v>
+      </c>
+      <c r="E589" t="n">
+        <v>95274.67999999999</v>
+      </c>
+      <c r="F589" t="n">
+        <v>-95274.67999999999</v>
+      </c>
+      <c r="G589" t="n">
+        <v>0</v>
+      </c>
+      <c r="H589" t="n">
+        <v>2705126.654</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D590" t="n">
+        <v>0</v>
+      </c>
+      <c r="E590" t="n">
+        <v>0</v>
+      </c>
+      <c r="F590" t="n">
+        <v>0</v>
+      </c>
+      <c r="G590" t="n">
+        <v>0</v>
+      </c>
+      <c r="H590" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>140040192.783</v>
+      </c>
+      <c r="D591" t="n">
+        <v>0</v>
+      </c>
+      <c r="E591" t="n">
+        <v>646860.8</v>
+      </c>
+      <c r="F591" t="n">
+        <v>-646860.8</v>
+      </c>
+      <c r="G591" t="n">
+        <v>0</v>
+      </c>
+      <c r="H591" t="n">
+        <v>139393331.983</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>4393566.397</v>
+      </c>
+      <c r="D592" t="n">
+        <v>0</v>
+      </c>
+      <c r="E592" t="n">
+        <v>0</v>
+      </c>
+      <c r="F592" t="n">
+        <v>0</v>
+      </c>
+      <c r="G592" t="n">
+        <v>-4945.7</v>
+      </c>
+      <c r="H592" t="n">
+        <v>4388620.697</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>24791930.336</v>
+      </c>
+      <c r="D593" t="n">
+        <v>0</v>
+      </c>
+      <c r="E593" t="n">
+        <v>302805.91</v>
+      </c>
+      <c r="F593" t="n">
+        <v>-302805.91</v>
+      </c>
+      <c r="G593" t="n">
+        <v>4945.7</v>
+      </c>
+      <c r="H593" t="n">
+        <v>24494070.126</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>0</v>
+      </c>
+      <c r="D594" t="n">
+        <v>0</v>
+      </c>
+      <c r="E594" t="n">
+        <v>0</v>
+      </c>
+      <c r="F594" t="n">
+        <v>0</v>
+      </c>
+      <c r="G594" t="n">
+        <v>0</v>
+      </c>
+      <c r="H594" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>0</v>
+      </c>
+      <c r="D595" t="n">
+        <v>0</v>
+      </c>
+      <c r="E595" t="n">
+        <v>0</v>
+      </c>
+      <c r="F595" t="n">
+        <v>0</v>
+      </c>
+      <c r="G595" t="n">
+        <v>0</v>
+      </c>
+      <c r="H595" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>582110.3370000001</v>
+      </c>
+      <c r="D596" t="n">
+        <v>0</v>
+      </c>
+      <c r="E596" t="n">
+        <v>0</v>
+      </c>
+      <c r="F596" t="n">
+        <v>0</v>
+      </c>
+      <c r="G596" t="n">
+        <v>0</v>
+      </c>
+      <c r="H596" t="n">
+        <v>582110.3370000001</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>945167.377</v>
+      </c>
+      <c r="D597" t="n">
+        <v>0</v>
+      </c>
+      <c r="E597" t="n">
+        <v>0</v>
+      </c>
+      <c r="F597" t="n">
+        <v>0</v>
+      </c>
+      <c r="G597" t="n">
+        <v>0</v>
+      </c>
+      <c r="H597" t="n">
+        <v>945167.377</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>5417618.057</v>
+      </c>
+      <c r="D598" t="n">
+        <v>0</v>
+      </c>
+      <c r="E598" t="n">
+        <v>0</v>
+      </c>
+      <c r="F598" t="n">
+        <v>0</v>
+      </c>
+      <c r="G598" t="n">
+        <v>0</v>
+      </c>
+      <c r="H598" t="n">
+        <v>5417618.057</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>7740765.443</v>
+      </c>
+      <c r="D599" t="n">
+        <v>0</v>
+      </c>
+      <c r="E599" t="n">
+        <v>0</v>
+      </c>
+      <c r="F599" t="n">
+        <v>0</v>
+      </c>
+      <c r="G599" t="n">
+        <v>0</v>
+      </c>
+      <c r="H599" t="n">
+        <v>7740765.443</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>5714749.7</v>
+      </c>
+      <c r="D600" t="n">
+        <v>0</v>
+      </c>
+      <c r="E600" t="n">
+        <v>0</v>
+      </c>
+      <c r="F600" t="n">
+        <v>0</v>
+      </c>
+      <c r="G600" t="n">
+        <v>0</v>
+      </c>
+      <c r="H600" t="n">
+        <v>5714749.7</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>2814557.93</v>
+      </c>
+      <c r="D601" t="n">
+        <v>0</v>
+      </c>
+      <c r="E601" t="n">
+        <v>0</v>
+      </c>
+      <c r="F601" t="n">
+        <v>0</v>
+      </c>
+      <c r="G601" t="n">
+        <v>0</v>
+      </c>
+      <c r="H601" t="n">
         <v>2814557.93</v>
       </c>
     </row>
@@ -16647,13 +17319,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1915100.608</v>
+        <v>1064402.578</v>
       </c>
       <c r="C2" t="n">
-        <v>22231922.592</v>
+        <v>22226973.992</v>
       </c>
       <c r="D2" t="n">
-        <v>24147023.2</v>
+        <v>23291376.57</v>
       </c>
     </row>
     <row r="3">
@@ -16663,13 +17335,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39171936.161</v>
+        <v>39141575.921</v>
       </c>
       <c r="C3" t="n">
         <v>11651846.571</v>
       </c>
       <c r="D3" t="n">
-        <v>50823782.732</v>
+        <v>50793422.492</v>
       </c>
     </row>
     <row r="4">
@@ -16679,13 +17351,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9294932.366</v>
+        <v>9078903.994999999</v>
       </c>
       <c r="C4" t="n">
         <v>11785958.483</v>
       </c>
       <c r="D4" t="n">
-        <v>21080890.849</v>
+        <v>20864862.478</v>
       </c>
     </row>
     <row r="5">
@@ -16695,13 +17367,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15512444.005</v>
+        <v>15518474.305</v>
       </c>
       <c r="C5" t="n">
         <v>1637870.342</v>
       </c>
       <c r="D5" t="n">
-        <v>17150314.347</v>
+        <v>17156344.647</v>
       </c>
     </row>
     <row r="6">
@@ -16727,13 +17399,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2800401.334</v>
+        <v>2705126.654</v>
       </c>
       <c r="C7" t="n">
         <v>178515.19</v>
       </c>
       <c r="D7" t="n">
-        <v>2978916.524</v>
+        <v>2883641.844</v>
       </c>
     </row>
     <row r="8">
@@ -16743,13 +17415,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>140040192.783</v>
+        <v>139393331.983</v>
       </c>
       <c r="C8" t="n">
         <v>11981013.97</v>
       </c>
       <c r="D8" t="n">
-        <v>152021206.753</v>
+        <v>151374345.953</v>
       </c>
     </row>
     <row r="9">
@@ -16759,13 +17431,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24791930.336</v>
+        <v>24494070.126</v>
       </c>
       <c r="C9" t="n">
-        <v>4393566.397</v>
+        <v>4388620.697</v>
       </c>
       <c r="D9" t="n">
-        <v>29185496.733</v>
+        <v>28882690.823</v>
       </c>
     </row>
     <row r="10">
@@ -16875,13 +17547,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>262770858.566</v>
+        <v>260639806.535</v>
       </c>
       <c r="C2" t="n">
-        <v>78952350.289</v>
+        <v>78942455.98899999</v>
       </c>
       <c r="D2" t="n">
-        <v>341723208.855</v>
+        <v>339582262.524</v>
       </c>
     </row>
     <row r="3">
@@ -16949,10 +17621,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1672190.88</v>
+        <v>2527837.51</v>
       </c>
       <c r="E8" t="n">
-        <v>1915100.608</v>
+        <v>1064402.578</v>
       </c>
     </row>
     <row r="9">
@@ -16973,7 +17645,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>22231922.592</v>
+        <v>22226973.992</v>
       </c>
     </row>
     <row r="10">
@@ -16991,10 +17663,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>4211214.911</v>
+        <v>4241575.151</v>
       </c>
       <c r="E10" t="n">
-        <v>39171936.161</v>
+        <v>39141575.921</v>
       </c>
     </row>
     <row r="11">
@@ -17033,10 +17705,10 @@
         <v>627861.84</v>
       </c>
       <c r="D12" t="n">
-        <v>3544668.306</v>
+        <v>3760696.678</v>
       </c>
       <c r="E12" t="n">
-        <v>9294932.366</v>
+        <v>9078903.994999999</v>
       </c>
     </row>
     <row r="13">
@@ -17072,13 +17744,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2789.9</v>
+        <v>8820.200000000001</v>
       </c>
       <c r="D14" t="n">
         <v>70273.08900000001</v>
       </c>
       <c r="E14" t="n">
-        <v>15512444.005</v>
+        <v>15518474.305</v>
       </c>
     </row>
     <row r="15">
@@ -17159,10 +17831,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>603511.95</v>
+        <v>698786.6299999999</v>
       </c>
       <c r="E18" t="n">
-        <v>2800401.334</v>
+        <v>2705126.654</v>
       </c>
     </row>
     <row r="19">
@@ -17201,10 +17873,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>773532.9000000001</v>
+        <v>1420393.7</v>
       </c>
       <c r="E20" t="n">
-        <v>140040192.783</v>
+        <v>139393331.983</v>
       </c>
     </row>
     <row r="21">
@@ -17243,10 +17915,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1162155.23</v>
+        <v>1464961.14</v>
       </c>
       <c r="E22" t="n">
-        <v>24791930.336</v>
+        <v>24494070.126</v>
       </c>
     </row>
     <row r="23">
@@ -17267,7 +17939,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4393566.397</v>
+        <v>4388620.697</v>
       </c>
     </row>
     <row r="24">

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H601"/>
+  <dimension ref="A1:H625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17273,6 +17273,678 @@
         <v>0</v>
       </c>
       <c r="H601" t="n">
+        <v>2814557.93</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>22226973.992</v>
+      </c>
+      <c r="D602" t="n">
+        <v>0</v>
+      </c>
+      <c r="E602" t="n">
+        <v>0</v>
+      </c>
+      <c r="F602" t="n">
+        <v>0</v>
+      </c>
+      <c r="G602" t="n">
+        <v>0</v>
+      </c>
+      <c r="H602" t="n">
+        <v>22226973.992</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>1064402.578</v>
+      </c>
+      <c r="D603" t="n">
+        <v>0</v>
+      </c>
+      <c r="E603" t="n">
+        <v>0</v>
+      </c>
+      <c r="F603" t="n">
+        <v>0</v>
+      </c>
+      <c r="G603" t="n">
+        <v>0</v>
+      </c>
+      <c r="H603" t="n">
+        <v>1064402.578</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>11651846.571</v>
+      </c>
+      <c r="D604" t="n">
+        <v>0</v>
+      </c>
+      <c r="E604" t="n">
+        <v>0</v>
+      </c>
+      <c r="F604" t="n">
+        <v>0</v>
+      </c>
+      <c r="G604" t="n">
+        <v>-24467.5</v>
+      </c>
+      <c r="H604" t="n">
+        <v>11627379.071</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>39141575.921</v>
+      </c>
+      <c r="D605" t="n">
+        <v>0</v>
+      </c>
+      <c r="E605" t="n">
+        <v>379199.63</v>
+      </c>
+      <c r="F605" t="n">
+        <v>-379199.63</v>
+      </c>
+      <c r="G605" t="n">
+        <v>24467.5</v>
+      </c>
+      <c r="H605" t="n">
+        <v>38786843.791</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>11785958.483</v>
+      </c>
+      <c r="D606" t="n">
+        <v>0</v>
+      </c>
+      <c r="E606" t="n">
+        <v>0</v>
+      </c>
+      <c r="F606" t="n">
+        <v>0</v>
+      </c>
+      <c r="G606" t="n">
+        <v>0</v>
+      </c>
+      <c r="H606" t="n">
+        <v>11785958.483</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>9078903.994999999</v>
+      </c>
+      <c r="D607" t="n">
+        <v>0</v>
+      </c>
+      <c r="E607" t="n">
+        <v>10191.61</v>
+      </c>
+      <c r="F607" t="n">
+        <v>-10191.61</v>
+      </c>
+      <c r="G607" t="n">
+        <v>0</v>
+      </c>
+      <c r="H607" t="n">
+        <v>9068712.385</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D608" t="n">
+        <v>0</v>
+      </c>
+      <c r="E608" t="n">
+        <v>0</v>
+      </c>
+      <c r="F608" t="n">
+        <v>0</v>
+      </c>
+      <c r="G608" t="n">
+        <v>0</v>
+      </c>
+      <c r="H608" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>15518474.305</v>
+      </c>
+      <c r="D609" t="n">
+        <v>0</v>
+      </c>
+      <c r="E609" t="n">
+        <v>0</v>
+      </c>
+      <c r="F609" t="n">
+        <v>0</v>
+      </c>
+      <c r="G609" t="n">
+        <v>0</v>
+      </c>
+      <c r="H609" t="n">
+        <v>15518474.305</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>3377178.65</v>
+      </c>
+      <c r="D610" t="n">
+        <v>0</v>
+      </c>
+      <c r="E610" t="n">
+        <v>0</v>
+      </c>
+      <c r="F610" t="n">
+        <v>0</v>
+      </c>
+      <c r="G610" t="n">
+        <v>0</v>
+      </c>
+      <c r="H610" t="n">
+        <v>3377178.65</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>17743430.223</v>
+      </c>
+      <c r="D611" t="n">
+        <v>0</v>
+      </c>
+      <c r="E611" t="n">
+        <v>0</v>
+      </c>
+      <c r="F611" t="n">
+        <v>0</v>
+      </c>
+      <c r="G611" t="n">
+        <v>0</v>
+      </c>
+      <c r="H611" t="n">
+        <v>17743430.223</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>178515.19</v>
+      </c>
+      <c r="D612" t="n">
+        <v>0</v>
+      </c>
+      <c r="E612" t="n">
+        <v>0</v>
+      </c>
+      <c r="F612" t="n">
+        <v>0</v>
+      </c>
+      <c r="G612" t="n">
+        <v>0</v>
+      </c>
+      <c r="H612" t="n">
+        <v>178515.19</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>2705126.654</v>
+      </c>
+      <c r="D613" t="n">
+        <v>0</v>
+      </c>
+      <c r="E613" t="n">
+        <v>0</v>
+      </c>
+      <c r="F613" t="n">
+        <v>0</v>
+      </c>
+      <c r="G613" t="n">
+        <v>0</v>
+      </c>
+      <c r="H613" t="n">
+        <v>2705126.654</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D614" t="n">
+        <v>0</v>
+      </c>
+      <c r="E614" t="n">
+        <v>0</v>
+      </c>
+      <c r="F614" t="n">
+        <v>0</v>
+      </c>
+      <c r="G614" t="n">
+        <v>0</v>
+      </c>
+      <c r="H614" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>139393331.983</v>
+      </c>
+      <c r="D615" t="n">
+        <v>0</v>
+      </c>
+      <c r="E615" t="n">
+        <v>1300178.3</v>
+      </c>
+      <c r="F615" t="n">
+        <v>-1300178.3</v>
+      </c>
+      <c r="G615" t="n">
+        <v>0</v>
+      </c>
+      <c r="H615" t="n">
+        <v>138093153.683</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>4388620.697</v>
+      </c>
+      <c r="D616" t="n">
+        <v>0</v>
+      </c>
+      <c r="E616" t="n">
+        <v>0</v>
+      </c>
+      <c r="F616" t="n">
+        <v>0</v>
+      </c>
+      <c r="G616" t="n">
+        <v>-14620.62</v>
+      </c>
+      <c r="H616" t="n">
+        <v>4374000.077</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>24494070.126</v>
+      </c>
+      <c r="D617" t="n">
+        <v>0</v>
+      </c>
+      <c r="E617" t="n">
+        <v>0</v>
+      </c>
+      <c r="F617" t="n">
+        <v>0</v>
+      </c>
+      <c r="G617" t="n">
+        <v>14620.62</v>
+      </c>
+      <c r="H617" t="n">
+        <v>24508690.746</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>0</v>
+      </c>
+      <c r="D618" t="n">
+        <v>0</v>
+      </c>
+      <c r="E618" t="n">
+        <v>0</v>
+      </c>
+      <c r="F618" t="n">
+        <v>0</v>
+      </c>
+      <c r="G618" t="n">
+        <v>0</v>
+      </c>
+      <c r="H618" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>0</v>
+      </c>
+      <c r="D619" t="n">
+        <v>0</v>
+      </c>
+      <c r="E619" t="n">
+        <v>0</v>
+      </c>
+      <c r="F619" t="n">
+        <v>0</v>
+      </c>
+      <c r="G619" t="n">
+        <v>0</v>
+      </c>
+      <c r="H619" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>582110.3370000001</v>
+      </c>
+      <c r="D620" t="n">
+        <v>0</v>
+      </c>
+      <c r="E620" t="n">
+        <v>0</v>
+      </c>
+      <c r="F620" t="n">
+        <v>0</v>
+      </c>
+      <c r="G620" t="n">
+        <v>0</v>
+      </c>
+      <c r="H620" t="n">
+        <v>582110.3370000001</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>945167.377</v>
+      </c>
+      <c r="D621" t="n">
+        <v>0</v>
+      </c>
+      <c r="E621" t="n">
+        <v>0</v>
+      </c>
+      <c r="F621" t="n">
+        <v>0</v>
+      </c>
+      <c r="G621" t="n">
+        <v>0</v>
+      </c>
+      <c r="H621" t="n">
+        <v>945167.377</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>5417618.057</v>
+      </c>
+      <c r="D622" t="n">
+        <v>0</v>
+      </c>
+      <c r="E622" t="n">
+        <v>0</v>
+      </c>
+      <c r="F622" t="n">
+        <v>0</v>
+      </c>
+      <c r="G622" t="n">
+        <v>0</v>
+      </c>
+      <c r="H622" t="n">
+        <v>5417618.057</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>7740765.443</v>
+      </c>
+      <c r="D623" t="n">
+        <v>0</v>
+      </c>
+      <c r="E623" t="n">
+        <v>0</v>
+      </c>
+      <c r="F623" t="n">
+        <v>0</v>
+      </c>
+      <c r="G623" t="n">
+        <v>0</v>
+      </c>
+      <c r="H623" t="n">
+        <v>7740765.443</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>5714749.7</v>
+      </c>
+      <c r="D624" t="n">
+        <v>0</v>
+      </c>
+      <c r="E624" t="n">
+        <v>0</v>
+      </c>
+      <c r="F624" t="n">
+        <v>0</v>
+      </c>
+      <c r="G624" t="n">
+        <v>0</v>
+      </c>
+      <c r="H624" t="n">
+        <v>5714749.7</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>2814557.93</v>
+      </c>
+      <c r="D625" t="n">
+        <v>0</v>
+      </c>
+      <c r="E625" t="n">
+        <v>0</v>
+      </c>
+      <c r="F625" t="n">
+        <v>0</v>
+      </c>
+      <c r="G625" t="n">
+        <v>0</v>
+      </c>
+      <c r="H625" t="n">
         <v>2814557.93</v>
       </c>
     </row>
@@ -17335,13 +18007,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39141575.921</v>
+        <v>38786843.791</v>
       </c>
       <c r="C3" t="n">
-        <v>11651846.571</v>
+        <v>11627379.071</v>
       </c>
       <c r="D3" t="n">
-        <v>50793422.492</v>
+        <v>50414222.862</v>
       </c>
     </row>
     <row r="4">
@@ -17351,13 +18023,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9078903.994999999</v>
+        <v>9068712.385</v>
       </c>
       <c r="C4" t="n">
         <v>11785958.483</v>
       </c>
       <c r="D4" t="n">
-        <v>20864862.478</v>
+        <v>20854670.868</v>
       </c>
     </row>
     <row r="5">
@@ -17415,13 +18087,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>139393331.983</v>
+        <v>138093153.683</v>
       </c>
       <c r="C8" t="n">
         <v>11981013.97</v>
       </c>
       <c r="D8" t="n">
-        <v>151374345.953</v>
+        <v>150074167.653</v>
       </c>
     </row>
     <row r="9">
@@ -17431,10 +18103,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24494070.126</v>
+        <v>24508690.746</v>
       </c>
       <c r="C9" t="n">
-        <v>4388620.697</v>
+        <v>4374000.077</v>
       </c>
       <c r="D9" t="n">
         <v>28882690.823</v>
@@ -17547,13 +18219,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>260639806.535</v>
+        <v>258989325.115</v>
       </c>
       <c r="C2" t="n">
-        <v>78942455.98899999</v>
+        <v>78903367.869</v>
       </c>
       <c r="D2" t="n">
-        <v>339582262.524</v>
+        <v>337892692.984</v>
       </c>
     </row>
     <row r="3">
@@ -17663,10 +18335,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>4241575.151</v>
+        <v>4620774.780999999</v>
       </c>
       <c r="E10" t="n">
-        <v>39141575.921</v>
+        <v>38786843.791</v>
       </c>
     </row>
     <row r="11">
@@ -17687,7 +18359,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>11651846.571</v>
+        <v>11627379.071</v>
       </c>
     </row>
     <row r="12">
@@ -17705,10 +18377,10 @@
         <v>627861.84</v>
       </c>
       <c r="D12" t="n">
-        <v>3760696.678</v>
+        <v>3770888.288</v>
       </c>
       <c r="E12" t="n">
-        <v>9078903.994999999</v>
+        <v>9068712.385</v>
       </c>
     </row>
     <row r="13">
@@ -17873,10 +18545,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1420393.7</v>
+        <v>2720572</v>
       </c>
       <c r="E20" t="n">
-        <v>139393331.983</v>
+        <v>138093153.683</v>
       </c>
     </row>
     <row r="21">
@@ -17918,7 +18590,7 @@
         <v>1464961.14</v>
       </c>
       <c r="E22" t="n">
-        <v>24494070.126</v>
+        <v>24508690.746</v>
       </c>
     </row>
     <row r="23">
@@ -17939,7 +18611,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4388620.697</v>
+        <v>4374000.077</v>
       </c>
     </row>
     <row r="24">

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H625"/>
+  <dimension ref="A1:H649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17946,6 +17946,678 @@
       </c>
       <c r="H625" t="n">
         <v>2814557.93</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>22226973.992</v>
+      </c>
+      <c r="D626" t="n">
+        <v>0</v>
+      </c>
+      <c r="E626" t="n">
+        <v>0</v>
+      </c>
+      <c r="F626" t="n">
+        <v>0</v>
+      </c>
+      <c r="G626" t="n">
+        <v>0</v>
+      </c>
+      <c r="H626" t="n">
+        <v>22226973.992</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>1064402.578</v>
+      </c>
+      <c r="D627" t="n">
+        <v>0</v>
+      </c>
+      <c r="E627" t="n">
+        <v>0</v>
+      </c>
+      <c r="F627" t="n">
+        <v>0</v>
+      </c>
+      <c r="G627" t="n">
+        <v>0</v>
+      </c>
+      <c r="H627" t="n">
+        <v>1064402.578</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>11627379.071</v>
+      </c>
+      <c r="D628" t="n">
+        <v>0</v>
+      </c>
+      <c r="E628" t="n">
+        <v>0</v>
+      </c>
+      <c r="F628" t="n">
+        <v>0</v>
+      </c>
+      <c r="G628" t="n">
+        <v>0</v>
+      </c>
+      <c r="H628" t="n">
+        <v>11627379.071</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>38786843.791</v>
+      </c>
+      <c r="D629" t="n">
+        <v>0</v>
+      </c>
+      <c r="E629" t="n">
+        <v>0</v>
+      </c>
+      <c r="F629" t="n">
+        <v>0</v>
+      </c>
+      <c r="G629" t="n">
+        <v>0</v>
+      </c>
+      <c r="H629" t="n">
+        <v>38786843.791</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>11785958.483</v>
+      </c>
+      <c r="D630" t="n">
+        <v>0</v>
+      </c>
+      <c r="E630" t="n">
+        <v>0</v>
+      </c>
+      <c r="F630" t="n">
+        <v>0</v>
+      </c>
+      <c r="G630" t="n">
+        <v>0</v>
+      </c>
+      <c r="H630" t="n">
+        <v>11785958.483</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>9068712.385</v>
+      </c>
+      <c r="D631" t="n">
+        <v>0</v>
+      </c>
+      <c r="E631" t="n">
+        <v>0</v>
+      </c>
+      <c r="F631" t="n">
+        <v>0</v>
+      </c>
+      <c r="G631" t="n">
+        <v>0</v>
+      </c>
+      <c r="H631" t="n">
+        <v>9068712.385</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D632" t="n">
+        <v>0</v>
+      </c>
+      <c r="E632" t="n">
+        <v>0</v>
+      </c>
+      <c r="F632" t="n">
+        <v>0</v>
+      </c>
+      <c r="G632" t="n">
+        <v>0</v>
+      </c>
+      <c r="H632" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>15518474.305</v>
+      </c>
+      <c r="D633" t="n">
+        <v>0</v>
+      </c>
+      <c r="E633" t="n">
+        <v>0</v>
+      </c>
+      <c r="F633" t="n">
+        <v>0</v>
+      </c>
+      <c r="G633" t="n">
+        <v>0</v>
+      </c>
+      <c r="H633" t="n">
+        <v>15518474.305</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>3377178.65</v>
+      </c>
+      <c r="D634" t="n">
+        <v>0</v>
+      </c>
+      <c r="E634" t="n">
+        <v>0</v>
+      </c>
+      <c r="F634" t="n">
+        <v>0</v>
+      </c>
+      <c r="G634" t="n">
+        <v>0</v>
+      </c>
+      <c r="H634" t="n">
+        <v>3377178.65</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>17743430.223</v>
+      </c>
+      <c r="D635" t="n">
+        <v>0</v>
+      </c>
+      <c r="E635" t="n">
+        <v>19930.44</v>
+      </c>
+      <c r="F635" t="n">
+        <v>-19930.44</v>
+      </c>
+      <c r="G635" t="n">
+        <v>0</v>
+      </c>
+      <c r="H635" t="n">
+        <v>17723499.783</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>178515.19</v>
+      </c>
+      <c r="D636" t="n">
+        <v>0</v>
+      </c>
+      <c r="E636" t="n">
+        <v>0</v>
+      </c>
+      <c r="F636" t="n">
+        <v>0</v>
+      </c>
+      <c r="G636" t="n">
+        <v>0</v>
+      </c>
+      <c r="H636" t="n">
+        <v>178515.19</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>2705126.654</v>
+      </c>
+      <c r="D637" t="n">
+        <v>0</v>
+      </c>
+      <c r="E637" t="n">
+        <v>0</v>
+      </c>
+      <c r="F637" t="n">
+        <v>0</v>
+      </c>
+      <c r="G637" t="n">
+        <v>0</v>
+      </c>
+      <c r="H637" t="n">
+        <v>2705126.654</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D638" t="n">
+        <v>0</v>
+      </c>
+      <c r="E638" t="n">
+        <v>0</v>
+      </c>
+      <c r="F638" t="n">
+        <v>0</v>
+      </c>
+      <c r="G638" t="n">
+        <v>0</v>
+      </c>
+      <c r="H638" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>138093153.683</v>
+      </c>
+      <c r="D639" t="n">
+        <v>0</v>
+      </c>
+      <c r="E639" t="n">
+        <v>1611910.2</v>
+      </c>
+      <c r="F639" t="n">
+        <v>-1611910.2</v>
+      </c>
+      <c r="G639" t="n">
+        <v>0</v>
+      </c>
+      <c r="H639" t="n">
+        <v>136481243.483</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>4374000.077</v>
+      </c>
+      <c r="D640" t="n">
+        <v>0</v>
+      </c>
+      <c r="E640" t="n">
+        <v>0</v>
+      </c>
+      <c r="F640" t="n">
+        <v>0</v>
+      </c>
+      <c r="G640" t="n">
+        <v>0</v>
+      </c>
+      <c r="H640" t="n">
+        <v>4374000.077</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>24508690.746</v>
+      </c>
+      <c r="D641" t="n">
+        <v>0</v>
+      </c>
+      <c r="E641" t="n">
+        <v>0</v>
+      </c>
+      <c r="F641" t="n">
+        <v>0</v>
+      </c>
+      <c r="G641" t="n">
+        <v>0</v>
+      </c>
+      <c r="H641" t="n">
+        <v>24508690.746</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>0</v>
+      </c>
+      <c r="D642" t="n">
+        <v>0</v>
+      </c>
+      <c r="E642" t="n">
+        <v>0</v>
+      </c>
+      <c r="F642" t="n">
+        <v>0</v>
+      </c>
+      <c r="G642" t="n">
+        <v>0</v>
+      </c>
+      <c r="H642" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>0</v>
+      </c>
+      <c r="D643" t="n">
+        <v>0</v>
+      </c>
+      <c r="E643" t="n">
+        <v>0</v>
+      </c>
+      <c r="F643" t="n">
+        <v>0</v>
+      </c>
+      <c r="G643" t="n">
+        <v>0</v>
+      </c>
+      <c r="H643" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>582110.3370000001</v>
+      </c>
+      <c r="D644" t="n">
+        <v>0</v>
+      </c>
+      <c r="E644" t="n">
+        <v>0</v>
+      </c>
+      <c r="F644" t="n">
+        <v>0</v>
+      </c>
+      <c r="G644" t="n">
+        <v>0</v>
+      </c>
+      <c r="H644" t="n">
+        <v>582110.3370000001</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>945167.377</v>
+      </c>
+      <c r="D645" t="n">
+        <v>0</v>
+      </c>
+      <c r="E645" t="n">
+        <v>0</v>
+      </c>
+      <c r="F645" t="n">
+        <v>0</v>
+      </c>
+      <c r="G645" t="n">
+        <v>0</v>
+      </c>
+      <c r="H645" t="n">
+        <v>945167.377</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>5417618.057</v>
+      </c>
+      <c r="D646" t="n">
+        <v>0</v>
+      </c>
+      <c r="E646" t="n">
+        <v>0</v>
+      </c>
+      <c r="F646" t="n">
+        <v>0</v>
+      </c>
+      <c r="G646" t="n">
+        <v>0</v>
+      </c>
+      <c r="H646" t="n">
+        <v>5417618.057</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>7740765.443</v>
+      </c>
+      <c r="D647" t="n">
+        <v>0</v>
+      </c>
+      <c r="E647" t="n">
+        <v>0</v>
+      </c>
+      <c r="F647" t="n">
+        <v>0</v>
+      </c>
+      <c r="G647" t="n">
+        <v>0</v>
+      </c>
+      <c r="H647" t="n">
+        <v>7740765.443</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>5714749.7</v>
+      </c>
+      <c r="D648" t="n">
+        <v>0</v>
+      </c>
+      <c r="E648" t="n">
+        <v>0</v>
+      </c>
+      <c r="F648" t="n">
+        <v>0</v>
+      </c>
+      <c r="G648" t="n">
+        <v>0</v>
+      </c>
+      <c r="H648" t="n">
+        <v>5714749.7</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>2814557.93</v>
+      </c>
+      <c r="D649" t="n">
+        <v>0</v>
+      </c>
+      <c r="E649" t="n">
+        <v>1185217.24</v>
+      </c>
+      <c r="F649" t="n">
+        <v>-1185217.24</v>
+      </c>
+      <c r="G649" t="n">
+        <v>0</v>
+      </c>
+      <c r="H649" t="n">
+        <v>1629340.69</v>
       </c>
     </row>
   </sheetData>
@@ -18055,13 +18727,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17743430.223</v>
+        <v>17723499.783</v>
       </c>
       <c r="C6" t="n">
         <v>3377178.65</v>
       </c>
       <c r="D6" t="n">
-        <v>21120608.873</v>
+        <v>21100678.433</v>
       </c>
     </row>
     <row r="7">
@@ -18087,13 +18759,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>138093153.683</v>
+        <v>136481243.483</v>
       </c>
       <c r="C8" t="n">
         <v>11981013.97</v>
       </c>
       <c r="D8" t="n">
-        <v>150074167.653</v>
+        <v>148462257.453</v>
       </c>
     </row>
     <row r="9">
@@ -18167,13 +18839,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2814557.93</v>
+        <v>1629340.69</v>
       </c>
       <c r="C13" t="n">
         <v>5714749.7</v>
       </c>
       <c r="D13" t="n">
-        <v>8529307.630000001</v>
+        <v>7344090.390000001</v>
       </c>
     </row>
   </sheetData>
@@ -18219,13 +18891,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>258989325.115</v>
+        <v>256172267.235</v>
       </c>
       <c r="C2" t="n">
         <v>78903367.869</v>
       </c>
       <c r="D2" t="n">
-        <v>337892692.984</v>
+        <v>335075635.104</v>
       </c>
     </row>
     <row r="3">
@@ -18461,10 +19133,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>31267.17</v>
+        <v>51197.61</v>
       </c>
       <c r="E16" t="n">
-        <v>17743430.223</v>
+        <v>17723499.783</v>
       </c>
     </row>
     <row r="17">
@@ -18545,10 +19217,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2720572</v>
+        <v>4332482.2</v>
       </c>
       <c r="E20" t="n">
-        <v>138093153.683</v>
+        <v>136481243.483</v>
       </c>
     </row>
     <row r="21">
@@ -18755,10 +19427,10 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>161200.68</v>
+        <v>1346417.92</v>
       </c>
       <c r="E30" t="n">
-        <v>2814557.93</v>
+        <v>1629340.69</v>
       </c>
     </row>
     <row r="31">

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H649"/>
+  <dimension ref="A1:H673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18618,6 +18618,678 @@
       </c>
       <c r="H649" t="n">
         <v>1629340.69</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>22226973.992</v>
+      </c>
+      <c r="D650" t="n">
+        <v>0</v>
+      </c>
+      <c r="E650" t="n">
+        <v>0</v>
+      </c>
+      <c r="F650" t="n">
+        <v>0</v>
+      </c>
+      <c r="G650" t="n">
+        <v>0</v>
+      </c>
+      <c r="H650" t="n">
+        <v>22226973.992</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>1064402.578</v>
+      </c>
+      <c r="D651" t="n">
+        <v>0</v>
+      </c>
+      <c r="E651" t="n">
+        <v>0</v>
+      </c>
+      <c r="F651" t="n">
+        <v>0</v>
+      </c>
+      <c r="G651" t="n">
+        <v>0</v>
+      </c>
+      <c r="H651" t="n">
+        <v>1064402.578</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>11627379.071</v>
+      </c>
+      <c r="D652" t="n">
+        <v>0</v>
+      </c>
+      <c r="E652" t="n">
+        <v>0</v>
+      </c>
+      <c r="F652" t="n">
+        <v>0</v>
+      </c>
+      <c r="G652" t="n">
+        <v>0</v>
+      </c>
+      <c r="H652" t="n">
+        <v>11627379.071</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>38786843.791</v>
+      </c>
+      <c r="D653" t="n">
+        <v>0</v>
+      </c>
+      <c r="E653" t="n">
+        <v>0</v>
+      </c>
+      <c r="F653" t="n">
+        <v>0</v>
+      </c>
+      <c r="G653" t="n">
+        <v>0</v>
+      </c>
+      <c r="H653" t="n">
+        <v>38786843.791</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>11785958.483</v>
+      </c>
+      <c r="D654" t="n">
+        <v>0</v>
+      </c>
+      <c r="E654" t="n">
+        <v>0</v>
+      </c>
+      <c r="F654" t="n">
+        <v>0</v>
+      </c>
+      <c r="G654" t="n">
+        <v>0</v>
+      </c>
+      <c r="H654" t="n">
+        <v>11785958.483</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>9068712.385</v>
+      </c>
+      <c r="D655" t="n">
+        <v>0</v>
+      </c>
+      <c r="E655" t="n">
+        <v>0</v>
+      </c>
+      <c r="F655" t="n">
+        <v>0</v>
+      </c>
+      <c r="G655" t="n">
+        <v>0</v>
+      </c>
+      <c r="H655" t="n">
+        <v>9068712.385</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D656" t="n">
+        <v>0</v>
+      </c>
+      <c r="E656" t="n">
+        <v>0</v>
+      </c>
+      <c r="F656" t="n">
+        <v>0</v>
+      </c>
+      <c r="G656" t="n">
+        <v>0</v>
+      </c>
+      <c r="H656" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>15518474.305</v>
+      </c>
+      <c r="D657" t="n">
+        <v>0</v>
+      </c>
+      <c r="E657" t="n">
+        <v>995</v>
+      </c>
+      <c r="F657" t="n">
+        <v>-995</v>
+      </c>
+      <c r="G657" t="n">
+        <v>0</v>
+      </c>
+      <c r="H657" t="n">
+        <v>15517479.305</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>3377178.65</v>
+      </c>
+      <c r="D658" t="n">
+        <v>0</v>
+      </c>
+      <c r="E658" t="n">
+        <v>0</v>
+      </c>
+      <c r="F658" t="n">
+        <v>0</v>
+      </c>
+      <c r="G658" t="n">
+        <v>0</v>
+      </c>
+      <c r="H658" t="n">
+        <v>3377178.65</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>17723499.783</v>
+      </c>
+      <c r="D659" t="n">
+        <v>0</v>
+      </c>
+      <c r="E659" t="n">
+        <v>0</v>
+      </c>
+      <c r="F659" t="n">
+        <v>0</v>
+      </c>
+      <c r="G659" t="n">
+        <v>0</v>
+      </c>
+      <c r="H659" t="n">
+        <v>17723499.783</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>178515.19</v>
+      </c>
+      <c r="D660" t="n">
+        <v>0</v>
+      </c>
+      <c r="E660" t="n">
+        <v>0</v>
+      </c>
+      <c r="F660" t="n">
+        <v>0</v>
+      </c>
+      <c r="G660" t="n">
+        <v>0</v>
+      </c>
+      <c r="H660" t="n">
+        <v>178515.19</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>2705126.654</v>
+      </c>
+      <c r="D661" t="n">
+        <v>0</v>
+      </c>
+      <c r="E661" t="n">
+        <v>0</v>
+      </c>
+      <c r="F661" t="n">
+        <v>0</v>
+      </c>
+      <c r="G661" t="n">
+        <v>0</v>
+      </c>
+      <c r="H661" t="n">
+        <v>2705126.654</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D662" t="n">
+        <v>0</v>
+      </c>
+      <c r="E662" t="n">
+        <v>0</v>
+      </c>
+      <c r="F662" t="n">
+        <v>0</v>
+      </c>
+      <c r="G662" t="n">
+        <v>0</v>
+      </c>
+      <c r="H662" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>136481243.483</v>
+      </c>
+      <c r="D663" t="n">
+        <v>0</v>
+      </c>
+      <c r="E663" t="n">
+        <v>948163.9</v>
+      </c>
+      <c r="F663" t="n">
+        <v>-948163.9</v>
+      </c>
+      <c r="G663" t="n">
+        <v>0</v>
+      </c>
+      <c r="H663" t="n">
+        <v>135533079.583</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>4374000.077</v>
+      </c>
+      <c r="D664" t="n">
+        <v>10008.94</v>
+      </c>
+      <c r="E664" t="n">
+        <v>0</v>
+      </c>
+      <c r="F664" t="n">
+        <v>10008.94</v>
+      </c>
+      <c r="G664" t="n">
+        <v>0</v>
+      </c>
+      <c r="H664" t="n">
+        <v>4384009.017</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>24508690.746</v>
+      </c>
+      <c r="D665" t="n">
+        <v>0</v>
+      </c>
+      <c r="E665" t="n">
+        <v>0</v>
+      </c>
+      <c r="F665" t="n">
+        <v>0</v>
+      </c>
+      <c r="G665" t="n">
+        <v>0</v>
+      </c>
+      <c r="H665" t="n">
+        <v>24508690.746</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>0</v>
+      </c>
+      <c r="D666" t="n">
+        <v>0</v>
+      </c>
+      <c r="E666" t="n">
+        <v>0</v>
+      </c>
+      <c r="F666" t="n">
+        <v>0</v>
+      </c>
+      <c r="G666" t="n">
+        <v>0</v>
+      </c>
+      <c r="H666" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>0</v>
+      </c>
+      <c r="D667" t="n">
+        <v>0</v>
+      </c>
+      <c r="E667" t="n">
+        <v>0</v>
+      </c>
+      <c r="F667" t="n">
+        <v>0</v>
+      </c>
+      <c r="G667" t="n">
+        <v>0</v>
+      </c>
+      <c r="H667" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>582110.3370000001</v>
+      </c>
+      <c r="D668" t="n">
+        <v>0</v>
+      </c>
+      <c r="E668" t="n">
+        <v>0</v>
+      </c>
+      <c r="F668" t="n">
+        <v>0</v>
+      </c>
+      <c r="G668" t="n">
+        <v>0</v>
+      </c>
+      <c r="H668" t="n">
+        <v>582110.3370000001</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>945167.377</v>
+      </c>
+      <c r="D669" t="n">
+        <v>0</v>
+      </c>
+      <c r="E669" t="n">
+        <v>0</v>
+      </c>
+      <c r="F669" t="n">
+        <v>0</v>
+      </c>
+      <c r="G669" t="n">
+        <v>0</v>
+      </c>
+      <c r="H669" t="n">
+        <v>945167.377</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>5417618.057</v>
+      </c>
+      <c r="D670" t="n">
+        <v>0</v>
+      </c>
+      <c r="E670" t="n">
+        <v>0</v>
+      </c>
+      <c r="F670" t="n">
+        <v>0</v>
+      </c>
+      <c r="G670" t="n">
+        <v>0</v>
+      </c>
+      <c r="H670" t="n">
+        <v>5417618.057</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>7740765.443</v>
+      </c>
+      <c r="D671" t="n">
+        <v>0</v>
+      </c>
+      <c r="E671" t="n">
+        <v>0</v>
+      </c>
+      <c r="F671" t="n">
+        <v>0</v>
+      </c>
+      <c r="G671" t="n">
+        <v>0</v>
+      </c>
+      <c r="H671" t="n">
+        <v>7740765.443</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>5714749.7</v>
+      </c>
+      <c r="D672" t="n">
+        <v>498343.66</v>
+      </c>
+      <c r="E672" t="n">
+        <v>0</v>
+      </c>
+      <c r="F672" t="n">
+        <v>498343.66</v>
+      </c>
+      <c r="G672" t="n">
+        <v>0</v>
+      </c>
+      <c r="H672" t="n">
+        <v>6213093.36</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>1629340.69</v>
+      </c>
+      <c r="D673" t="n">
+        <v>49889.64</v>
+      </c>
+      <c r="E673" t="n">
+        <v>0</v>
+      </c>
+      <c r="F673" t="n">
+        <v>49889.64</v>
+      </c>
+      <c r="G673" t="n">
+        <v>0</v>
+      </c>
+      <c r="H673" t="n">
+        <v>1679230.33</v>
       </c>
     </row>
   </sheetData>
@@ -18711,13 +19383,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15518474.305</v>
+        <v>15517479.305</v>
       </c>
       <c r="C5" t="n">
         <v>1637870.342</v>
       </c>
       <c r="D5" t="n">
-        <v>17156344.647</v>
+        <v>17155349.647</v>
       </c>
     </row>
     <row r="6">
@@ -18759,13 +19431,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>136481243.483</v>
+        <v>135533079.583</v>
       </c>
       <c r="C8" t="n">
         <v>11981013.97</v>
       </c>
       <c r="D8" t="n">
-        <v>148462257.453</v>
+        <v>147514093.553</v>
       </c>
     </row>
     <row r="9">
@@ -18778,10 +19450,10 @@
         <v>24508690.746</v>
       </c>
       <c r="C9" t="n">
-        <v>4374000.077</v>
+        <v>4384009.017</v>
       </c>
       <c r="D9" t="n">
-        <v>28882690.823</v>
+        <v>28892699.763</v>
       </c>
     </row>
     <row r="10">
@@ -18839,13 +19511,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1629340.69</v>
+        <v>1679230.33</v>
       </c>
       <c r="C13" t="n">
-        <v>5714749.7</v>
+        <v>6213093.36</v>
       </c>
       <c r="D13" t="n">
-        <v>7344090.390000001</v>
+        <v>7892323.69</v>
       </c>
     </row>
   </sheetData>
@@ -18891,13 +19563,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>256172267.235</v>
+        <v>255272997.975</v>
       </c>
       <c r="C2" t="n">
-        <v>78903367.869</v>
+        <v>79411720.469</v>
       </c>
       <c r="D2" t="n">
-        <v>335075635.104</v>
+        <v>334684718.444</v>
       </c>
     </row>
     <row r="3">
@@ -19091,10 +19763,10 @@
         <v>8820.200000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>70273.08900000001</v>
+        <v>71268.08900000001</v>
       </c>
       <c r="E14" t="n">
-        <v>15518474.305</v>
+        <v>15517479.305</v>
       </c>
     </row>
     <row r="15">
@@ -19217,10 +19889,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>4332482.2</v>
+        <v>5280646.100000001</v>
       </c>
       <c r="E20" t="n">
-        <v>136481243.483</v>
+        <v>135533079.583</v>
       </c>
     </row>
     <row r="21">
@@ -19277,13 +19949,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>10008.94</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4374000.077</v>
+        <v>4384009.017</v>
       </c>
     </row>
     <row r="24">
@@ -19424,13 +20096,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>49889.64</v>
       </c>
       <c r="D30" t="n">
         <v>1346417.92</v>
       </c>
       <c r="E30" t="n">
-        <v>1629340.69</v>
+        <v>1679230.33</v>
       </c>
     </row>
     <row r="31">
@@ -19445,13 +20117,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>630063.0600000001</v>
+        <v>1128406.72</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>5714749.7</v>
+        <v>6213093.36</v>
       </c>
     </row>
     <row r="32">

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H673"/>
+  <dimension ref="A1:H697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19290,6 +19290,678 @@
       </c>
       <c r="H673" t="n">
         <v>1679230.33</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>22226973.992</v>
+      </c>
+      <c r="D674" t="n">
+        <v>0</v>
+      </c>
+      <c r="E674" t="n">
+        <v>0</v>
+      </c>
+      <c r="F674" t="n">
+        <v>0</v>
+      </c>
+      <c r="G674" t="n">
+        <v>-102298.7</v>
+      </c>
+      <c r="H674" t="n">
+        <v>22124675.292</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>1064402.578</v>
+      </c>
+      <c r="D675" t="n">
+        <v>0</v>
+      </c>
+      <c r="E675" t="n">
+        <v>0</v>
+      </c>
+      <c r="F675" t="n">
+        <v>0</v>
+      </c>
+      <c r="G675" t="n">
+        <v>102298.7</v>
+      </c>
+      <c r="H675" t="n">
+        <v>1166701.278</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>11627379.071</v>
+      </c>
+      <c r="D676" t="n">
+        <v>0</v>
+      </c>
+      <c r="E676" t="n">
+        <v>0</v>
+      </c>
+      <c r="F676" t="n">
+        <v>0</v>
+      </c>
+      <c r="G676" t="n">
+        <v>0</v>
+      </c>
+      <c r="H676" t="n">
+        <v>11627379.071</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>38786843.791</v>
+      </c>
+      <c r="D677" t="n">
+        <v>0</v>
+      </c>
+      <c r="E677" t="n">
+        <v>616162.834</v>
+      </c>
+      <c r="F677" t="n">
+        <v>-616162.834</v>
+      </c>
+      <c r="G677" t="n">
+        <v>0</v>
+      </c>
+      <c r="H677" t="n">
+        <v>38170680.957</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>11785958.483</v>
+      </c>
+      <c r="D678" t="n">
+        <v>0</v>
+      </c>
+      <c r="E678" t="n">
+        <v>0</v>
+      </c>
+      <c r="F678" t="n">
+        <v>0</v>
+      </c>
+      <c r="G678" t="n">
+        <v>-40932.5</v>
+      </c>
+      <c r="H678" t="n">
+        <v>11745025.983</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>9068712.385</v>
+      </c>
+      <c r="D679" t="n">
+        <v>40890.85</v>
+      </c>
+      <c r="E679" t="n">
+        <v>0</v>
+      </c>
+      <c r="F679" t="n">
+        <v>40890.85</v>
+      </c>
+      <c r="G679" t="n">
+        <v>40932.5</v>
+      </c>
+      <c r="H679" t="n">
+        <v>9150535.734999999</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D680" t="n">
+        <v>0</v>
+      </c>
+      <c r="E680" t="n">
+        <v>0</v>
+      </c>
+      <c r="F680" t="n">
+        <v>0</v>
+      </c>
+      <c r="G680" t="n">
+        <v>0</v>
+      </c>
+      <c r="H680" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>15517479.305</v>
+      </c>
+      <c r="D681" t="n">
+        <v>0</v>
+      </c>
+      <c r="E681" t="n">
+        <v>969.9</v>
+      </c>
+      <c r="F681" t="n">
+        <v>-969.9</v>
+      </c>
+      <c r="G681" t="n">
+        <v>0</v>
+      </c>
+      <c r="H681" t="n">
+        <v>15516509.405</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>3377178.65</v>
+      </c>
+      <c r="D682" t="n">
+        <v>0</v>
+      </c>
+      <c r="E682" t="n">
+        <v>0</v>
+      </c>
+      <c r="F682" t="n">
+        <v>0</v>
+      </c>
+      <c r="G682" t="n">
+        <v>-63950.2</v>
+      </c>
+      <c r="H682" t="n">
+        <v>3313228.45</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>17723499.783</v>
+      </c>
+      <c r="D683" t="n">
+        <v>0</v>
+      </c>
+      <c r="E683" t="n">
+        <v>0</v>
+      </c>
+      <c r="F683" t="n">
+        <v>0</v>
+      </c>
+      <c r="G683" t="n">
+        <v>63950.2</v>
+      </c>
+      <c r="H683" t="n">
+        <v>17787449.983</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>178515.19</v>
+      </c>
+      <c r="D684" t="n">
+        <v>0</v>
+      </c>
+      <c r="E684" t="n">
+        <v>0</v>
+      </c>
+      <c r="F684" t="n">
+        <v>0</v>
+      </c>
+      <c r="G684" t="n">
+        <v>0</v>
+      </c>
+      <c r="H684" t="n">
+        <v>178515.19</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>2705126.654</v>
+      </c>
+      <c r="D685" t="n">
+        <v>0</v>
+      </c>
+      <c r="E685" t="n">
+        <v>0</v>
+      </c>
+      <c r="F685" t="n">
+        <v>0</v>
+      </c>
+      <c r="G685" t="n">
+        <v>0</v>
+      </c>
+      <c r="H685" t="n">
+        <v>2705126.654</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D686" t="n">
+        <v>0</v>
+      </c>
+      <c r="E686" t="n">
+        <v>0</v>
+      </c>
+      <c r="F686" t="n">
+        <v>0</v>
+      </c>
+      <c r="G686" t="n">
+        <v>0</v>
+      </c>
+      <c r="H686" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>135533079.583</v>
+      </c>
+      <c r="D687" t="n">
+        <v>0</v>
+      </c>
+      <c r="E687" t="n">
+        <v>0</v>
+      </c>
+      <c r="F687" t="n">
+        <v>0</v>
+      </c>
+      <c r="G687" t="n">
+        <v>0</v>
+      </c>
+      <c r="H687" t="n">
+        <v>135533079.583</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>4384009.017</v>
+      </c>
+      <c r="D688" t="n">
+        <v>0</v>
+      </c>
+      <c r="E688" t="n">
+        <v>0</v>
+      </c>
+      <c r="F688" t="n">
+        <v>0</v>
+      </c>
+      <c r="G688" t="n">
+        <v>0</v>
+      </c>
+      <c r="H688" t="n">
+        <v>4384009.017</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>24508690.746</v>
+      </c>
+      <c r="D689" t="n">
+        <v>0</v>
+      </c>
+      <c r="E689" t="n">
+        <v>0</v>
+      </c>
+      <c r="F689" t="n">
+        <v>0</v>
+      </c>
+      <c r="G689" t="n">
+        <v>0</v>
+      </c>
+      <c r="H689" t="n">
+        <v>24508690.746</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>0</v>
+      </c>
+      <c r="D690" t="n">
+        <v>0</v>
+      </c>
+      <c r="E690" t="n">
+        <v>0</v>
+      </c>
+      <c r="F690" t="n">
+        <v>0</v>
+      </c>
+      <c r="G690" t="n">
+        <v>0</v>
+      </c>
+      <c r="H690" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>0</v>
+      </c>
+      <c r="D691" t="n">
+        <v>0</v>
+      </c>
+      <c r="E691" t="n">
+        <v>0</v>
+      </c>
+      <c r="F691" t="n">
+        <v>0</v>
+      </c>
+      <c r="G691" t="n">
+        <v>0</v>
+      </c>
+      <c r="H691" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>582110.3370000001</v>
+      </c>
+      <c r="D692" t="n">
+        <v>0</v>
+      </c>
+      <c r="E692" t="n">
+        <v>0</v>
+      </c>
+      <c r="F692" t="n">
+        <v>0</v>
+      </c>
+      <c r="G692" t="n">
+        <v>0</v>
+      </c>
+      <c r="H692" t="n">
+        <v>582110.3370000001</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>945167.377</v>
+      </c>
+      <c r="D693" t="n">
+        <v>0</v>
+      </c>
+      <c r="E693" t="n">
+        <v>0</v>
+      </c>
+      <c r="F693" t="n">
+        <v>0</v>
+      </c>
+      <c r="G693" t="n">
+        <v>0</v>
+      </c>
+      <c r="H693" t="n">
+        <v>945167.377</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>5417618.057</v>
+      </c>
+      <c r="D694" t="n">
+        <v>0</v>
+      </c>
+      <c r="E694" t="n">
+        <v>0</v>
+      </c>
+      <c r="F694" t="n">
+        <v>0</v>
+      </c>
+      <c r="G694" t="n">
+        <v>0</v>
+      </c>
+      <c r="H694" t="n">
+        <v>5417618.057</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>7740765.443</v>
+      </c>
+      <c r="D695" t="n">
+        <v>0</v>
+      </c>
+      <c r="E695" t="n">
+        <v>1413221.936</v>
+      </c>
+      <c r="F695" t="n">
+        <v>-1413221.936</v>
+      </c>
+      <c r="G695" t="n">
+        <v>0</v>
+      </c>
+      <c r="H695" t="n">
+        <v>6327543.507</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>6213093.36</v>
+      </c>
+      <c r="D696" t="n">
+        <v>0</v>
+      </c>
+      <c r="E696" t="n">
+        <v>0</v>
+      </c>
+      <c r="F696" t="n">
+        <v>0</v>
+      </c>
+      <c r="G696" t="n">
+        <v>-4991.43</v>
+      </c>
+      <c r="H696" t="n">
+        <v>6208101.93</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>1679230.33</v>
+      </c>
+      <c r="D697" t="n">
+        <v>0</v>
+      </c>
+      <c r="E697" t="n">
+        <v>0</v>
+      </c>
+      <c r="F697" t="n">
+        <v>0</v>
+      </c>
+      <c r="G697" t="n">
+        <v>4991.43</v>
+      </c>
+      <c r="H697" t="n">
+        <v>1684221.76</v>
       </c>
     </row>
   </sheetData>
@@ -19335,10 +20007,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1064402.578</v>
+        <v>1166701.278</v>
       </c>
       <c r="C2" t="n">
-        <v>22226973.992</v>
+        <v>22124675.292</v>
       </c>
       <c r="D2" t="n">
         <v>23291376.57</v>
@@ -19351,13 +20023,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38786843.791</v>
+        <v>38170680.957</v>
       </c>
       <c r="C3" t="n">
         <v>11627379.071</v>
       </c>
       <c r="D3" t="n">
-        <v>50414222.862</v>
+        <v>49798060.028</v>
       </c>
     </row>
     <row r="4">
@@ -19367,13 +20039,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9068712.385</v>
+        <v>9150535.734999999</v>
       </c>
       <c r="C4" t="n">
-        <v>11785958.483</v>
+        <v>11745025.983</v>
       </c>
       <c r="D4" t="n">
-        <v>20854670.868</v>
+        <v>20895561.718</v>
       </c>
     </row>
     <row r="5">
@@ -19383,13 +20055,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15517479.305</v>
+        <v>15516509.405</v>
       </c>
       <c r="C5" t="n">
         <v>1637870.342</v>
       </c>
       <c r="D5" t="n">
-        <v>17155349.647</v>
+        <v>17154379.747</v>
       </c>
     </row>
     <row r="6">
@@ -19399,10 +20071,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17723499.783</v>
+        <v>17787449.983</v>
       </c>
       <c r="C6" t="n">
-        <v>3377178.65</v>
+        <v>3313228.45</v>
       </c>
       <c r="D6" t="n">
         <v>21100678.433</v>
@@ -19495,13 +20167,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7740765.443</v>
+        <v>6327543.507</v>
       </c>
       <c r="C12" t="n">
         <v>5417618.057</v>
       </c>
       <c r="D12" t="n">
-        <v>13158383.5</v>
+        <v>11745161.564</v>
       </c>
     </row>
     <row r="13">
@@ -19511,13 +20183,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1679230.33</v>
+        <v>1684221.76</v>
       </c>
       <c r="C13" t="n">
-        <v>6213093.36</v>
+        <v>6208101.93</v>
       </c>
       <c r="D13" t="n">
-        <v>7892323.69</v>
+        <v>7892323.689999999</v>
       </c>
     </row>
   </sheetData>
@@ -19563,13 +20235,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255272997.975</v>
+        <v>253495706.985</v>
       </c>
       <c r="C2" t="n">
-        <v>79411720.469</v>
+        <v>79199547.639</v>
       </c>
       <c r="D2" t="n">
-        <v>334684718.444</v>
+        <v>332695254.624</v>
       </c>
     </row>
     <row r="3">
@@ -19640,7 +20312,7 @@
         <v>2527837.51</v>
       </c>
       <c r="E8" t="n">
-        <v>1064402.578</v>
+        <v>1166701.278</v>
       </c>
     </row>
     <row r="9">
@@ -19661,7 +20333,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>22226973.992</v>
+        <v>22124675.292</v>
       </c>
     </row>
     <row r="10">
@@ -19679,10 +20351,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>4620774.780999999</v>
+        <v>5236937.615</v>
       </c>
       <c r="E10" t="n">
-        <v>38786843.791</v>
+        <v>38170680.957</v>
       </c>
     </row>
     <row r="11">
@@ -19718,13 +20390,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>627861.84</v>
+        <v>668752.6899999999</v>
       </c>
       <c r="D12" t="n">
         <v>3770888.288</v>
       </c>
       <c r="E12" t="n">
-        <v>9068712.385</v>
+        <v>9150535.734999999</v>
       </c>
     </row>
     <row r="13">
@@ -19745,7 +20417,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>11785958.483</v>
+        <v>11745025.983</v>
       </c>
     </row>
     <row r="14">
@@ -19763,10 +20435,10 @@
         <v>8820.200000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>71268.08900000001</v>
+        <v>72237.989</v>
       </c>
       <c r="E14" t="n">
-        <v>15517479.305</v>
+        <v>15516509.405</v>
       </c>
     </row>
     <row r="15">
@@ -19808,7 +20480,7 @@
         <v>51197.61</v>
       </c>
       <c r="E16" t="n">
-        <v>17723499.783</v>
+        <v>17787449.983</v>
       </c>
     </row>
     <row r="17">
@@ -19829,7 +20501,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>3377178.65</v>
+        <v>3313228.45</v>
       </c>
     </row>
     <row r="18">
@@ -20057,10 +20729,10 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>4505340.429</v>
+        <v>5918562.365</v>
       </c>
       <c r="E28" t="n">
-        <v>7740765.443</v>
+        <v>6327543.507</v>
       </c>
     </row>
     <row r="29">
@@ -20102,7 +20774,7 @@
         <v>1346417.92</v>
       </c>
       <c r="E30" t="n">
-        <v>1679230.33</v>
+        <v>1684221.76</v>
       </c>
     </row>
     <row r="31">
@@ -20123,7 +20795,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>6213093.36</v>
+        <v>6208101.93</v>
       </c>
     </row>
     <row r="32">

--- a/silver_daily_report.xlsx
+++ b/silver_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H697"/>
+  <dimension ref="A1:H721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19961,6 +19961,678 @@
         <v>4991.43</v>
       </c>
       <c r="H697" t="n">
+        <v>1684221.76</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>22124675.292</v>
+      </c>
+      <c r="D698" t="n">
+        <v>0</v>
+      </c>
+      <c r="E698" t="n">
+        <v>0</v>
+      </c>
+      <c r="F698" t="n">
+        <v>0</v>
+      </c>
+      <c r="G698" t="n">
+        <v>0</v>
+      </c>
+      <c r="H698" t="n">
+        <v>22124675.292</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>1166701.278</v>
+      </c>
+      <c r="D699" t="n">
+        <v>0</v>
+      </c>
+      <c r="E699" t="n">
+        <v>0</v>
+      </c>
+      <c r="F699" t="n">
+        <v>0</v>
+      </c>
+      <c r="G699" t="n">
+        <v>0</v>
+      </c>
+      <c r="H699" t="n">
+        <v>1166701.278</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>11627379.071</v>
+      </c>
+      <c r="D700" t="n">
+        <v>0</v>
+      </c>
+      <c r="E700" t="n">
+        <v>0</v>
+      </c>
+      <c r="F700" t="n">
+        <v>0</v>
+      </c>
+      <c r="G700" t="n">
+        <v>0</v>
+      </c>
+      <c r="H700" t="n">
+        <v>11627379.071</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>38170680.957</v>
+      </c>
+      <c r="D701" t="n">
+        <v>0</v>
+      </c>
+      <c r="E701" t="n">
+        <v>0</v>
+      </c>
+      <c r="F701" t="n">
+        <v>0</v>
+      </c>
+      <c r="G701" t="n">
+        <v>0</v>
+      </c>
+      <c r="H701" t="n">
+        <v>38170680.957</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>11745025.983</v>
+      </c>
+      <c r="D702" t="n">
+        <v>0</v>
+      </c>
+      <c r="E702" t="n">
+        <v>0</v>
+      </c>
+      <c r="F702" t="n">
+        <v>0</v>
+      </c>
+      <c r="G702" t="n">
+        <v>0</v>
+      </c>
+      <c r="H702" t="n">
+        <v>11745025.983</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>9150535.734999999</v>
+      </c>
+      <c r="D703" t="n">
+        <v>0</v>
+      </c>
+      <c r="E703" t="n">
+        <v>4904.1</v>
+      </c>
+      <c r="F703" t="n">
+        <v>-4904.1</v>
+      </c>
+      <c r="G703" t="n">
+        <v>0</v>
+      </c>
+      <c r="H703" t="n">
+        <v>9145631.635</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>1637870.342</v>
+      </c>
+      <c r="D704" t="n">
+        <v>0</v>
+      </c>
+      <c r="E704" t="n">
+        <v>0</v>
+      </c>
+      <c r="F704" t="n">
+        <v>0</v>
+      </c>
+      <c r="G704" t="n">
+        <v>0</v>
+      </c>
+      <c r="H704" t="n">
+        <v>1637870.342</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>15516509.405</v>
+      </c>
+      <c r="D705" t="n">
+        <v>0</v>
+      </c>
+      <c r="E705" t="n">
+        <v>0</v>
+      </c>
+      <c r="F705" t="n">
+        <v>0</v>
+      </c>
+      <c r="G705" t="n">
+        <v>0</v>
+      </c>
+      <c r="H705" t="n">
+        <v>15516509.405</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>3313228.45</v>
+      </c>
+      <c r="D706" t="n">
+        <v>0</v>
+      </c>
+      <c r="E706" t="n">
+        <v>0</v>
+      </c>
+      <c r="F706" t="n">
+        <v>0</v>
+      </c>
+      <c r="G706" t="n">
+        <v>0</v>
+      </c>
+      <c r="H706" t="n">
+        <v>3313228.45</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>17787449.983</v>
+      </c>
+      <c r="D707" t="n">
+        <v>0</v>
+      </c>
+      <c r="E707" t="n">
+        <v>0</v>
+      </c>
+      <c r="F707" t="n">
+        <v>0</v>
+      </c>
+      <c r="G707" t="n">
+        <v>0</v>
+      </c>
+      <c r="H707" t="n">
+        <v>17787449.983</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>178515.19</v>
+      </c>
+      <c r="D708" t="n">
+        <v>0</v>
+      </c>
+      <c r="E708" t="n">
+        <v>0</v>
+      </c>
+      <c r="F708" t="n">
+        <v>0</v>
+      </c>
+      <c r="G708" t="n">
+        <v>0</v>
+      </c>
+      <c r="H708" t="n">
+        <v>178515.19</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>2705126.654</v>
+      </c>
+      <c r="D709" t="n">
+        <v>0</v>
+      </c>
+      <c r="E709" t="n">
+        <v>0</v>
+      </c>
+      <c r="F709" t="n">
+        <v>0</v>
+      </c>
+      <c r="G709" t="n">
+        <v>0</v>
+      </c>
+      <c r="H709" t="n">
+        <v>2705126.654</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>11981013.97</v>
+      </c>
+      <c r="D710" t="n">
+        <v>0</v>
+      </c>
+      <c r="E710" t="n">
+        <v>0</v>
+      </c>
+      <c r="F710" t="n">
+        <v>0</v>
+      </c>
+      <c r="G710" t="n">
+        <v>0</v>
+      </c>
+      <c r="H710" t="n">
+        <v>11981013.97</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>135533079.583</v>
+      </c>
+      <c r="D711" t="n">
+        <v>0</v>
+      </c>
+      <c r="E711" t="n">
+        <v>599857.2</v>
+      </c>
+      <c r="F711" t="n">
+        <v>-599857.2</v>
+      </c>
+      <c r="G711" t="n">
+        <v>0</v>
+      </c>
+      <c r="H711" t="n">
+        <v>134933222.383</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>4384009.017</v>
+      </c>
+      <c r="D712" t="n">
+        <v>0</v>
+      </c>
+      <c r="E712" t="n">
+        <v>0</v>
+      </c>
+      <c r="F712" t="n">
+        <v>0</v>
+      </c>
+      <c r="G712" t="n">
+        <v>0</v>
+      </c>
+      <c r="H712" t="n">
+        <v>4384009.017</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>24508690.746</v>
+      </c>
+      <c r="D713" t="n">
+        <v>0</v>
+      </c>
+      <c r="E713" t="n">
+        <v>0</v>
+      </c>
+      <c r="F713" t="n">
+        <v>0</v>
+      </c>
+      <c r="G713" t="n">
+        <v>0</v>
+      </c>
+      <c r="H713" t="n">
+        <v>24508690.746</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>0</v>
+      </c>
+      <c r="D714" t="n">
+        <v>0</v>
+      </c>
+      <c r="E714" t="n">
+        <v>0</v>
+      </c>
+      <c r="F714" t="n">
+        <v>0</v>
+      </c>
+      <c r="G714" t="n">
+        <v>0</v>
+      </c>
+      <c r="H714" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT ARMORED, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>0</v>
+      </c>
+      <c r="D715" t="n">
+        <v>0</v>
+      </c>
+      <c r="E715" t="n">
+        <v>0</v>
+      </c>
+      <c r="F715" t="n">
+        <v>0</v>
+      </c>
+      <c r="G715" t="n">
+        <v>0</v>
+      </c>
+      <c r="H715" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>582110.3370000001</v>
+      </c>
+      <c r="D716" t="n">
+        <v>0</v>
+      </c>
+      <c r="E716" t="n">
+        <v>0</v>
+      </c>
+      <c r="F716" t="n">
+        <v>0</v>
+      </c>
+      <c r="G716" t="n">
+        <v>0</v>
+      </c>
+      <c r="H716" t="n">
+        <v>582110.3370000001</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>945167.377</v>
+      </c>
+      <c r="D717" t="n">
+        <v>0</v>
+      </c>
+      <c r="E717" t="n">
+        <v>0</v>
+      </c>
+      <c r="F717" t="n">
+        <v>0</v>
+      </c>
+      <c r="G717" t="n">
+        <v>0</v>
+      </c>
+      <c r="H717" t="n">
+        <v>945167.377</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>5417618.057</v>
+      </c>
+      <c r="D718" t="n">
+        <v>0</v>
+      </c>
+      <c r="E718" t="n">
+        <v>0</v>
+      </c>
+      <c r="F718" t="n">
+        <v>0</v>
+      </c>
+      <c r="G718" t="n">
+        <v>0</v>
+      </c>
+      <c r="H718" t="n">
+        <v>5417618.057</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>6327543.507</v>
+      </c>
+      <c r="D719" t="n">
+        <v>0</v>
+      </c>
+      <c r="E719" t="n">
+        <v>0</v>
+      </c>
+      <c r="F719" t="n">
+        <v>0</v>
+      </c>
+      <c r="G719" t="n">
+        <v>0</v>
+      </c>
+      <c r="H719" t="n">
+        <v>6327543.507</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>6208101.93</v>
+      </c>
+      <c r="D720" t="n">
+        <v>0</v>
+      </c>
+      <c r="E720" t="n">
+        <v>0</v>
+      </c>
+      <c r="F720" t="n">
+        <v>0</v>
+      </c>
+      <c r="G720" t="n">
+        <v>0</v>
+      </c>
+      <c r="H720" t="n">
+        <v>6208101.93</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>1684221.76</v>
+      </c>
+      <c r="D721" t="n">
+        <v>0</v>
+      </c>
+      <c r="E721" t="n">
+        <v>0</v>
+      </c>
+      <c r="F721" t="n">
+        <v>0</v>
+      </c>
+      <c r="G721" t="n">
+        <v>0</v>
+      </c>
+      <c r="H721" t="n">
         <v>1684221.76</v>
       </c>
     </row>
@@ -20039,13 +20711,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9150535.734999999</v>
+        <v>9145631.635</v>
       </c>
       <c r="C4" t="n">
         <v>11745025.983</v>
       </c>
       <c r="D4" t="n">
-        <v>20895561.718</v>
+        <v>20890657.618</v>
       </c>
     </row>
     <row r="5">
@@ -20103,13 +20775,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>135533079.583</v>
+        <v>134933222.383</v>
       </c>
       <c r="C8" t="n">
         <v>11981013.97</v>
       </c>
       <c r="D8" t="n">
-        <v>147514093.553</v>
+        <v>146914236.353</v>
       </c>
     </row>
     <row r="9">
@@ -20235,13 +20907,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253495706.985</v>
+        <v>252890945.685</v>
       </c>
       <c r="C2" t="n">
         <v>79199547.639</v>
       </c>
       <c r="D2" t="n">
-        <v>332695254.624</v>
+        <v>332090493.324</v>
       </c>
     </row>
     <row r="3">
@@ -20393,10 +21065,10 @@
         <v>668752.6899999999</v>
       </c>
       <c r="D12" t="n">
-        <v>3770888.288</v>
+        <v>3775792.388</v>
       </c>
       <c r="E12" t="n">
-        <v>9150535.734999999</v>
+        <v>9145631.635</v>
       </c>
     </row>
     <row r="13">
@@ -20561,10 +21233,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>5280646.100000001</v>
+        <v>5880503.3</v>
       </c>
       <c r="E20" t="n">
-        <v>135533079.583</v>
+        <v>134933222.383</v>
       </c>
     </row>
     <row r="21">
